--- a/rapporten/voorbeeld/dagrapport.xlsx
+++ b/rapporten/voorbeeld/dagrapport.xlsx
@@ -25,9 +25,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="€ #,##0.00;[Red]-€ #,##0.00"/>
-    <numFmt numFmtId="165" formatCode="0.00%;[Red]-0.00%"/>
+    <numFmt numFmtId="165" formatCode="[Color10]+€ #,##0.00;[Red]-€ #,##0.00;€ 0.00"/>
+    <numFmt numFmtId="166" formatCode="[Color10]+0.00%;[Red]-0.00%;0.00%"/>
+    <numFmt numFmtId="167" formatCode="0.00%;[Red]-0.00%"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -45,7 +47,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +57,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F3A5F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7D7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9F2D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -70,17 +82,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -729,16 +745,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -754,25 +773,40 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Vandaag</t>
+          <t>Winst of verlies</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Sinds start €</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Sinds start %</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Vandaag €</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Vandaag %</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Sinds start %</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Afgesloten trades €</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Tegenover wereld-ETF</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Klaar voor echt geld?</t>
         </is>
@@ -785,21 +819,32 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>9879.74</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>-105.2700000000004</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>-0.01054280366269045</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>-0.01202599999999998</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>-0.01099848832890138</v>
-      </c>
-      <c r="G2" t="inlineStr">
+        <v>9891.379999999999</v>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>VERLIES</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>-108.62</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>-0.01086200000000004</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>-93.63000000000102</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>-0.009377056207254819</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>-0.009832740873465751</v>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>Nog niet klaar: de bot is nog bezig met bewijzen. Blijven oefenen.</t>
         </is>
@@ -812,21 +857,32 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>10029.84</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>26.94000000000051</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>0.002693218966499655</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>0.002984000000000098</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>0.002237534300288724</v>
-      </c>
-      <c r="G3" t="inlineStr">
+        <v>10029.01</v>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>WINST</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>29.01</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>0.002901000000000042</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>26.11000000000058</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>0.002610243029521397</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>0.002154558363310466</v>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>Nog niet klaar: de bot is nog bezig met bewijzen. Blijven oefenen.</t>
         </is>
@@ -835,96 +891,95 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Winst of verlies = waarde nu tegenover de €10.000 bij de start, inclusief posities die nog openstaan. Afgesloten trades = winst of verlies dat al echt is vastgezet door te verkopen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Handelsdag 2026-10-12. Twee oefenbots met elk €10.000 nepgeld. Geen beleggingsadvies.</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Investeerder: wat de bot eruit haalt</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="B8" s="5" t="inlineStr">
+    <row r="10" ht="30" customHeight="1">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>De markt stijgt: de kern (wereld-ETF) doet zijn werk, de sterkste aandelen lopen mee.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="B9" s="5" t="inlineStr">
+    <row r="11" ht="30" customHeight="1">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>Uit de top gevallen: IFX.DE, SMH. Blijft dat zo, dan worden ze bij de volgende herverdeling (eerste handelsdag van 2026-11) vervangen door CRWD, PANW.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Trend-agent: wat de bot eruit haalt</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="B12" s="5" t="inlineStr">
+    <row r="14" ht="30" customHeight="1">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>De markt stijgt breed: goede omstandigheden voor trendvolgen.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="B13" s="5" t="inlineStr">
+    <row r="15" ht="30" customHeight="1">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>De markt is rustig: stops liggen dichterbij, posities kunnen iets groter.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="B14" s="5" t="inlineStr">
+    <row r="16" ht="30" customHeight="1">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>Amerika staat er duidelijk beter voor dan Europa (78% tegen 52% in een stijgende trend).</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>21 van de 50 instrumenten zijn een koopbare trend: veel keus, de bot neemt alleen de rustigste, sterkste.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="B16" s="5" t="inlineStr">
+    <row r="17" ht="30" customHeight="1">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>Alle plekken zijn bezet, dus de bot koopt niets bij, hoe sterk een trend ook is.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>Vandaag gedaan</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" t="inlineStr">
+    <row r="20">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Niets gekocht of verkocht.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="6">
     <mergeCell ref="B16:G16"/>
+    <mergeCell ref="B10:G10"/>
     <mergeCell ref="B14:G14"/>
-    <mergeCell ref="B9:G9"/>
-    <mergeCell ref="B8:G8"/>
-    <mergeCell ref="B12:G12"/>
-    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="B17:G17"/>
     <mergeCell ref="B15:G15"/>
+    <mergeCell ref="B11:G11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -956,144 +1011,144 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Wereld-ETF</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>Een fonds met ongeveer 1.500 grote bedrijven wereldwijd (IWDA). Dit is de maatstaf: doet de bot het beter dan dit simpelweg vasthouden?</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>200-daags gemiddelde</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>De gemiddelde slotkoers van de laatste 200 handelsdagen. Erboven = stijgende trend op lange termijn.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Breedte</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Hoeveel van de gevolgde aandelen boven hun 200-daags gemiddelde staan. Hoog = de stijging wordt breed gedragen.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Beweeglijkheid</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Hoe hard de koersen op en neer gaan, vergeleken met het afgelopen jaar.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>ATR</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>De gemiddelde dagbeweging van een aandeel. De stop-loss ligt 2x de ATR onder de instap.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Maat voor hoe hard een koers recent is gestegen (0-100). Boven 70-75 = mogelijk te snel opgelopen.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Laat zien of een stijging versnelt (positief) of vertraagt (negatief).</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Stop-loss</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>De prijs waarop de bot automatisch verkoopt om het verlies te beperken. Schuift mee omhoog als het goed gaat.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Resultaat van een trade gedeeld door het risico bij instap. +2 R = twee keer zoveel gewonnen als je riskeerde.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Instapmoment</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>Ongeteste vuistregel: gunstig = sterk maar niet ver weggelopen; opgelopen = ver boven het 20-daags gemiddelde.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>Momentum</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Stijging over 12 maanden zonder de laatste maand. De investeerder kiest de 5 hoogste.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Kill switch</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>Noodstop. Bij te veel verlies koopt de bot niets meer tot jij hem weer aanzet.</t>
         </is>
@@ -1124,7 +1179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1150,323 +1205,306 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>Markt (IWDA.AS)</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>koers 131,73, 9,6% boven het 200-daags gemiddelde (120,18); de afgelopen maand +4,0%. Trend: stijgend.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>Beweeglijkheid</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>8% op jaarbasis, tegen normaal 10% het afgelopen jaar: laag.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Breedte</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>33 van de 50 instrumenten staan boven hun 200-daags gemiddelde (66%; EU 12 van 23, US 21 van 27).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Sterkste momentum nu (12 maanden, zonder laatste maand)</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>Micron +409%, AMD +130%, CrowdStrike +91%, Palo Alto Networks +79%, ASML +70%.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>BTC-USD</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>15,4% boven het 200-daags gemiddelde (mag in de mix).</t>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>15,7% boven het 200-daags gemiddelde (mag in de mix).</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>ETH-USD</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>17,2% boven het 200-daags gemiddelde (mag in de mix).</t>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>17,8% boven het 200-daags gemiddelde (mag in de mix).</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Conclusie</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>De markt stijgt: de kern (wereld-ETF) doet zijn werk, de sterkste aandelen lopen mee.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Conclusie</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>Uit de top gevallen: IFX.DE, SMH. Blijft dat zo, dan worden ze bij de volgende herverdeling (eerste handelsdag van 2026-11) vervangen door CRWD, PANW.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Markt (IWDA.AS)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>koers 131,73, 9,6% boven het 200-daags gemiddelde (120,18); de afgelopen maand +4,0%. Trend: stijgend.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>Beweeglijkheid</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>8% op jaarbasis, tegen normaal 10% het afgelopen jaar: laag.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Breedte</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>33 van de 50 instrumenten staan boven hun 200-daags gemiddelde (66%; EU 12 van 23, US 21 van 27).</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>Bekeken</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>50 instrumenten.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Afgevallen (een instrument kan op meer regels afvallen)</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>geen stijgende trend (koers niet boven 50- en 200-daags gemiddelde): 25; niet gestegen over 1 of 3 maanden: 24; te weinig handel: 1.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>Door de zeef</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>21. Koopbare trends: 21.</t>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>20. Koopbare trends: 20.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>Conclusie</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>De markt stijgt breed: goede omstandigheden voor trendvolgen.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>Conclusie</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>De markt is rustig: stops liggen dichterbij, posities kunnen iets groter.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Conclusie</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>Amerika staat er duidelijk beter voor dan Europa (78% tegen 52% in een stijgende trend).</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>Conclusie</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>21 van de 50 instrumenten zijn een koopbare trend: veel keus, de bot neemt alleen de rustigste, sterkste.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>Trend-agent</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>Conclusie</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>Alle plekken zijn bezet, dus de bot koopt niets bij, hoe sterk een trend ook is.</t>
         </is>
@@ -1564,16 +1602,16 @@
       <c r="E2" t="n">
         <v>43.2368</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="4" t="n">
         <v>11.6</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" s="5" t="n">
         <v>0.0198</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="H2" s="9" t="n">
         <v>0.06279999999999999</v>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="I2" s="4" t="n">
         <v>-24.67</v>
       </c>
     </row>
@@ -1592,22 +1630,22 @@
         <v>191.5557</v>
       </c>
       <c r="D3" t="n">
-        <v>197.52</v>
+        <v>197.28</v>
       </c>
       <c r="E3" t="n">
-        <v>181.2686</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>11.93</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>0.0311</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>0.0897</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>-21.57</v>
+        <v>181.0286</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>0.0299</v>
+      </c>
+      <c r="H3" s="9" t="n">
+        <v>0.0898</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>-22.05</v>
       </c>
     </row>
     <row r="4">
@@ -1625,26 +1663,26 @@
         <v>535.3375</v>
       </c>
       <c r="D4" t="n">
-        <v>545.155</v>
+        <v>545</v>
       </c>
       <c r="E4" t="n">
         <v>509.899</v>
       </c>
-      <c r="F4" s="2" t="n">
-        <v>9.31</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>0.0183</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>0.06909999999999999</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>-23.19</v>
+      <c r="F4" s="4" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="H4" s="9" t="n">
+        <v>0.0688</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>-23.4</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Trend-agent remmen</t>
         </is>
@@ -1666,10 +1704,10 @@
           <t>Daling vanaf top</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C7" s="9" t="n">
         <v>-0.05</v>
       </c>
     </row>
@@ -1679,10 +1717,10 @@
           <t>Vandaag</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
-        <v>0.0027</v>
-      </c>
-      <c r="C8" s="3" t="n">
+      <c r="B8" s="9" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="C8" s="9" t="n">
         <v>-0.01</v>
       </c>
     </row>
@@ -1700,32 +1738,32 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Instrument</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>Waarde</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>Ingelegd</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>Resultaat €</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>Resultaat %</t>
         </is>
@@ -1743,10 +1781,10 @@
       <c r="D12" s="2" t="n">
         <v>600</v>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E12" s="4" t="n">
         <v>-35.69</v>
       </c>
-      <c r="F12" s="3" t="n">
+      <c r="F12" s="5" t="n">
         <v>-0.0595</v>
       </c>
     </row>
@@ -1757,16 +1795,16 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>567.04</v>
+        <v>568.29</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>600</v>
       </c>
-      <c r="E13" s="2" t="n">
-        <v>-32.96</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>-0.0549</v>
+      <c r="E13" s="4" t="n">
+        <v>-31.71</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-0.0528</v>
       </c>
     </row>
     <row r="14">
@@ -1781,10 +1819,10 @@
       <c r="D14" s="2" t="n">
         <v>600</v>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E14" s="4" t="n">
         <v>-30.39</v>
       </c>
-      <c r="F14" s="3" t="n">
+      <c r="F14" s="5" t="n">
         <v>-0.0507</v>
       </c>
     </row>
@@ -1795,16 +1833,16 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>585.86</v>
+        <v>589.05</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>600</v>
       </c>
-      <c r="E15" s="2" t="n">
-        <v>-14.14</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>-0.0236</v>
+      <c r="E15" s="4" t="n">
+        <v>-10.95</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>-0.0183</v>
       </c>
     </row>
     <row r="16">
@@ -1814,16 +1852,16 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>591.62</v>
+        <v>596</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>600</v>
       </c>
-      <c r="E16" s="2" t="n">
-        <v>-8.380000000000001</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>-0.014</v>
+      <c r="E16" s="4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-0.0067</v>
       </c>
     </row>
     <row r="17">
@@ -1838,10 +1876,10 @@
       <c r="D17" s="2" t="n">
         <v>6000</v>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="E17" s="4" t="n">
         <v>-3.27</v>
       </c>
-      <c r="F17" s="3" t="n">
+      <c r="F17" s="5" t="n">
         <v>-0.0005</v>
       </c>
     </row>
@@ -1852,16 +1890,16 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>501.28</v>
+        <v>502.1</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="E18" s="2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>0.0026</v>
+      <c r="E18" s="4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0.0042</v>
       </c>
     </row>
     <row r="19">
@@ -1871,16 +1909,16 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>503.3</v>
+        <v>505.29</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="E19" s="2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>0.0066</v>
+      <c r="E19" s="4" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>0.0106</v>
       </c>
     </row>
   </sheetData>
@@ -1995,37 +2033,37 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>SHELL.AS</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>Shell</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>opgelopen</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>Shell steeg +25,7% in 3 maanden en +11,0% in 1 maand; koers boven het 50-daags en dat boven het 200-daags gemiddelde; MACD positief (de stijging versnelt); handel 1,1x het normale volume; beweegt gemiddeld 2,0% per dag</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="8" t="inlineStr">
         <is>
           <t>de koers staat +7,3% van het 20-daags gemiddelde (3,7x de normale dagbeweging) en RSI is 79; na zo'n sprint volgt vaak eerst een terugval</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="8" t="inlineStr">
         <is>
           <t>al in bezit</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H2" s="8" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -2036,7 +2074,7 @@
       <c r="J2" t="n">
         <v>44.1544</v>
       </c>
-      <c r="K2" s="3" t="n">
+      <c r="K2" s="9" t="n">
         <v>-0.0396</v>
       </c>
       <c r="L2" t="n">
@@ -2056,159 +2094,159 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>SAP.DE</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>neutraal</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>SAP steeg +44,2% in 3 maanden en +11,4% in 1 maand; koers boven het 50-daags en dat boven het 200-daags gemiddelde; MACD positief (de stijging versnelt); handel 0,8x het normale volume; beweegt gemiddeld 2,7% per dag</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>de koers staat +5,8% van het 20-daags gemiddelde, RSI 67</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>SAP steeg +44,0% in 3 maanden en +11,3% in 1 maand; koers boven het 50-daags en dat boven het 200-daags gemiddelde; MACD positief (de stijging versnelt); handel 0,8x het normale volume; beweegt gemiddeld 2,8% per dag</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>de koers staat +5,7% van het 20-daags gemiddelde, RSI 66</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>al in bezit</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" s="8" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>197.6188</v>
+        <v>197.3786</v>
       </c>
       <c r="J3" t="n">
-        <v>186.7845</v>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>-0.0548</v>
+        <v>186.5443</v>
+      </c>
+      <c r="K3" s="9" t="n">
+        <v>-0.0549</v>
       </c>
       <c r="L3" t="n">
         <v>2</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>395.24</v>
+        <v>394.76</v>
       </c>
       <c r="N3" s="2" t="n">
         <v>23.67</v>
       </c>
       <c r="O3" t="n">
-        <v>219.2873</v>
+        <v>219.0472</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>XLE</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Energie-ETF</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>neutraal</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>Energie-ETF steeg +19,1% in 3 maanden en +4,3% in 1 maand; koers boven het 50-daags en dat boven het 200-daags gemiddelde; MACD positief (de stijging versnelt); handel 1,1x het normale volume; beweegt gemiddeld 1,9% per dag</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Energie-ETF steeg +19,0% in 3 maanden en +4,2% in 1 maand; koers boven het 50-daags en dat boven het 200-daags gemiddelde; MACD positief (de stijging versnelt); handel 1,1x het normale volume; beweegt gemiddeld 1,9% per dag</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>de koers staat +4,7% van het 20-daags gemiddelde, RSI 70</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>niet gekocht: alle 3 plekken zijn bezet</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>66.95350000000001</v>
+        <v>66.8884</v>
       </c>
       <c r="J4" t="n">
-        <v>64.4806</v>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>-0.0369</v>
+        <v>64.4156</v>
+      </c>
+      <c r="K4" s="9" t="n">
+        <v>-0.037</v>
       </c>
       <c r="L4" t="n">
         <v>11</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>657.98</v>
+        <v>657.05</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>26.3</v>
+        <v>26.29</v>
       </c>
       <c r="O4" t="n">
-        <v>71.89919999999999</v>
+        <v>71.83410000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>WKL.AS</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>Wolters Kluwer</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>opgelopen</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>Wolters Kluwer steeg +26,6% in 3 maanden en +19,0% in 1 maand; koers boven het 50-daags en dat boven het 200-daags gemiddelde; MACD positief (de stijging versnelt); handel 1,2x het normale volume; beweegt gemiddeld 2,9% per dag</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>de koers staat +12,1% van het 20-daags gemiddelde (4,1x de normale dagbeweging) en RSI is 76; na zo'n sprint volgt vaak eerst een terugval</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>niet gekocht: alle 3 plekken zijn bezet</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -2219,7 +2257,7 @@
       <c r="J5" t="n">
         <v>74.2423</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="9" t="n">
         <v>-0.0588</v>
       </c>
       <c r="L5" t="n">
@@ -2239,66 +2277,66 @@
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>MSFT</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>neutraal</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>Microsoft steeg +38,1% in 3 maanden en +7,9% in 1 maand; koers boven het 50-daags en dat boven het 200-daags gemiddelde; MACD positief (de stijging versnelt); handel 0,8x het normale volume; beweegt gemiddeld 2,2% per dag</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>Microsoft steeg +38,0% in 3 maanden en +7,8% in 1 maand; koers boven het 50-daags en dat boven het 200-daags gemiddelde; MACD positief (de stijging versnelt); handel 0,8x het normale volume; beweegt gemiddeld 2,2% per dag</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>de koers staat +5,1% van het 20-daags gemiddelde, RSI 71</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>al in bezit</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>545.4276</v>
+        <v>545.2725</v>
       </c>
       <c r="J6" t="n">
-        <v>521.5232999999999</v>
-      </c>
-      <c r="K6" s="3" t="n">
+        <v>521.3682</v>
+      </c>
+      <c r="K6" s="9" t="n">
         <v>-0.0438</v>
       </c>
       <c r="L6" t="n">
         <v>1</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>487.29</v>
+        <v>486.93</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>23.36</v>
+        <v>23.35</v>
       </c>
       <c r="O6" t="n">
-        <v>593.2362000000001</v>
+        <v>593.0811</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr"/>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr"/>
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Wat de oefenbot met nepgeld zou doen volgens zijn regels. Geen advies voor echt geld. Het instapmoment is een ongeteste vuistregel en wordt door de bot niet gebruikt.</t>
         </is>
@@ -2347,198 +2385,198 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>Oefentijd</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>⏳ nog bezig</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>2 van 63 handelsdagen (ongeveer 3 maanden)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>Minstens zo goed als de wereld-ETF</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>⏳ nog bezig</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>verschil tot nu toe -1,10%</t>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>verschil tot nu toe -0,98%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Daling niet veel dieper dan de ETF</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>✅ gehaald</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>bot -1,20%, ETF +0,00%</t>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>bot -1,09%, ETF +0,00%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Oordeel</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr"/>
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>Nog niet klaar: de bot is nog bezig met bewijzen. Blijven oefenen.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Oefentijd</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>⏳ nog bezig</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>3 van 63 handelsdagen (ongeveer 3 maanden)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Minstens zo goed als de wereld-ETF</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>⏳ nog bezig</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>verschil tot nu toe +0,22%</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Grootste daling onder 5%</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>✅ gehaald</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>grootste daling tot nu toe -0,04%</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Genoeg afgesloten trades</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>⏳ nog bezig</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>0 van 20</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>Oordeel</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr"/>
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>Nog niet klaar: de bot is nog bezig met bewijzen. Blijven oefenen.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr"/>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr"/>
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>Eerst bewijzen, dan een oefenaccount bij een echte broker, dan een klein bedrag met jouw goedkeuring per order. Die beslissing neem jij, niet de bot.</t>
         </is>
@@ -2555,13 +2593,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2577,10 +2617,20 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Investeerder t.o.v. start</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Trend-agent t.o.v. start</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Wereld-ETF (koers in €)</t>
         </is>
@@ -2595,8 +2645,14 @@
       <c r="B2" s="2" t="n">
         <v>10000</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2" t="n">
         <v>10000</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -2606,8 +2662,12 @@
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="2" t="n">
         <v>9996.280000000001</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>-3.72</v>
       </c>
     </row>
     <row r="4">
@@ -2617,12 +2677,18 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>9879.74</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>10029.84</v>
-      </c>
-      <c r="D4" t="n">
+        <v>9891.379999999999</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>-108.62</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>10029.01</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>29.01</v>
+      </c>
+      <c r="F4" t="n">
         <v>131.73</v>
       </c>
     </row>
@@ -2635,10 +2701,16 @@
       <c r="B5" s="2" t="n">
         <v>9985.01</v>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="4" t="n">
+        <v>-14.99</v>
+      </c>
+      <c r="D5" s="2" t="n">
         <v>10002.9</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" s="4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F5" t="n">
         <v>131.67</v>
       </c>
     </row>
@@ -2753,7 +2825,7 @@
       <c r="H2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="2" t="n"/>
+      <c r="I2" s="4" t="n"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>trend OK: 3m +23.4%, 1m +9.2%, volume x1.07</t>
@@ -2793,7 +2865,7 @@
       <c r="H3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I3" s="2" t="n"/>
+      <c r="I3" s="4" t="n"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>trend OK: 3m +40.0%, 1m +7.7%, volume x0.83</t>
@@ -2833,7 +2905,7 @@
       <c r="H4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I4" s="2" t="n"/>
+      <c r="I4" s="4" t="n"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>trend OK: 3m +37.1%, 1m +8.7%, volume x0.82</t>
@@ -2873,7 +2945,7 @@
       <c r="H5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="I5" s="2" t="n"/>
+      <c r="I5" s="4" t="n"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>doelgewicht 60%</t>
@@ -2913,7 +2985,7 @@
       <c r="H6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I6" s="2" t="n"/>
+      <c r="I6" s="4" t="n"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>doelgewicht 6%</t>
@@ -2953,7 +3025,7 @@
       <c r="H7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I7" s="2" t="n"/>
+      <c r="I7" s="4" t="n"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>doelgewicht 6%</t>
@@ -2993,7 +3065,7 @@
       <c r="H8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I8" s="2" t="n"/>
+      <c r="I8" s="4" t="n"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>doelgewicht 6%</t>
@@ -3033,7 +3105,7 @@
       <c r="H9" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="2" t="n"/>
+      <c r="I9" s="4" t="n"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>doelgewicht 6%</t>
@@ -3073,7 +3145,7 @@
       <c r="H10" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="2" t="n"/>
+      <c r="I10" s="4" t="n"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>doelgewicht 6%</t>
@@ -3113,7 +3185,7 @@
       <c r="H11" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="2" t="n"/>
+      <c r="I11" s="4" t="n"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>doelgewicht 5%</t>
@@ -3153,7 +3225,7 @@
       <c r="H12" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="2" t="n"/>
+      <c r="I12" s="4" t="n"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>doelgewicht 5%</t>
@@ -3191,48 +3263,48 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>Investeerder: status OK, 52 van 52 koersen opgehaald, marktregime stijgend-laag.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>Koersbronnen: 0 bevestigd door twee bronnen, 52 uit één bron, 0 afwijkend. Wisselkoers: bevestigd. Tweede bron overgeslagen na herhaalde fouten (GOOGL: Stooq gaf geen koersen ('&lt;!DOCTYPE html&gt;&lt;html&gt;&lt;head&gt;&lt;meta charset')).</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Trend-agent: status OK, 50 van 50 koersen opgehaald, marktregime stijgend-laag.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Koersbronnen: 0 bevestigd door twee bronnen, 50 uit één bron, 0 afwijkend. Wisselkoers: bevestigd. Tweede bron overgeslagen na herhaalde fouten (GOOGL: Stooq gaf geen koersen ('&lt;!DOCTYPE html&gt;&lt;html&gt;&lt;head&gt;&lt;meta charset')).</t>
         </is>

--- a/rapporten/voorbeeld/dagrapport.xlsx
+++ b/rapporten/voorbeeld/dagrapport.xlsx
@@ -31,7 +31,7 @@
     <numFmt numFmtId="166" formatCode="[Color10]+0.00%;[Red]-0.00%;0.00%"/>
     <numFmt numFmtId="167" formatCode="0.00%;[Red]-0.00%"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,10 +41,50 @@
     </font>
     <font>
       <b val="1"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="0052514E"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <color rgb="0052514E"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
     </font>
   </fonts>
   <fills count="5">
@@ -56,17 +96,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F3A5F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00F8D7D7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9F2D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3A5F"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,24 +122,61 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -180,12 +257,45 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>0</row>
+      <row>41</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5440680" cy="3337560"/>
+    <ext cx="7810500" cy="3905250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8572499" cy="4286249"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -205,12 +315,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>30</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5440680" cy="3337560"/>
+    <ext cx="8572499" cy="5143500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -230,12 +340,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>38</row>
+      <row>61</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5440680" cy="3337560"/>
+    <ext cx="8572499" cy="5143500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -255,12 +365,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>57</row>
+      <row>92</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5440680" cy="3337560"/>
+    <ext cx="8572499" cy="5143500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -280,12 +390,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>76</row>
+      <row>123</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5440680" cy="3337560"/>
+    <ext cx="8572499" cy="5143500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -305,12 +415,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>95</row>
+      <row>154</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5440680" cy="3337560"/>
+    <ext cx="8572499" cy="5143500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -330,12 +440,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>114</row>
+      <row>185</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5440680" cy="3337560"/>
+    <ext cx="8572499" cy="5143500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -355,12 +465,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>133</row>
+      <row>216</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5440680" cy="3337560"/>
+    <ext cx="8572499" cy="5143500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -380,12 +490,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>152</row>
+      <row>247</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5440680" cy="3337560"/>
+    <ext cx="8572499" cy="5143500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -405,12 +515,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>171</row>
+      <row>278</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5440680" cy="3337560"/>
+    <ext cx="8572499" cy="5143500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -430,12 +540,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>190</row>
+      <row>309</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5440680" cy="3337560"/>
+    <ext cx="8572499" cy="5143500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -443,6 +553,31 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>340</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8572499" cy="5143500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -743,245 +878,370 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="B1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Bot</t>
-        </is>
-      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Waarde</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Winst of verlies</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Sinds start €</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Sinds start %</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Vandaag €</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Vandaag %</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Afgesloten trades €</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Tegenover wereld-ETF</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
+          <t>Dagrapport dinsdag 13 oktober 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Twee oefenbots met elk €10.000 nepgeld. Geen beleggingsadvies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Investeerder</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Waarde nu</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>9926.040000000001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>VERLIES sinds de start</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>-73.95999999999999</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Sinds de start in %</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>-0.007395999999999958</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Al vastgezet door verkopen</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Klaar voor echt geld?</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Investeerder</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>9891.379999999999</v>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>VERLIES</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>-108.62</v>
-      </c>
-      <c r="E2" s="5" t="n">
-        <v>-0.01086200000000004</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>-93.63000000000102</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>-0.009377056207254819</v>
-      </c>
-      <c r="H2" s="4" t="n">
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Nog niet klaar: de bot is nog bezig met bewijzen. Blijven oefenen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Trend-agent</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Waarde nu</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>10038.05</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>WINST sinds de start</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>38.05</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Sinds de start in %</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>0.003804999999999836</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Vandaag</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>41.76999999999862</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Al vastgezet door verkopen</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="5" t="n">
-        <v>-0.009832740873465751</v>
-      </c>
-      <c r="J2" t="inlineStr">
+    </row>
+    <row r="17">
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Klaar voor echt geld?</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>Nog niet klaar: de bot is nog bezig met bewijzen. Blijven oefenen.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Trend-agent</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>10029.01</v>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>WINST</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>29.01</v>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>0.002901000000000042</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>26.11000000000058</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>0.002610243029521397</v>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="5" t="n">
-        <v>0.002154558363310466</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Nog niet klaar: de bot is nog bezig met bewijzen. Blijven oefenen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Winst of verlies = waarde nu tegenover de €10.000 bij de start, inclusief posities die nog openstaan. Afgesloten trades = winst of verlies dat al echt is vastgezet door te verkopen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Handelsdag 2026-10-12. Twee oefenbots met elk €10.000 nepgeld. Geen beleggingsadvies.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Investeerder: wat de bot eruit haalt</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="B10" s="8" t="inlineStr">
+    <row r="19">
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>Investeerder: wat de bot uit de analyse haalt</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="21.4" customHeight="1">
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
         <is>
           <t>De markt stijgt: de kern (wereld-ETF) doet zijn werk, de sterkste aandelen lopen mee.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Uit de top gevallen: IFX.DE, SMH. Blijft dat zo, dan worden ze bij de volgende herverdeling (eerste handelsdag van 2026-11) vervangen door CRWD, PANW.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Trend-agent: wat de bot eruit haalt</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="B14" s="8" t="inlineStr">
+    <row r="21" ht="38.8" customHeight="1">
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>Uit de top gevallen: ASML.AS, IFX.DE, SMH. Blijft dat zo, dan worden ze bij de volgende herverdeling (eerste handelsdag van 2026-11) vervangen door CRWD, PANW, INGA.AS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>Trend-agent: wat de bot uit de analyse haalt</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="21.4" customHeight="1">
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="inlineStr">
         <is>
           <t>De markt stijgt breed: goede omstandigheden voor trendvolgen.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="B15" s="8" t="inlineStr">
+    <row r="25" ht="21.4" customHeight="1">
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <t>De markt is rustig: stops liggen dichterbij, posities kunnen iets groter.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>Amerika staat er duidelijk beter voor dan Europa (78% tegen 52% in een stijgende trend).</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="B17" s="8" t="inlineStr">
+    <row r="26" ht="38.8" customHeight="1">
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>Amerika staat er duidelijk beter voor dan Europa (81% tegen 57% in een stijgende trend).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="38.8" customHeight="1">
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>24 van de 50 instrumenten zijn een koopbare trend: veel keus, de bot neemt alleen de rustigste, sterkste.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="21.4" customHeight="1">
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
         <is>
           <t>Alle plekken zijn bezet, dus de bot koopt niets bij, hoe sterk een trend ook is.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Vandaag gedaan</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Niets gekocht of verkocht.</t>
+    <row r="30">
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>Vandaag gekocht en verkocht</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="21.4" customHeight="1">
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>Investeerder kocht IWDA.AS voor €5.997,00 (doelgewicht 60%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="21.4" customHeight="1">
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="inlineStr">
+        <is>
+          <t>Investeerder kocht MU voor €599,00 (doelgewicht 6%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="21.4" customHeight="1">
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>Investeerder kocht SMH voor €599,00 (doelgewicht 6%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="21.4" customHeight="1">
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>Investeerder kocht ASML.AS voor €599,00 (doelgewicht 6%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="21.4" customHeight="1">
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>Investeerder kocht IFX.DE voor €599,00 (doelgewicht 6%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="21.4" customHeight="1">
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="inlineStr">
+        <is>
+          <t>Investeerder kocht AMD voor €599,00 (doelgewicht 6%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="21.4" customHeight="1">
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>Investeerder kocht ETH-USD voor €499,00 (doelgewicht 5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="21.4" customHeight="1">
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="inlineStr">
+        <is>
+          <t>Investeerder kocht BTC-USD voor €499,00 (doelgewicht 5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Meer weten? Zie de tabbladen hieronder: Grafieken, Analyse, Verlies en risico, Kansen, Klaar voor echt geld.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="B16:G16"/>
-    <mergeCell ref="B10:G10"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="B17:G17"/>
-    <mergeCell ref="B15:G15"/>
-    <mergeCell ref="B11:G11"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -989,7 +1249,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -999,156 +1259,156 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>Begrip</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Betekenis</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+    <row r="2" ht="35.9" customHeight="1">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Wereld-ETF</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>Een fonds met ongeveer 1.500 grote bedrijven wereldwijd (IWDA). Dit is de maatstaf: doet de bot het beter dan dit simpelweg vasthouden?</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+    <row r="3" ht="19.95" customHeight="1">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>200-daags gemiddelde</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>De gemiddelde slotkoers van de laatste 200 handelsdagen. Erboven = stijgende trend op lange termijn.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+    <row r="4" ht="19.95" customHeight="1">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Breedte</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>Hoeveel van de gevolgde aandelen boven hun 200-daags gemiddelde staan. Hoog = de stijging wordt breed gedragen.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+    <row r="5" ht="19.95" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Beweeglijkheid</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>Hoe hard de koersen op en neer gaan, vergeleken met het afgelopen jaar.</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+    <row r="6" ht="19.95" customHeight="1">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>ATR</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>De gemiddelde dagbeweging van een aandeel. De stop-loss ligt 2x de ATR onder de instap.</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+    <row r="7" ht="19.95" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>Maat voor hoe hard een koers recent is gestegen (0-100). Boven 70-75 = mogelijk te snel opgelopen.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+    <row r="8" ht="19.95" customHeight="1">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>Laat zien of een stijging versnelt (positief) of vertraagt (negatief).</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="9" ht="19.95" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Stop-loss</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>De prijs waarop de bot automatisch verkoopt om het verlies te beperken. Schuift mee omhoog als het goed gaat.</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+    <row r="10" ht="19.95" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>Resultaat van een trade gedeeld door het risico bij instap. +2 R = twee keer zoveel gewonnen als je riskeerde.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+    <row r="11" ht="19.95" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Instapmoment</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>Ongeteste vuistregel: gunstig = sterk maar niet ver weggelopen; opgelopen = ver boven het 20-daags gemiddelde.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+    <row r="12" ht="19.95" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Momentum</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>Stijging over 12 maanden zonder de laatste maand. De investeerder kiest de 5 hoogste.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+    <row r="13" ht="19.95" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Kill switch</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>Noodstop. Bij te veel verlies koopt de bot niets meer tot jij hem weer aanzet.</t>
         </is>
@@ -1156,6 +1416,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1163,12 +1424,116 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="B1:B340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="130" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="26" t="inlineStr">
+        <is>
+          <t>Grafieken van vandaag</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Elke grafiek legt bovenaan in gewone taal uit hoe het ervoor staat, en onderaan hoe je hem leest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="B4" s="27" t="inlineStr">
+        <is>
+          <t>Waarde van de bots tegenover de wereld-ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="B30" s="27" t="inlineStr">
+        <is>
+          <t>Trend-agent: Microsoft (MSFT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="24" customHeight="1">
+      <c r="B61" s="27" t="inlineStr">
+        <is>
+          <t>Trend-agent: SAP (SAP.DE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="24" customHeight="1">
+      <c r="B92" s="27" t="inlineStr">
+        <is>
+          <t>Trend-agent: Shell (SHELL.AS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="24" customHeight="1">
+      <c r="B123" s="27" t="inlineStr">
+        <is>
+          <t>Investeerder: AMD (AMD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="24" customHeight="1">
+      <c r="B154" s="27" t="inlineStr">
+        <is>
+          <t>Investeerder: ASML (ASML.AS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="24" customHeight="1">
+      <c r="B185" s="27" t="inlineStr">
+        <is>
+          <t>Investeerder: Bitcoin (BTC-USD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="24" customHeight="1">
+      <c r="B216" s="27" t="inlineStr">
+        <is>
+          <t>Investeerder: Ethereum (ETH-USD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="24" customHeight="1">
+      <c r="B247" s="27" t="inlineStr">
+        <is>
+          <t>Investeerder: Infineon (IFX.DE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="278" ht="24" customHeight="1">
+      <c r="B278" s="27" t="inlineStr">
+        <is>
+          <t>Investeerder: iShares MSCI World (IWDA.AS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="309" ht="24" customHeight="1">
+      <c r="B309" s="27" t="inlineStr">
+        <is>
+          <t>Investeerder: Micron (MU)</t>
+        </is>
+      </c>
+    </row>
+    <row r="340" ht="24" customHeight="1">
+      <c r="B340" s="27" t="inlineStr">
+        <is>
+          <t>Investeerder: Halfgeleider-ETF (SMH)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -1177,9 +1542,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1188,323 +1553,340 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>Bot</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Onderdeel</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>Wat de bot zag of concludeert</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+    <row r="2" ht="19.95" customHeight="1">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>Markt (IWDA.AS)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>koers 131,73, 9,6% boven het 200-daags gemiddelde (120,18); de afgelopen maand +4,0%. Trend: stijgend.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="C2" s="16" t="inlineStr">
+        <is>
+          <t>koers 132,29, 10,0% boven het 200-daags gemiddelde (120,29); de afgelopen maand +4,6%. Trend: stijgend.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="19.95" customHeight="1">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Beweeglijkheid</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>8% op jaarbasis, tegen normaal 10% het afgelopen jaar: laag.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+    <row r="4" ht="19.95" customHeight="1">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>Breedte</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>33 van de 50 instrumenten staan boven hun 200-daags gemiddelde (66%; EU 12 van 23, US 21 van 27).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>35 van de 50 instrumenten staan boven hun 200-daags gemiddelde (70%; EU 13 van 23, US 22 van 27).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="51.85" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>Sterkste momentum nu (12 maanden, zonder laatste maand)</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>Micron +409%, AMD +130%, CrowdStrike +91%, Palo Alto Networks +79%, ASML +70%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>Micron +382%, AMD +133%, CrowdStrike +91%, Palo Alto Networks +76%, ING +63%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="19.95" customHeight="1">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>BTC-USD</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>15,7% boven het 200-daags gemiddelde (mag in de mix).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>14,4% boven het 200-daags gemiddelde (mag in de mix).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="19.95" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>ETH-USD</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>17,8% boven het 200-daags gemiddelde (mag in de mix).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>15,1% boven het 200-daags gemiddelde (mag in de mix).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="19.95" customHeight="1">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>Conclusie</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>De markt stijgt: de kern (wereld-ETF) doet zijn werk, de sterkste aandelen lopen mee.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="9" ht="35.9" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>Conclusie</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>Uit de top gevallen: IFX.DE, SMH. Blijft dat zo, dan worden ze bij de volgende herverdeling (eerste handelsdag van 2026-11) vervangen door CRWD, PANW.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>Uit de top gevallen: ASML.AS, IFX.DE, SMH. Blijft dat zo, dan worden ze bij de volgende herverdeling (eerste handelsdag van 2026-11) vervangen door CRWD, PANW, INGA.AS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="19.95" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>Markt (IWDA.AS)</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>koers 131,73, 9,6% boven het 200-daags gemiddelde (120,18); de afgelopen maand +4,0%. Trend: stijgend.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>koers 132,29, 10,0% boven het 200-daags gemiddelde (120,29); de afgelopen maand +4,6%. Trend: stijgend.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="19.95" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>Beweeglijkheid</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>8% op jaarbasis, tegen normaal 10% het afgelopen jaar: laag.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+    <row r="12" ht="19.95" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>Breedte</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>33 van de 50 instrumenten staan boven hun 200-daags gemiddelde (66%; EU 12 van 23, US 21 van 27).</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>35 van de 50 instrumenten staan boven hun 200-daags gemiddelde (70%; EU 13 van 23, US 22 van 27).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="19.95" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>Bekeken</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t>50 instrumenten.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+    <row r="14" ht="51.85" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>Afgevallen (een instrument kan op meer regels afvallen)</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>geen stijgende trend (koers niet boven 50- en 200-daags gemiddelde): 25; niet gestegen over 1 of 3 maanden: 24; te weinig handel: 1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>geen stijgende trend (koers niet boven 50- en 200-daags gemiddelde): 23; niet gestegen over 1 of 3 maanden: 21; te weinig handel: 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="19.95" customHeight="1">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>Door de zeef</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>20. Koopbare trends: 20.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>24. Koopbare trends: 24.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="19.95" customHeight="1">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>Conclusie</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>De markt stijgt breed: goede omstandigheden voor trendvolgen.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+    <row r="17" ht="19.95" customHeight="1">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>Conclusie</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C17" s="16" t="inlineStr">
         <is>
           <t>De markt is rustig: stops liggen dichterbij, posities kunnen iets groter.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+    <row r="18" ht="19.95" customHeight="1">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>Conclusie</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>Amerika staat er duidelijk beter voor dan Europa (78% tegen 52% in een stijgende trend).</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>Amerika staat er duidelijk beter voor dan Europa (81% tegen 57% in een stijgende trend).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="19.95" customHeight="1">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>Conclusie</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>24 van de 50 instrumenten zijn een koopbare trend: veel keus, de bot neemt alleen de rustigste, sterkste.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="19.95" customHeight="1">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>Trend-agent</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>Conclusie</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
         <is>
           <t>Alle plekken zijn bezet, dus de bot koopt niets bij, hoe sterk een trend ook is.</t>
         </is>
@@ -1512,6 +1894,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1519,9 +1902,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1533,62 +1916,68 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="70" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>Bot</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>Instap</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="15" t="inlineStr">
         <is>
           <t>Koers nu</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="15" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="15" t="inlineStr">
         <is>
           <t>Resultaat €</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="15" t="inlineStr">
         <is>
           <t>Resultaat %</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="15" t="inlineStr">
         <is>
           <t>Afstand tot stop</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="15" t="inlineStr">
         <is>
           <t>Als de stop geraakt wordt €</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="J1" s="15" t="inlineStr">
+        <is>
+          <t>In gewone taal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="35.9" customHeight="1">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>SHELL.AS</t>
         </is>
@@ -1597,31 +1986,36 @@
         <v>45.0575</v>
       </c>
       <c r="D2" t="n">
-        <v>45.95</v>
+        <v>46.455</v>
       </c>
       <c r="E2" t="n">
-        <v>43.2368</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>0.0198</v>
-      </c>
-      <c r="H2" s="9" t="n">
-        <v>0.06279999999999999</v>
-      </c>
-      <c r="I2" s="4" t="n">
-        <v>-24.67</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+        <v>43.7325</v>
+      </c>
+      <c r="F2" s="17" t="n">
+        <v>18.17</v>
+      </c>
+      <c r="G2" s="18" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="H2" s="19" t="n">
+        <v>0.0623</v>
+      </c>
+      <c r="I2" s="17" t="n">
+        <v>-18.23</v>
+      </c>
+      <c r="J2" s="16" t="inlineStr">
+        <is>
+          <t>Staat €18,17 in de plus. Zakt de koers 6,2% naar 43,73, dan verkoopt de bot met ongeveer €18,23 verlies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="35.9" customHeight="1">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>SAP.DE</t>
         </is>
@@ -1630,31 +2024,36 @@
         <v>191.5557</v>
       </c>
       <c r="D3" t="n">
-        <v>197.28</v>
+        <v>198.06</v>
       </c>
       <c r="E3" t="n">
-        <v>181.0286</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>11.45</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>0.0299</v>
-      </c>
-      <c r="H3" s="9" t="n">
-        <v>0.0898</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>-22.05</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+        <v>181.9971</v>
+      </c>
+      <c r="F3" s="17" t="n">
+        <v>13.01</v>
+      </c>
+      <c r="G3" s="18" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="H3" s="19" t="n">
+        <v>0.0883</v>
+      </c>
+      <c r="I3" s="17" t="n">
+        <v>-20.12</v>
+      </c>
+      <c r="J3" s="16" t="inlineStr">
+        <is>
+          <t>Staat €13,01 in de plus. Zakt de koers 8,8% naar 182,00, dan verkoopt de bot met ongeveer €20,12 verlies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="35.9" customHeight="1">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>MSFT</t>
         </is>
@@ -1663,69 +2062,75 @@
         <v>535.3375</v>
       </c>
       <c r="D4" t="n">
-        <v>545</v>
+        <v>542.265</v>
       </c>
       <c r="E4" t="n">
         <v>509.899</v>
       </c>
-      <c r="F4" s="4" t="n">
-        <v>8.949999999999999</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="H4" s="9" t="n">
-        <v>0.0688</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>-23.4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="F4" s="17" t="n">
+        <v>9.869999999999999</v>
+      </c>
+      <c r="G4" s="18" t="n">
+        <v>0.0129</v>
+      </c>
+      <c r="H4" s="19" t="n">
+        <v>0.0635</v>
+      </c>
+      <c r="I4" s="17" t="n">
+        <v>-20.23</v>
+      </c>
+      <c r="J4" s="16" t="inlineStr">
+        <is>
+          <t>Staat €9,87 in de plus. Zakt de koers 6,3% naar 509,90, dan verkoopt de bot met ongeveer €20,23 verlies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1"/>
+    <row r="6" ht="35.9" customHeight="1">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>Trend-agent remmen</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>Nu</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>Grens</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="7" ht="35.9" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Daling vanaf top</t>
         </is>
       </c>
-      <c r="B7" s="9" t="n">
+      <c r="B7" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="19" t="n">
         <v>-0.05</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Vandaag</t>
         </is>
       </c>
-      <c r="B8" s="9" t="n">
-        <v>0.0026</v>
-      </c>
-      <c r="C8" s="9" t="n">
+      <c r="B8" s="19" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="C8" s="19" t="n">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="9" ht="35.9" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Verliestrades op rij</t>
         </is>
@@ -1737,192 +2142,202 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+    <row r="10" ht="18" customHeight="1"/>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>Instrument</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>Waarde</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>Ingelegd</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>Resultaat €</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>Resultaat %</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" t="inlineStr">
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="16" t="inlineStr"/>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>IFX.DE</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="n">
+        <v>569.71</v>
+      </c>
+      <c r="D12" s="21" t="n">
+        <v>600</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>-30.29</v>
+      </c>
+      <c r="F12" s="18" t="n">
+        <v>-0.0505</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="16" t="inlineStr"/>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="n">
+        <v>573.6799999999999</v>
+      </c>
+      <c r="D13" s="21" t="n">
+        <v>600</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>-26.32</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>-0.0439</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="16" t="inlineStr"/>
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>ASML.AS</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n">
-        <v>564.3099999999999</v>
-      </c>
-      <c r="D12" s="2" t="n">
+      <c r="C14" s="21" t="n">
+        <v>581.13</v>
+      </c>
+      <c r="D14" s="21" t="n">
         <v>600</v>
       </c>
-      <c r="E12" s="4" t="n">
-        <v>-35.69</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>-0.0595</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>MU</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>568.29</v>
-      </c>
-      <c r="D13" s="2" t="n">
+      <c r="E14" s="17" t="n">
+        <v>-18.87</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <v>-0.0314</v>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="16" t="inlineStr"/>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>SMH</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="n">
+        <v>586.51</v>
+      </c>
+      <c r="D15" s="21" t="n">
         <v>600</v>
       </c>
-      <c r="E13" s="4" t="n">
-        <v>-31.71</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>-0.0528</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>IFX.DE</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>569.61</v>
-      </c>
-      <c r="D14" s="2" t="n">
+      <c r="E15" s="17" t="n">
+        <v>-13.49</v>
+      </c>
+      <c r="F15" s="18" t="n">
+        <v>-0.0225</v>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="16" t="inlineStr"/>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="n">
+        <v>594</v>
+      </c>
+      <c r="D16" s="21" t="n">
         <v>600</v>
       </c>
-      <c r="E14" s="4" t="n">
-        <v>-30.39</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>-0.0507</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>SMH</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>589.05</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>600</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>-10.95</v>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>-0.0183</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>AMD</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>596</v>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>600</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>-4</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>-0.0067</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" t="inlineStr">
+      <c r="E16" s="17" t="n">
+        <v>-6</v>
+      </c>
+      <c r="F16" s="18" t="n">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="16" t="inlineStr"/>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="n">
+        <v>498.01</v>
+      </c>
+      <c r="D17" s="21" t="n">
+        <v>500</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>-1.99</v>
+      </c>
+      <c r="F17" s="18" t="n">
+        <v>-0.004</v>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="16" t="inlineStr"/>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="n">
+        <v>500.77</v>
+      </c>
+      <c r="D18" s="21" t="n">
+        <v>500</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F18" s="18" t="n">
+        <v>0.0015</v>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="16" t="inlineStr"/>
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>IWDA.AS</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n">
-        <v>5996.73</v>
-      </c>
-      <c r="D17" s="2" t="n">
+      <c r="C19" s="21" t="n">
+        <v>6022.23</v>
+      </c>
+      <c r="D19" s="21" t="n">
         <v>6000</v>
       </c>
-      <c r="E17" s="4" t="n">
-        <v>-3.27</v>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>-0.0005</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>BTC-USD</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>502.1</v>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>500</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="F18" s="5" t="n">
-        <v>0.0042</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>ETH-USD</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>505.29</v>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>500</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>0.0106</v>
+      <c r="E19" s="17" t="n">
+        <v>22.23</v>
+      </c>
+      <c r="F19" s="18" t="n">
+        <v>0.0037</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1930,420 +2345,308 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O8"/>
+  <dimension ref="B1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="95" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Naam</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="B1" s="22" t="inlineStr">
+        <is>
+          <t>Kansen: wat de trend-agent vandaag het sterkst vond</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Wat de oefenbot met nepgeld zou doen volgens zijn regels. Geen advies voor echt geld. Het instapmoment is een ongeteste vuistregel en wordt door de bot niet gebruikt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>1. Shell (SHELL.AS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="38.8" customHeight="1">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Instapmoment</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>Opgelopen: de koers staat +7,0% van het 20-daags gemiddelde (3,6x de normale dagbeweging) en RSI is 81; na zo'n sprint volgt vaak eerst een terugval</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="56.2" customHeight="1">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>Waarom sterk</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Uitleg instapmoment</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Valuta</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Instap</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Stop %</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Aantal</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Inzet €</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Max verlies €</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>2x risico (oriëntatie)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>SHELL.AS</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>Shell</t>
-        </is>
-      </c>
-      <c r="D2" s="8" t="inlineStr">
-        <is>
-          <t>opgelopen</t>
-        </is>
-      </c>
-      <c r="E2" s="8" t="inlineStr">
-        <is>
-          <t>Shell steeg +25,7% in 3 maanden en +11,0% in 1 maand; koers boven het 50-daags en dat boven het 200-daags gemiddelde; MACD positief (de stijging versnelt); handel 1,1x het normale volume; beweegt gemiddeld 2,0% per dag</t>
-        </is>
-      </c>
-      <c r="F2" s="8" t="inlineStr">
-        <is>
-          <t>de koers staat +7,3% van het 20-daags gemiddelde (3,7x de normale dagbeweging) en RSI is 79; na zo'n sprint volgt vaak eerst een terugval</t>
-        </is>
-      </c>
-      <c r="G2" s="8" t="inlineStr">
-        <is>
-          <t>al in bezit</t>
-        </is>
-      </c>
-      <c r="H2" s="8" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>45.973</v>
-      </c>
-      <c r="J2" t="n">
-        <v>44.1544</v>
-      </c>
-      <c r="K2" s="9" t="n">
-        <v>-0.0396</v>
-      </c>
-      <c r="L2" t="n">
-        <v>13</v>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>597.65</v>
-      </c>
-      <c r="N2" s="2" t="n">
-        <v>25.64</v>
-      </c>
-      <c r="O2" t="n">
-        <v>49.6101</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>SAP.DE</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>neutraal</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>SAP steeg +44,0% in 3 maanden en +11,3% in 1 maand; koers boven het 50-daags en dat boven het 200-daags gemiddelde; MACD positief (de stijging versnelt); handel 0,8x het normale volume; beweegt gemiddeld 2,8% per dag</t>
-        </is>
-      </c>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>de koers staat +5,7% van het 20-daags gemiddelde, RSI 66</t>
-        </is>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
-        <is>
-          <t>al in bezit</t>
-        </is>
-      </c>
-      <c r="H3" s="8" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>197.3786</v>
-      </c>
-      <c r="J3" t="n">
-        <v>186.5443</v>
-      </c>
-      <c r="K3" s="9" t="n">
-        <v>-0.0549</v>
-      </c>
-      <c r="L3" t="n">
-        <v>2</v>
-      </c>
-      <c r="M3" s="2" t="n">
-        <v>394.76</v>
-      </c>
-      <c r="N3" s="2" t="n">
-        <v>23.67</v>
-      </c>
-      <c r="O3" t="n">
-        <v>219.0472</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>XLE</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>Energie-ETF</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>neutraal</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>Energie-ETF steeg +19,0% in 3 maanden en +4,2% in 1 maand; koers boven het 50-daags en dat boven het 200-daags gemiddelde; MACD positief (de stijging versnelt); handel 1,1x het normale volume; beweegt gemiddeld 1,9% per dag</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>de koers staat +4,7% van het 20-daags gemiddelde, RSI 70</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>niet gekocht: alle 3 plekken zijn bezet</t>
-        </is>
-      </c>
-      <c r="H4" s="8" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>66.8884</v>
-      </c>
-      <c r="J4" t="n">
-        <v>64.4156</v>
-      </c>
-      <c r="K4" s="9" t="n">
-        <v>-0.037</v>
-      </c>
-      <c r="L4" t="n">
-        <v>11</v>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>657.05</v>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>26.29</v>
-      </c>
-      <c r="O4" t="n">
-        <v>71.83410000000001</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>WKL.AS</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>Wolters Kluwer</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>opgelopen</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>Wolters Kluwer steeg +26,6% in 3 maanden en +19,0% in 1 maand; koers boven het 50-daags en dat boven het 200-daags gemiddelde; MACD positief (de stijging versnelt); handel 1,2x het normale volume; beweegt gemiddeld 2,9% per dag</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>de koers staat +12,1% van het 20-daags gemiddelde (4,1x de normale dagbeweging) en RSI is 76; na zo'n sprint volgt vaak eerst een terugval</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>niet gekocht: alle 3 plekken zijn bezet</t>
-        </is>
-      </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>78.8794</v>
-      </c>
-      <c r="J5" t="n">
-        <v>74.2423</v>
-      </c>
-      <c r="K5" s="9" t="n">
-        <v>-0.0588</v>
-      </c>
-      <c r="L5" t="n">
-        <v>5</v>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>394.4</v>
-      </c>
-      <c r="N5" s="2" t="n">
-        <v>25.19</v>
-      </c>
-      <c r="O5" t="n">
-        <v>88.1537</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>MSFT</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>neutraal</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>Microsoft steeg +38,0% in 3 maanden en +7,8% in 1 maand; koers boven het 50-daags en dat boven het 200-daags gemiddelde; MACD positief (de stijging versnelt); handel 0,8x het normale volume; beweegt gemiddeld 2,2% per dag</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>de koers staat +5,1% van het 20-daags gemiddelde, RSI 71</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>al in bezit</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>545.2725</v>
-      </c>
-      <c r="J6" t="n">
-        <v>521.3682</v>
-      </c>
-      <c r="K6" s="9" t="n">
-        <v>-0.0438</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>486.93</v>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>23.35</v>
-      </c>
-      <c r="O6" t="n">
-        <v>593.0811</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr"/>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Wat de oefenbot met nepgeld zou doen volgens zijn regels. Geen advies voor echt geld. Het instapmoment is een ongeteste vuistregel en wordt door de bot niet gebruikt.</t>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>Shell steeg +23,4% in 3 maanden en +8,8% in 1 maand; koers boven het 50-daags en dat boven het 200-daags gemiddelde; MACD positief (de stijging versnelt); handel 1,0x het normale volume; beweegt gemiddeld 1,9% per dag</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="38.8" customHeight="1">
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>Plan van de bot</t>
+        </is>
+      </c>
+      <c r="C7" s="25" t="inlineStr">
+        <is>
+          <t>Koop 13 stuks rond 46,48 EUR (inzet €604,22). Stop-loss op 44,66 EUR (-3,9%). Gaat het mis, dan is het verlies ongeveer €25,59.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="21.4" customHeight="1">
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>Wat deed de bot?</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>Al in bezit</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>2. SAP (SAP.DE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="21.4" customHeight="1">
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>Instapmoment</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>Neutraal: de koers staat +5,1% van het 20-daags gemiddelde, RSI 67</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="56.2" customHeight="1">
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>Waarom sterk</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>SAP steeg +43,6% in 3 maanden en +5,9% in 1 maand; koers boven het 50-daags en dat boven het 200-daags gemiddelde; MACD positief (de stijging versnelt); handel 0,8x het normale volume; beweegt gemiddeld 2,7% per dag</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="38.8" customHeight="1">
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>Plan van de bot</t>
+        </is>
+      </c>
+      <c r="C13" s="25" t="inlineStr">
+        <is>
+          <t>Koop 2 stuks rond 198,16 EUR (inzet €396,32). Stop-loss op 187,45 EUR (-5,4%). Gaat het mis, dan is het verlies ongeveer €23,42.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="21.4" customHeight="1">
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>Wat deed de bot?</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>Al in bezit</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>3. Wolters Kluwer (WKL.AS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="38.8" customHeight="1">
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>Instapmoment</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>Opgelopen: de koers staat +9,2% van het 20-daags gemiddelde (3,2x de normale dagbeweging) en RSI is 74; na zo'n sprint volgt vaak eerst een terugval</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="56.2" customHeight="1">
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>Waarom sterk</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>Wolters Kluwer steeg +28,5% in 3 maanden en +13,9% in 1 maand; koers boven het 50-daags en dat boven het 200-daags gemiddelde; MACD positief (de stijging versnelt); handel 1,2x het normale volume; beweegt gemiddeld 2,8% per dag</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="38.8" customHeight="1">
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>Plan van de bot</t>
+        </is>
+      </c>
+      <c r="C19" s="25" t="inlineStr">
+        <is>
+          <t>Koop 5 stuks rond 78,28 EUR (inzet €391,40). Stop-loss op 73,86 EUR (-5,7%). Gaat het mis, dan is het verlies ongeveer €24,10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="21.4" customHeight="1">
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>Wat deed de bot?</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>Niet gekocht: alle 3 plekken zijn bezet</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>4. Microsoft (MSFT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="21.4" customHeight="1">
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>Instapmoment</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>Neutraal: de koers staat +4,1% van het 20-daags gemiddelde, RSI 70</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="56.2" customHeight="1">
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>Waarom sterk</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="inlineStr">
+        <is>
+          <t>Microsoft steeg +35,4% in 3 maanden en +9,1% in 1 maand; koers boven het 50-daags en dat boven het 200-daags gemiddelde; MACD positief (de stijging versnelt); handel 0,8x het normale volume; beweegt gemiddeld 2,1% per dag</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="38.8" customHeight="1">
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>Plan van de bot</t>
+        </is>
+      </c>
+      <c r="C25" s="25" t="inlineStr">
+        <is>
+          <t>Koop 1 stuk rond 542,54 USD (inzet €487,85). Stop-loss op 519,40 USD (-4,3%). Gaat het mis, dan is het verlies ongeveer €22,81.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="21.4" customHeight="1">
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>Wat deed de bot?</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>Al in bezit</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>5. Energie-ETF (XLE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="21.4" customHeight="1">
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>Instapmoment</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>Neutraal: de koers staat +4,8% van het 20-daags gemiddelde, RSI 71</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="56.2" customHeight="1">
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>Waarom sterk</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>Energie-ETF steeg +18,7% in 3 maanden en +2,7% in 1 maand; koers boven het 50-daags en dat boven het 200-daags gemiddelde; MACD positief (de stijging versnelt); handel 1,1x het normale volume; beweegt gemiddeld 1,8% per dag</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="38.8" customHeight="1">
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>Plan van de bot</t>
+        </is>
+      </c>
+      <c r="C31" s="25" t="inlineStr">
+        <is>
+          <t>Koop 11 stuks rond 67,34 USD (inzet €666,11). Stop-loss op 64,91 USD (-3,6%). Gaat het mis, dan is het verlies ongeveer €26,10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="21.4" customHeight="1">
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>Wat deed de bot?</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="inlineStr">
+        <is>
+          <t>Niet gekocht: alle 3 plekken zijn bezet</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2351,7 +2654,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2363,220 +2666,222 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>Bot</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Eis</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>Stand</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="15" t="inlineStr">
         <is>
           <t>Nu</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+    <row r="2" ht="19.95" customHeight="1">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>Oefentijd</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="16" t="inlineStr">
         <is>
           <t>⏳ nog bezig</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" s="16" t="inlineStr">
+        <is>
+          <t>1 van 63 handelsdagen (ongeveer 3 maanden)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="19.95" customHeight="1">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Investeerder</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>Minstens zo goed als de wereld-ETF</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
+        <is>
+          <t>⏳ nog bezig</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>nog te weinig dagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="19.95" customHeight="1">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Investeerder</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>Daling niet veel dieper dan de ETF</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>✅ gehaald</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>bot -0,74%, ETF +0,00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="35.9" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Investeerder</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>Oordeel</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>Nog niet klaar: de bot is nog bezig met bewijzen. Blijven oefenen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1"/>
+    <row r="7" ht="19.95" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>Trend-agent</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>Oefentijd</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>⏳ nog bezig</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>2 van 63 handelsdagen (ongeveer 3 maanden)</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>Investeerder</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
+    <row r="8" ht="19.95" customHeight="1">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>Trend-agent</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>Minstens zo goed als de wereld-ETF</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>⏳ nog bezig</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>verschil tot nu toe -0,98%</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>Investeerder</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>Daling niet veel dieper dan de ETF</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>nog te weinig dagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="19.95" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>Trend-agent</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>Grootste daling onder 5%</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>✅ gehaald</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>bot -1,09%, ETF +0,00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>Investeerder</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>grootste daling tot nu toe -0,04%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="19.95" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>Trend-agent</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>Genoeg afgesloten trades</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>⏳ nog bezig</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>0 van 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="35.9" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>Trend-agent</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>Oordeel</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr"/>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr"/>
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>Nog niet klaar: de bot is nog bezig met bewijzen. Blijven oefenen.</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Trend-agent</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Oefentijd</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>⏳ nog bezig</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>3 van 63 handelsdagen (ongeveer 3 maanden)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>Trend-agent</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Minstens zo goed als de wereld-ETF</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>⏳ nog bezig</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>verschil tot nu toe +0,22%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>Trend-agent</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Grootste daling onder 5%</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>✅ gehaald</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>grootste daling tot nu toe -0,04%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Trend-agent</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Genoeg afgesloten trades</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>⏳ nog bezig</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>0 van 20</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>Trend-agent</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Oordeel</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr"/>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>Nog niet klaar: de bot is nog bezig met bewijzen. Blijven oefenen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr"/>
-      <c r="B13" s="8" t="inlineStr">
+    <row r="12" ht="18" customHeight="1"/>
+    <row r="13" ht="67.8" customHeight="1">
+      <c r="A13" s="16" t="inlineStr"/>
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>Eerst bewijzen, dan een oefenaccount bij een echte broker, dan een klein bedrag met jouw goedkeuring per order. Die beslissing neem jij, niet de bot.</t>
         </is>
@@ -2584,6 +2889,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2591,9 +2897,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2605,32 +2911,32 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>Investeerder t.o.v. start</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="15" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="15" t="inlineStr">
         <is>
           <t>Trend-agent t.o.v. start</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="15" t="inlineStr">
         <is>
           <t>Wereld-ETF (koers in €)</t>
         </is>
@@ -2642,16 +2948,16 @@
           <t>start</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="21" t="n">
         <v>10000</v>
       </c>
-      <c r="C2" s="4" t="n">
+      <c r="C2" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="21" t="n">
         <v>10000</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2661,61 +2967,40 @@
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="2" t="n">
+      <c r="B3" s="21" t="n"/>
+      <c r="C3" s="17" t="n"/>
+      <c r="D3" s="21" t="n">
         <v>9996.280000000001</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="17" t="n">
         <v>-3.72</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>9891.379999999999</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>-108.62</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>10029.01</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>29.01</v>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B4" s="21" t="n">
+        <v>9926.040000000001</v>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>-73.95999999999999</v>
+      </c>
+      <c r="D4" s="21" t="n">
+        <v>10038.05</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>38.05</v>
       </c>
       <c r="F4" t="n">
-        <v>131.73</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>9985.01</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>-14.99</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>10002.9</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="F5" t="n">
-        <v>131.67</v>
+        <v>132.29</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2723,7 +3008,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2741,74 +3026,74 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Bot</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="15" t="inlineStr">
         <is>
           <t>Koop/verkoop</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="15" t="inlineStr">
         <is>
           <t>Aantal</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="15" t="inlineStr">
         <is>
           <t>Prijs</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="15" t="inlineStr">
         <is>
           <t>Waarde €</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="15" t="inlineStr">
         <is>
           <t>Kosten €</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="15" t="inlineStr">
         <is>
           <t>Resultaat €</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="15" t="inlineStr">
         <is>
           <t>Reden</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="19.95" customHeight="1">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="16" t="inlineStr">
         <is>
           <t>SHELL.AS</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="16" t="inlineStr">
         <is>
           <t>koop</t>
         </is>
@@ -2819,36 +3104,36 @@
       <c r="F2" t="n">
         <v>45.0575</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="21" t="n">
         <v>585.75</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="4" t="n"/>
-      <c r="J2" t="inlineStr">
+      <c r="I2" s="17" t="n"/>
+      <c r="J2" s="16" t="inlineStr">
         <is>
           <t>trend OK: 3m +23.4%, 1m +9.2%, volume x1.07</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="19.95" customHeight="1">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>SAP.DE</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>koop</t>
         </is>
@@ -2859,36 +3144,36 @@
       <c r="F3" t="n">
         <v>191.5557</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="21" t="n">
         <v>383.11</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="H3" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="I3" s="4" t="n"/>
-      <c r="J3" t="inlineStr">
+      <c r="I3" s="17" t="n"/>
+      <c r="J3" s="16" t="inlineStr">
         <is>
           <t>trend OK: 3m +40.0%, 1m +7.7%, volume x0.83</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="19.95" customHeight="1">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>MSFT</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>koop</t>
         </is>
@@ -2899,36 +3184,36 @@
       <c r="F4" t="n">
         <v>535.3375</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="21" t="n">
         <v>477.74</v>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H4" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="I4" s="4" t="n"/>
-      <c r="J4" t="inlineStr">
+      <c r="I4" s="17" t="n"/>
+      <c r="J4" s="16" t="inlineStr">
         <is>
           <t>trend OK: 3m +37.1%, 1m +8.7%, volume x0.82</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="5" ht="19.95" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>IWDA.AS</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>koop</t>
         </is>
@@ -2939,36 +3224,36 @@
       <c r="F5" t="n">
         <v>131.7358</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="21" t="n">
         <v>5997</v>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="H5" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="I5" s="4" t="n"/>
-      <c r="J5" t="inlineStr">
+      <c r="I5" s="17" t="n"/>
+      <c r="J5" s="16" t="inlineStr">
         <is>
           <t>doelgewicht 60%</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="6" ht="19.95" customHeight="1">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>MU</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>koop</t>
         </is>
@@ -2979,36 +3264,36 @@
       <c r="F6" t="n">
         <v>885.2376</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="21" t="n">
         <v>599</v>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="H6" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="I6" s="4" t="n"/>
-      <c r="J6" t="inlineStr">
+      <c r="I6" s="17" t="n"/>
+      <c r="J6" s="16" t="inlineStr">
         <is>
           <t>doelgewicht 6%</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="7" ht="19.95" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>SMH</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>koop</t>
         </is>
@@ -3019,36 +3304,36 @@
       <c r="F7" t="n">
         <v>528.9640000000001</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="21" t="n">
         <v>599</v>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="H7" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="I7" s="4" t="n"/>
-      <c r="J7" t="inlineStr">
+      <c r="I7" s="17" t="n"/>
+      <c r="J7" s="16" t="inlineStr">
         <is>
           <t>doelgewicht 6%</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="8" ht="19.95" customHeight="1">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>ASML.AS</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>koop</t>
         </is>
@@ -3059,36 +3344,36 @@
       <c r="F8" t="n">
         <v>1602.4008</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G8" s="21" t="n">
         <v>599</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H8" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="I8" s="4" t="n"/>
-      <c r="J8" t="inlineStr">
+      <c r="I8" s="17" t="n"/>
+      <c r="J8" s="16" t="inlineStr">
         <is>
           <t>doelgewicht 6%</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="9" ht="19.95" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>IFX.DE</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>koop</t>
         </is>
@@ -3099,36 +3384,36 @@
       <c r="F9" t="n">
         <v>58.8894</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="G9" s="21" t="n">
         <v>599</v>
       </c>
-      <c r="H9" s="2" t="n">
+      <c r="H9" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="4" t="n"/>
-      <c r="J9" t="inlineStr">
+      <c r="I9" s="17" t="n"/>
+      <c r="J9" s="16" t="inlineStr">
         <is>
           <t>doelgewicht 6%</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="10" ht="19.95" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>AMD</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>koop</t>
         </is>
@@ -3139,36 +3424,36 @@
       <c r="F10" t="n">
         <v>531.8729</v>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="G10" s="21" t="n">
         <v>599</v>
       </c>
-      <c r="H10" s="2" t="n">
+      <c r="H10" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="4" t="n"/>
-      <c r="J10" t="inlineStr">
+      <c r="I10" s="17" t="n"/>
+      <c r="J10" s="16" t="inlineStr">
         <is>
           <t>doelgewicht 6%</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="11" ht="19.95" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>ETH-USD</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>koop</t>
         </is>
@@ -3179,36 +3464,36 @@
       <c r="F11" t="n">
         <v>2220.7914</v>
       </c>
-      <c r="G11" s="2" t="n">
+      <c r="G11" s="21" t="n">
         <v>499</v>
       </c>
-      <c r="H11" s="2" t="n">
+      <c r="H11" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="4" t="n"/>
-      <c r="J11" t="inlineStr">
+      <c r="I11" s="17" t="n"/>
+      <c r="J11" s="16" t="inlineStr">
         <is>
           <t>doelgewicht 5%</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="12" ht="19.95" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>BTC-USD</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>koop</t>
         </is>
@@ -3219,14 +3504,14 @@
       <c r="F12" t="n">
         <v>74036.6848</v>
       </c>
-      <c r="G12" s="2" t="n">
+      <c r="G12" s="21" t="n">
         <v>499</v>
       </c>
-      <c r="H12" s="2" t="n">
+      <c r="H12" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="4" t="n"/>
-      <c r="J12" t="inlineStr">
+      <c r="I12" s="17" t="n"/>
+      <c r="J12" s="16" t="inlineStr">
         <is>
           <t>doelgewicht 5%</t>
         </is>
@@ -3234,6 +3519,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -3241,7 +3527,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -3251,60 +3537,60 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>Bot</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Controle</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+    <row r="2" ht="19.95" customHeight="1">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>Investeerder: status OK, 52 van 52 koersen opgehaald, marktregime stijgend-laag.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+    <row r="3" ht="35.9" customHeight="1">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Koersbronnen: 0 bevestigd door twee bronnen, 52 uit één bron, 0 afwijkend. Wisselkoers: bevestigd. Tweede bron overgeslagen na herhaalde fouten (GOOGL: Stooq gaf geen koersen ('&lt;!DOCTYPE html&gt;&lt;html&gt;&lt;head&gt;&lt;meta charset')).</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+    <row r="4" ht="19.95" customHeight="1">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>Trend-agent: status OK, 50 van 50 koersen opgehaald, marktregime stijgend-laag.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+    <row r="5" ht="35.9" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>Koersbronnen: 0 bevestigd door twee bronnen, 50 uit één bron, 0 afwijkend. Wisselkoers: bevestigd. Tweede bron overgeslagen na herhaalde fouten (GOOGL: Stooq gaf geen koersen ('&lt;!DOCTYPE html&gt;&lt;html&gt;&lt;head&gt;&lt;meta charset')).</t>
         </is>
@@ -3312,5 +3598,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/rapporten/voorbeeld/dagrapport.xlsx
+++ b/rapporten/voorbeeld/dagrapport.xlsx
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>9926.040000000001</v>
+        <v>9918.809999999999</v>
       </c>
     </row>
     <row r="6">
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>-73.95999999999999</v>
+        <v>-81.19</v>
       </c>
     </row>
     <row r="7">
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>-0.007395999999999958</v>
+        <v>-0.008119000000000098</v>
       </c>
     </row>
     <row r="8">
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>10038.05</v>
+        <v>10038.91</v>
       </c>
     </row>
     <row r="13">
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>38.05</v>
+        <v>38.91</v>
       </c>
     </row>
     <row r="14">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>0.003804999999999836</v>
+        <v>0.003891000000000089</v>
       </c>
     </row>
     <row r="15">
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="C15" s="9" t="n">
-        <v>41.76999999999862</v>
+        <v>42.6299999999992</v>
       </c>
     </row>
     <row r="16">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>24 van de 50 instrumenten zijn een koopbare trend: veel keus, de bot neemt alleen de rustigste, sterkste.</t>
+          <t>23 van de 50 instrumenten zijn een koopbare trend: veel keus, de bot neemt alleen de rustigste, sterkste.</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="C2" s="16" t="inlineStr">
         <is>
-          <t>koers 132,29, 10,0% boven het 200-daags gemiddelde (120,29); de afgelopen maand +4,6%. Trend: stijgend.</t>
+          <t>koers 132,30, 10,0% boven het 200-daags gemiddelde (120,29); de afgelopen maand +4,6%. Trend: stijgend.</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="C6" s="16" t="inlineStr">
         <is>
-          <t>14,4% boven het 200-daags gemiddelde (mag in de mix).</t>
+          <t>14,2% boven het 200-daags gemiddelde (mag in de mix).</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>15,1% boven het 200-daags gemiddelde (mag in de mix).</t>
+          <t>14,9% boven het 200-daags gemiddelde (mag in de mix).</t>
         </is>
       </c>
     </row>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="C10" s="16" t="inlineStr">
         <is>
-          <t>koers 132,29, 10,0% boven het 200-daags gemiddelde (120,29); de afgelopen maand +4,6%. Trend: stijgend.</t>
+          <t>koers 132,30, 10,0% boven het 200-daags gemiddelde (120,29); de afgelopen maand +4,6%. Trend: stijgend.</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>geen stijgende trend (koers niet boven 50- en 200-daags gemiddelde): 23; niet gestegen over 1 of 3 maanden: 21; te weinig handel: 1.</t>
+          <t>geen stijgende trend (koers niet boven 50- en 200-daags gemiddelde): 24; niet gestegen over 1 of 3 maanden: 21; te weinig handel: 1.</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>24. Koopbare trends: 24.</t>
+          <t>23. Koopbare trends: 23.</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>24 van de 50 instrumenten zijn een koopbare trend: veel keus, de bot neemt alleen de rustigste, sterkste.</t>
+          <t>23 van de 50 instrumenten zijn een koopbare trend: veel keus, de bot neemt alleen de rustigste, sterkste.</t>
         </is>
       </c>
     </row>
@@ -1986,26 +1986,26 @@
         <v>45.0575</v>
       </c>
       <c r="D2" t="n">
-        <v>46.455</v>
+        <v>46.51</v>
       </c>
       <c r="E2" t="n">
-        <v>43.7325</v>
+        <v>43.7875</v>
       </c>
       <c r="F2" s="17" t="n">
-        <v>18.17</v>
+        <v>18.88</v>
       </c>
       <c r="G2" s="18" t="n">
-        <v>0.031</v>
+        <v>0.0322</v>
       </c>
       <c r="H2" s="19" t="n">
-        <v>0.0623</v>
+        <v>0.0622</v>
       </c>
       <c r="I2" s="17" t="n">
-        <v>-18.23</v>
+        <v>-17.51</v>
       </c>
       <c r="J2" s="16" t="inlineStr">
         <is>
-          <t>Staat €18,17 in de plus. Zakt de koers 6,2% naar 43,73, dan verkoopt de bot met ongeveer €18,23 verlies.</t>
+          <t>Staat €18,88 in de plus. Zakt de koers 6,2% naar 43,79, dan verkoopt de bot met ongeveer €17,51 verlies.</t>
         </is>
       </c>
     </row>
@@ -2024,26 +2024,26 @@
         <v>191.5557</v>
       </c>
       <c r="D3" t="n">
-        <v>198.06</v>
+        <v>198.26</v>
       </c>
       <c r="E3" t="n">
-        <v>181.9971</v>
+        <v>182.1971</v>
       </c>
       <c r="F3" s="17" t="n">
-        <v>13.01</v>
+        <v>13.41</v>
       </c>
       <c r="G3" s="18" t="n">
-        <v>0.034</v>
+        <v>0.035</v>
       </c>
       <c r="H3" s="19" t="n">
-        <v>0.0883</v>
+        <v>0.0882</v>
       </c>
       <c r="I3" s="17" t="n">
-        <v>-20.12</v>
+        <v>-19.72</v>
       </c>
       <c r="J3" s="16" t="inlineStr">
         <is>
-          <t>Staat €13,01 in de plus. Zakt de koers 8,8% naar 182,00, dan verkoopt de bot met ongeveer €20,12 verlies.</t>
+          <t>Staat €13,41 in de plus. Zakt de koers 8,8% naar 182,20, dan verkoopt de bot met ongeveer €19,72 verlies.</t>
         </is>
       </c>
     </row>
@@ -2062,26 +2062,26 @@
         <v>535.3375</v>
       </c>
       <c r="D4" t="n">
-        <v>542.265</v>
+        <v>542.04</v>
       </c>
       <c r="E4" t="n">
         <v>509.899</v>
       </c>
       <c r="F4" s="17" t="n">
-        <v>9.869999999999999</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="G4" s="18" t="n">
-        <v>0.0129</v>
+        <v>0.0125</v>
       </c>
       <c r="H4" s="19" t="n">
-        <v>0.0635</v>
+        <v>0.063</v>
       </c>
       <c r="I4" s="17" t="n">
-        <v>-20.23</v>
+        <v>-20.29</v>
       </c>
       <c r="J4" s="16" t="inlineStr">
         <is>
-          <t>Staat €9,87 in de plus. Zakt de koers 6,3% naar 509,90, dan verkoopt de bot met ongeveer €20,23 verlies.</t>
+          <t>Staat €9,61 in de plus. Zakt de koers 6,3% naar 509,90, dan verkoopt de bot met ongeveer €20,29 verlies.</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
         </is>
       </c>
       <c r="B8" s="19" t="n">
-        <v>0.0042</v>
+        <v>0.0043</v>
       </c>
       <c r="C8" s="19" t="n">
         <v>-0.01</v>
@@ -2183,16 +2183,16 @@
         </is>
       </c>
       <c r="C12" s="21" t="n">
-        <v>569.71</v>
+        <v>569.8099999999999</v>
       </c>
       <c r="D12" s="21" t="n">
         <v>600</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>-30.29</v>
+        <v>-30.19</v>
       </c>
       <c r="F12" s="18" t="n">
-        <v>-0.0505</v>
+        <v>-0.0503</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2203,16 +2203,16 @@
         </is>
       </c>
       <c r="C13" s="21" t="n">
-        <v>573.6799999999999</v>
+        <v>572.28</v>
       </c>
       <c r="D13" s="21" t="n">
         <v>600</v>
       </c>
       <c r="E13" s="17" t="n">
-        <v>-26.32</v>
+        <v>-27.72</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>-0.0439</v>
+        <v>-0.0462</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2223,16 +2223,16 @@
         </is>
       </c>
       <c r="C14" s="21" t="n">
-        <v>581.13</v>
+        <v>579.26</v>
       </c>
       <c r="D14" s="21" t="n">
         <v>600</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>-18.87</v>
+        <v>-20.74</v>
       </c>
       <c r="F14" s="18" t="n">
-        <v>-0.0314</v>
+        <v>-0.0346</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2243,16 +2243,16 @@
         </is>
       </c>
       <c r="C15" s="21" t="n">
-        <v>586.51</v>
+        <v>585.09</v>
       </c>
       <c r="D15" s="21" t="n">
         <v>600</v>
       </c>
       <c r="E15" s="17" t="n">
-        <v>-13.49</v>
+        <v>-14.91</v>
       </c>
       <c r="F15" s="18" t="n">
-        <v>-0.0225</v>
+        <v>-0.0249</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2263,16 +2263,16 @@
         </is>
       </c>
       <c r="C16" s="21" t="n">
-        <v>594</v>
+        <v>592.76</v>
       </c>
       <c r="D16" s="21" t="n">
         <v>600</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>-6</v>
+        <v>-7.24</v>
       </c>
       <c r="F16" s="18" t="n">
-        <v>-0.01</v>
+        <v>-0.0121</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2283,16 +2283,16 @@
         </is>
       </c>
       <c r="C17" s="21" t="n">
-        <v>498.01</v>
+        <v>497.02</v>
       </c>
       <c r="D17" s="21" t="n">
         <v>500</v>
       </c>
       <c r="E17" s="17" t="n">
-        <v>-1.99</v>
+        <v>-2.98</v>
       </c>
       <c r="F17" s="18" t="n">
-        <v>-0.004</v>
+        <v>-0.006</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2303,16 +2303,16 @@
         </is>
       </c>
       <c r="C18" s="21" t="n">
-        <v>500.77</v>
+        <v>499.91</v>
       </c>
       <c r="D18" s="21" t="n">
         <v>500</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>0.77</v>
+        <v>-0.09</v>
       </c>
       <c r="F18" s="18" t="n">
-        <v>0.0015</v>
+        <v>-0.0002</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2323,16 +2323,16 @@
         </is>
       </c>
       <c r="C19" s="21" t="n">
-        <v>6022.23</v>
+        <v>6022.68</v>
       </c>
       <c r="D19" s="21" t="n">
         <v>6000</v>
       </c>
       <c r="E19" s="17" t="n">
-        <v>22.23</v>
+        <v>22.68</v>
       </c>
       <c r="F19" s="18" t="n">
-        <v>0.0037</v>
+        <v>0.0038</v>
       </c>
     </row>
   </sheetData>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>Opgelopen: de koers staat +7,0% van het 20-daags gemiddelde (3,6x de normale dagbeweging) en RSI is 81; na zo'n sprint volgt vaak eerst een terugval</t>
+          <t>Opgelopen: de koers staat +7,1% van het 20-daags gemiddelde (3,7x de normale dagbeweging) en RSI is 81; na zo'n sprint volgt vaak eerst een terugval</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>Shell steeg +23,4% in 3 maanden en +8,8% in 1 maand; koers boven het 50-daags en dat boven het 200-daags gemiddelde; MACD positief (de stijging versnelt); handel 1,0x het normale volume; beweegt gemiddeld 1,9% per dag</t>
+          <t>Shell steeg +23,5% in 3 maanden en +8,9% in 1 maand; koers boven het 50-daags en dat boven het 200-daags gemiddelde; MACD positief (de stijging versnelt); handel 1,0x het normale volume; beweegt gemiddeld 1,9% per dag</t>
         </is>
       </c>
     </row>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C7" s="25" t="inlineStr">
         <is>
-          <t>Koop 13 stuks rond 46,48 EUR (inzet €604,22). Stop-loss op 44,66 EUR (-3,9%). Gaat het mis, dan is het verlies ongeveer €25,59.</t>
+          <t>Koop 13 stuks rond 46,53 EUR (inzet €604,93). Stop-loss op 44,72 EUR (-3,9%). Gaat het mis, dan is het verlies ongeveer €25,59.</t>
         </is>
       </c>
     </row>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>Neutraal: de koers staat +5,1% van het 20-daags gemiddelde, RSI 67</t>
+          <t>Neutraal: de koers staat +5,2% van het 20-daags gemiddelde, RSI 68</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>SAP steeg +43,6% in 3 maanden en +5,9% in 1 maand; koers boven het 50-daags en dat boven het 200-daags gemiddelde; MACD positief (de stijging versnelt); handel 0,8x het normale volume; beweegt gemiddeld 2,7% per dag</t>
+          <t>SAP steeg +43,7% in 3 maanden en +6,0% in 1 maand; koers boven het 50-daags en dat boven het 200-daags gemiddelde; MACD positief (de stijging versnelt); handel 0,8x het normale volume; beweegt gemiddeld 2,7% per dag</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="C13" s="25" t="inlineStr">
         <is>
-          <t>Koop 2 stuks rond 198,16 EUR (inzet €396,32). Stop-loss op 187,45 EUR (-5,4%). Gaat het mis, dan is het verlies ongeveer €23,42.</t>
+          <t>Koop 2 stuks rond 198,36 EUR (inzet €396,72). Stop-loss op 187,65 EUR (-5,4%). Gaat het mis, dan is het verlies ongeveer €23,42.</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>Opgelopen: de koers staat +9,2% van het 20-daags gemiddelde (3,2x de normale dagbeweging) en RSI is 74; na zo'n sprint volgt vaak eerst een terugval</t>
+          <t>Opgelopen: de koers staat +9,4% van het 20-daags gemiddelde (3,3x de normale dagbeweging) en RSI is 74; na zo'n sprint volgt vaak eerst een terugval</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>Wolters Kluwer steeg +28,5% in 3 maanden en +13,9% in 1 maand; koers boven het 50-daags en dat boven het 200-daags gemiddelde; MACD positief (de stijging versnelt); handel 1,2x het normale volume; beweegt gemiddeld 2,8% per dag</t>
+          <t>Wolters Kluwer steeg +28,7% in 3 maanden en +14,2% in 1 maand; koers boven het 50-daags en dat boven het 200-daags gemiddelde; MACD positief (de stijging versnelt); handel 1,2x het normale volume; beweegt gemiddeld 2,8% per dag</t>
         </is>
       </c>
     </row>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="C19" s="25" t="inlineStr">
         <is>
-          <t>Koop 5 stuks rond 78,28 EUR (inzet €391,40). Stop-loss op 73,86 EUR (-5,7%). Gaat het mis, dan is het verlies ongeveer €24,10.</t>
+          <t>Koop 5 stuks rond 78,44 EUR (inzet €392,20). Stop-loss op 74,02 EUR (-5,6%). Gaat het mis, dan is het verlies ongeveer €24,10.</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>Microsoft steeg +35,4% in 3 maanden en +9,1% in 1 maand; koers boven het 50-daags en dat boven het 200-daags gemiddelde; MACD positief (de stijging versnelt); handel 0,8x het normale volume; beweegt gemiddeld 2,1% per dag</t>
+          <t>Microsoft steeg +35,4% in 3 maanden en +9,0% in 1 maand; koers boven het 50-daags en dat boven het 200-daags gemiddelde; MACD positief (de stijging versnelt); handel 0,8x het normale volume; beweegt gemiddeld 2,1% per dag</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="C25" s="25" t="inlineStr">
         <is>
-          <t>Koop 1 stuk rond 542,54 USD (inzet €487,85). Stop-loss op 519,40 USD (-4,3%). Gaat het mis, dan is het verlies ongeveer €22,81.</t>
+          <t>Koop 1 stuk rond 542,31 USD (inzet €487,59). Stop-loss op 519,16 USD (-4,3%). Gaat het mis, dan is het verlies ongeveer €22,81.</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>Neutraal: de koers staat +4,8% van het 20-daags gemiddelde, RSI 71</t>
+          <t>Neutraal: de koers staat +4,9% van het 20-daags gemiddelde, RSI 71</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>Energie-ETF steeg +18,7% in 3 maanden en +2,7% in 1 maand; koers boven het 50-daags en dat boven het 200-daags gemiddelde; MACD positief (de stijging versnelt); handel 1,1x het normale volume; beweegt gemiddeld 1,8% per dag</t>
+          <t>Energie-ETF steeg +18,9% in 3 maanden en +2,8% in 1 maand; koers boven het 50-daags en dat boven het 200-daags gemiddelde; MACD positief (de stijging versnelt); handel 1,1x het normale volume; beweegt gemiddeld 1,8% per dag</t>
         </is>
       </c>
     </row>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="C31" s="25" t="inlineStr">
         <is>
-          <t>Koop 11 stuks rond 67,34 USD (inzet €666,11). Stop-loss op 64,91 USD (-3,6%). Gaat het mis, dan is het verlies ongeveer €26,10.</t>
+          <t>Koop 11 stuks rond 67,40 USD (inzet €666,63). Stop-loss op 64,97 USD (-3,6%). Gaat het mis, dan is het verlies ongeveer €26,09.</t>
         </is>
       </c>
     </row>
@@ -2749,7 +2749,7 @@
       </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
-          <t>bot -0,74%, ETF +0,00%</t>
+          <t>bot -0,81%, ETF +0,00%</t>
         </is>
       </c>
     </row>
@@ -2983,19 +2983,19 @@
         </is>
       </c>
       <c r="B4" s="21" t="n">
-        <v>9926.040000000001</v>
+        <v>9918.809999999999</v>
       </c>
       <c r="C4" s="17" t="n">
-        <v>-73.95999999999999</v>
+        <v>-81.19</v>
       </c>
       <c r="D4" s="21" t="n">
-        <v>10038.05</v>
+        <v>10038.91</v>
       </c>
       <c r="E4" s="17" t="n">
-        <v>38.05</v>
+        <v>38.91</v>
       </c>
       <c r="F4" t="n">
-        <v>132.29</v>
+        <v>132.3</v>
       </c>
     </row>
   </sheetData>

--- a/rapporten/voorbeeld/dagrapport.xlsx
+++ b/rapporten/voorbeeld/dagrapport.xlsx
@@ -31,7 +31,7 @@
     <numFmt numFmtId="166" formatCode="[Color10]+0.00%;[Red]-0.00%;0.00%"/>
     <numFmt numFmtId="167" formatCode="0.00%;[Red]-0.00%"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -78,14 +78,6 @@
       <b val="1"/>
       <sz val="18"/>
     </font>
-    <font>
-      <b val="1"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="13"/>
-    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -122,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -175,8 +167,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -259,7 +249,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>41</row>
+      <row>38</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7810500" cy="3905250"/>
@@ -295,7 +285,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572499" cy="4286249"/>
+    <ext cx="8382000" cy="4191000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -317,10 +307,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>30</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572499" cy="5143500"/>
+    <ext cx="8382000" cy="5029200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -342,10 +332,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>61</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572499" cy="5143500"/>
+    <ext cx="8382000" cy="5029200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -367,10 +357,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>92</row>
+      <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572499" cy="5143500"/>
+    <ext cx="8382000" cy="5029200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -392,10 +382,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>123</row>
+      <row>16</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572499" cy="5143500"/>
+    <ext cx="8382000" cy="5029200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -417,10 +407,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>154</row>
+      <row>19</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572499" cy="5143500"/>
+    <ext cx="8382000" cy="5029200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -442,10 +432,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>185</row>
+      <row>22</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572499" cy="5143500"/>
+    <ext cx="8382000" cy="5029200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -467,10 +457,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>216</row>
+      <row>25</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572499" cy="5143500"/>
+    <ext cx="8382000" cy="5029200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -492,10 +482,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>247</row>
+      <row>28</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572499" cy="5143500"/>
+    <ext cx="8382000" cy="5029200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -517,10 +507,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>278</row>
+      <row>31</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572499" cy="5143500"/>
+    <ext cx="8382000" cy="5029200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -542,10 +532,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>309</row>
+      <row>34</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572499" cy="5143500"/>
+    <ext cx="8382000" cy="5029200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -567,10 +557,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>340</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572499" cy="5143500"/>
+    <ext cx="8382000" cy="5029200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -880,7 +870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:C40"/>
+  <dimension ref="B1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -891,7 +881,7 @@
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Dagrapport dinsdag 13 oktober 2026</t>
+          <t>Dagrapport woensdag 14 oktober 2026</t>
         </is>
       </c>
     </row>
@@ -916,7 +906,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>9918.809999999999</v>
+        <v>9816.290000000001</v>
       </c>
     </row>
     <row r="6">
@@ -926,7 +916,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>-81.19</v>
+        <v>-183.71</v>
       </c>
     </row>
     <row r="7">
@@ -936,183 +926,177 @@
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>-0.008119000000000098</v>
+        <v>-0.01837099999999992</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Al vastgezet door verkopen</t>
+          <t>Vandaag</t>
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>0</v>
+        <v>-169.3299999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="4" t="inlineStr">
         <is>
+          <t>Al vastgezet door verkopen</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Beter of slechter dan de wereld-ETF</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>-0.013554995485898</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="4" t="inlineStr">
+        <is>
           <t>Klaar voor echt geld?</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>Nog niet klaar: de bot is nog bezig met bewijzen. Blijven oefenen.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" s="3" t="inlineStr">
+    <row r="13">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Waarde nu</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>10038.91</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>WINST sinds de start</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="n">
-        <v>38.91</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Sinds de start in %</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="n">
-        <v>0.003891000000000089</v>
+          <t>Waarde nu</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>10026.44</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Vandaag</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="n">
-        <v>42.6299999999992</v>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>WINST sinds de start</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>26.44</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Al vastgezet door verkopen</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="n">
-        <v>0</v>
+          <t>Sinds de start in %</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>0.002644000000000091</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="4" t="inlineStr">
         <is>
+          <t>Vandaag</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="n">
+        <v>12.02000000000044</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Al vastgezet door verkopen</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Beter of slechter dan de wereld-ETF</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="n">
+        <v>0.004602658445124974</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="4" t="inlineStr">
+        <is>
           <t>Klaar voor echt geld?</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>Nog niet klaar: de bot is nog bezig met bewijzen. Blijven oefenen.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="12" t="inlineStr">
+    <row r="22">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>Investeerder: wat de bot uit de analyse haalt</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="21.4" customHeight="1">
-      <c r="B20" s="13" t="inlineStr">
+    <row r="23" ht="21.4" customHeight="1">
+      <c r="B23" s="13" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="C20" s="14" t="inlineStr">
+      <c r="C23" s="14" t="inlineStr">
         <is>
           <t>De markt stijgt: de kern (wereld-ETF) doet zijn werk, de sterkste aandelen lopen mee.</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="38.8" customHeight="1">
-      <c r="B21" s="13" t="inlineStr">
+    <row r="24" ht="38.8" customHeight="1">
+      <c r="B24" s="13" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C24" s="14" t="inlineStr">
         <is>
           <t>Uit de top gevallen: ASML.AS, IFX.DE, SMH. Blijft dat zo, dan worden ze bij de volgende herverdeling (eerste handelsdag van 2026-11) vervangen door CRWD, PANW, INGA.AS.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="12" t="inlineStr">
+    <row r="26">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>Trend-agent: wat de bot uit de analyse haalt</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="21.4" customHeight="1">
-      <c r="B24" s="13" t="inlineStr">
+    <row r="27" ht="21.4" customHeight="1">
+      <c r="B27" s="13" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="C24" s="14" t="inlineStr">
+      <c r="C27" s="14" t="inlineStr">
         <is>
           <t>De markt stijgt breed: goede omstandigheden voor trendvolgen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="21.4" customHeight="1">
-      <c r="B25" s="13" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="C25" s="14" t="inlineStr">
-        <is>
-          <t>De markt is rustig: stops liggen dichterbij, posities kunnen iets groter.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="38.8" customHeight="1">
-      <c r="B26" s="13" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="C26" s="14" t="inlineStr">
-        <is>
-          <t>Amerika staat er duidelijk beter voor dan Europa (81% tegen 57% in een stijgende trend).</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="38.8" customHeight="1">
-      <c r="B27" s="13" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="C27" s="14" t="inlineStr">
-        <is>
-          <t>23 van de 50 instrumenten zijn een koopbare trend: veel keus, de bot neemt alleen de rustigste, sterkste.</t>
         </is>
       </c>
     </row>
@@ -1124,14 +1108,31 @@
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>Alle plekken zijn bezet, dus de bot koopt niets bij, hoe sterk een trend ook is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="12" t="inlineStr">
-        <is>
-          <t>Vandaag gekocht en verkocht</t>
+          <t>De markt is rustig: stops liggen dichterbij, posities kunnen iets groter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="38.8" customHeight="1">
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>Amerika staat er duidelijk beter voor dan Europa (81% tegen 57% in een stijgende trend).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="38.8" customHeight="1">
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>3 van de 5 sterkste staan al ver boven hun gemiddelde (SHELL.AS, WKL.AS, XOM): de trend is sterk, maar instappen op zo'n moment kost vaker een terugval.</t>
         </is>
       </c>
     </row>
@@ -1143,31 +1144,14 @@
       </c>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>Investeerder kocht IWDA.AS voor €5.997,00 (doelgewicht 60%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="21.4" customHeight="1">
-      <c r="B32" s="13" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="C32" s="14" t="inlineStr">
-        <is>
-          <t>Investeerder kocht MU voor €599,00 (doelgewicht 6%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="21.4" customHeight="1">
-      <c r="B33" s="13" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="C33" s="14" t="inlineStr">
-        <is>
-          <t>Investeerder kocht SMH voor €599,00 (doelgewicht 6%)</t>
+          <t>Alle plekken zijn bezet, dus de bot koopt niets bij, hoe sterk een trend ook is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>Vandaag gekocht en verkocht</t>
         </is>
       </c>
     </row>
@@ -1179,65 +1163,25 @@
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>Investeerder kocht ASML.AS voor €599,00 (doelgewicht 6%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="21.4" customHeight="1">
-      <c r="B35" s="13" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="C35" s="14" t="inlineStr">
-        <is>
-          <t>Investeerder kocht IFX.DE voor €599,00 (doelgewicht 6%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="21.4" customHeight="1">
-      <c r="B36" s="13" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="C36" s="14" t="inlineStr">
-        <is>
-          <t>Investeerder kocht AMD voor €599,00 (doelgewicht 6%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="21.4" customHeight="1">
-      <c r="B37" s="13" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="C37" s="14" t="inlineStr">
-        <is>
-          <t>Investeerder kocht ETH-USD voor €499,00 (doelgewicht 5%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="21.4" customHeight="1">
-      <c r="B38" s="13" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="C38" s="14" t="inlineStr">
-        <is>
-          <t>Investeerder kocht BTC-USD voor €499,00 (doelgewicht 5%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="2" t="inlineStr">
+          <t>Niets gekocht of verkocht.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>Meer weten? Zie de tabbladen hieronder: Grafieken, Analyse, Verlies en risico, Kansen, Klaar voor echt geld.</t>
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>Hoeveel zijn de bots waard?</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="313.5" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -1426,111 +1370,135 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:B340"/>
+  <dimension ref="B1:B37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="130" customWidth="1" min="2" max="2"/>
+    <col width="128" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="26" t="inlineStr">
+    <row r="1" ht="28" customHeight="1">
+      <c r="B1" s="22" t="inlineStr">
         <is>
           <t>Grafieken van vandaag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Elke grafiek legt bovenaan in gewone taal uit hoe het ervoor staat, en onderaan hoe je hem leest.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="24" customHeight="1">
-      <c r="B4" s="27" t="inlineStr">
-        <is>
-          <t>Waarde van de bots tegenover de wereld-ETF</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="24" customHeight="1">
-      <c r="B30" s="27" t="inlineStr">
-        <is>
-          <t>Trend-agent: Microsoft (MSFT)</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="24" customHeight="1">
-      <c r="B61" s="27" t="inlineStr">
-        <is>
-          <t>Trend-agent: SAP (SAP.DE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="24" customHeight="1">
-      <c r="B92" s="27" t="inlineStr">
-        <is>
-          <t>Trend-agent: Shell (SHELL.AS)</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="24" customHeight="1">
-      <c r="B123" s="27" t="inlineStr">
-        <is>
-          <t>Investeerder: AMD (AMD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="24" customHeight="1">
-      <c r="B154" s="27" t="inlineStr">
-        <is>
-          <t>Investeerder: ASML (ASML.AS)</t>
-        </is>
-      </c>
-    </row>
-    <row r="185" ht="24" customHeight="1">
-      <c r="B185" s="27" t="inlineStr">
-        <is>
-          <t>Investeerder: Bitcoin (BTC-USD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="216" ht="24" customHeight="1">
-      <c r="B216" s="27" t="inlineStr">
-        <is>
-          <t>Investeerder: Ethereum (ETH-USD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="247" ht="24" customHeight="1">
-      <c r="B247" s="27" t="inlineStr">
-        <is>
-          <t>Investeerder: Infineon (IFX.DE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="278" ht="24" customHeight="1">
-      <c r="B278" s="27" t="inlineStr">
-        <is>
-          <t>Investeerder: iShares MSCI World (IWDA.AS)</t>
-        </is>
-      </c>
-    </row>
-    <row r="309" ht="24" customHeight="1">
-      <c r="B309" s="27" t="inlineStr">
-        <is>
-          <t>Investeerder: Micron (MU)</t>
-        </is>
-      </c>
-    </row>
-    <row r="340" ht="24" customHeight="1">
-      <c r="B340" s="27" t="inlineStr">
-        <is>
-          <t>Investeerder: Halfgeleider-ETF (SMH)</t>
-        </is>
-      </c>
-    </row>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Scroll naar beneden: alle grafieken staan onder elkaar. Elke grafiek legt bovenaan in gewone taal uit hoe het ervoor staat, en onderaan hoe je hem leest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>1. Waarde van de bots tegenover de wereld-ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="336" customHeight="1"/>
+    <row r="6" ht="30" customHeight="1"/>
+    <row r="7" ht="26" customHeight="1">
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>2. Trend-agent: Microsoft (MSFT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="402" customHeight="1"/>
+    <row r="9" ht="30" customHeight="1"/>
+    <row r="10" ht="26" customHeight="1">
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>3. Trend-agent: SAP (SAP.DE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="402" customHeight="1"/>
+    <row r="12" ht="30" customHeight="1"/>
+    <row r="13" ht="26" customHeight="1">
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>4. Trend-agent: Shell (SHELL.AS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="402" customHeight="1"/>
+    <row r="15" ht="30" customHeight="1"/>
+    <row r="16" ht="26" customHeight="1">
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>5. Investeerder: AMD (AMD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="402" customHeight="1"/>
+    <row r="18" ht="30" customHeight="1"/>
+    <row r="19" ht="26" customHeight="1">
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>6. Investeerder: ASML (ASML.AS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="402" customHeight="1"/>
+    <row r="21" ht="30" customHeight="1"/>
+    <row r="22" ht="26" customHeight="1">
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>7. Investeerder: Bitcoin (BTC-USD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="402" customHeight="1"/>
+    <row r="24" ht="30" customHeight="1"/>
+    <row r="25" ht="26" customHeight="1">
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>8. Investeerder: Ethereum (ETH-USD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="402" customHeight="1"/>
+    <row r="27" ht="30" customHeight="1"/>
+    <row r="28" ht="26" customHeight="1">
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>9. Investeerder: Infineon (IFX.DE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="402" customHeight="1"/>
+    <row r="30" ht="30" customHeight="1"/>
+    <row r="31" ht="26" customHeight="1">
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>10. Investeerder: iShares MSCI World (IWDA.AS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="402" customHeight="1"/>
+    <row r="33" ht="30" customHeight="1"/>
+    <row r="34" ht="26" customHeight="1">
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>11. Investeerder: Micron (MU)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="402" customHeight="1"/>
+    <row r="36" ht="30" customHeight="1"/>
+    <row r="37" ht="26" customHeight="1">
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>12. Investeerder: Halfgeleider-ETF (SMH)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="402" customHeight="1"/>
+    <row r="39" ht="30" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -1582,7 +1550,7 @@
       </c>
       <c r="C2" s="16" t="inlineStr">
         <is>
-          <t>koers 132,30, 10,0% boven het 200-daags gemiddelde (120,29); de afgelopen maand +4,6%. Trend: stijgend.</t>
+          <t>koers 131,81, 9,6% boven het 200-daags gemiddelde (120,29); de afgelopen maand +4,3%. Trend: stijgend.</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1618,7 @@
       </c>
       <c r="C6" s="16" t="inlineStr">
         <is>
-          <t>14,2% boven het 200-daags gemiddelde (mag in de mix).</t>
+          <t>13,1% boven het 200-daags gemiddelde (mag in de mix).</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1635,7 @@
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>14,9% boven het 200-daags gemiddelde (mag in de mix).</t>
+          <t>12,6% boven het 200-daags gemiddelde (mag in de mix).</t>
         </is>
       </c>
     </row>
@@ -1718,7 +1686,7 @@
       </c>
       <c r="C10" s="16" t="inlineStr">
         <is>
-          <t>koers 132,30, 10,0% boven het 200-daags gemiddelde (120,29); de afgelopen maand +4,6%. Trend: stijgend.</t>
+          <t>koers 131,81, 9,6% boven het 200-daags gemiddelde (120,29); de afgelopen maand +4,3%. Trend: stijgend.</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1754,7 @@
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>geen stijgende trend (koers niet boven 50- en 200-daags gemiddelde): 24; niet gestegen over 1 of 3 maanden: 21; te weinig handel: 1.</t>
+          <t>geen stijgende trend (koers niet boven 50- en 200-daags gemiddelde): 26; niet gestegen over 1 of 3 maanden: 27; te weinig handel: 1.</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1771,7 @@
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>23. Koopbare trends: 23.</t>
+          <t>18. Koopbare trends: 18.</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1826,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="19.95" customHeight="1">
+    <row r="19" ht="35.9" customHeight="1">
       <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Trend-agent</t>
@@ -1871,7 +1839,7 @@
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>23 van de 50 instrumenten zijn een koopbare trend: veel keus, de bot neemt alleen de rustigste, sterkste.</t>
+          <t>3 van de 5 sterkste staan al ver boven hun gemiddelde (SHELL.AS, WKL.AS, XOM): de trend is sterk, maar instappen op zo'n moment kost vaker een terugval.</t>
         </is>
       </c>
     </row>
@@ -1986,26 +1954,26 @@
         <v>45.0575</v>
       </c>
       <c r="D2" t="n">
-        <v>46.51</v>
+        <v>46.455</v>
       </c>
       <c r="E2" t="n">
-        <v>43.7875</v>
+        <v>43.7325</v>
       </c>
       <c r="F2" s="17" t="n">
-        <v>18.88</v>
+        <v>18.17</v>
       </c>
       <c r="G2" s="18" t="n">
-        <v>0.0322</v>
+        <v>0.031</v>
       </c>
       <c r="H2" s="19" t="n">
-        <v>0.0622</v>
+        <v>0.0623</v>
       </c>
       <c r="I2" s="17" t="n">
-        <v>-17.51</v>
+        <v>-18.23</v>
       </c>
       <c r="J2" s="16" t="inlineStr">
         <is>
-          <t>Staat €18,88 in de plus. Zakt de koers 6,2% naar 43,79, dan verkoopt de bot met ongeveer €17,51 verlies.</t>
+          <t>Staat €18,17 in de plus. Zakt de koers 6,2% naar 43,73, dan verkoopt de bot met ongeveer €18,23 verlies.</t>
         </is>
       </c>
     </row>
@@ -2024,26 +1992,26 @@
         <v>191.5557</v>
       </c>
       <c r="D3" t="n">
-        <v>198.26</v>
+        <v>196.94</v>
       </c>
       <c r="E3" t="n">
-        <v>182.1971</v>
+        <v>181.0371</v>
       </c>
       <c r="F3" s="17" t="n">
-        <v>13.41</v>
+        <v>10.77</v>
       </c>
       <c r="G3" s="18" t="n">
-        <v>0.035</v>
+        <v>0.0281</v>
       </c>
       <c r="H3" s="19" t="n">
-        <v>0.0882</v>
+        <v>0.0878</v>
       </c>
       <c r="I3" s="17" t="n">
-        <v>-19.72</v>
+        <v>-22.04</v>
       </c>
       <c r="J3" s="16" t="inlineStr">
         <is>
-          <t>Staat €13,41 in de plus. Zakt de koers 8,8% naar 182,20, dan verkoopt de bot met ongeveer €19,72 verlies.</t>
+          <t>Staat €10,77 in de plus. Zakt de koers 8,8% naar 181,04, dan verkoopt de bot met ongeveer €22,04 verlies.</t>
         </is>
       </c>
     </row>
@@ -2062,26 +2030,26 @@
         <v>535.3375</v>
       </c>
       <c r="D4" t="n">
-        <v>542.04</v>
+        <v>533.6900000000001</v>
       </c>
       <c r="E4" t="n">
         <v>509.899</v>
       </c>
       <c r="F4" s="17" t="n">
-        <v>9.609999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="G4" s="18" t="n">
-        <v>0.0125</v>
+        <v>-0.0031</v>
       </c>
       <c r="H4" s="19" t="n">
-        <v>0.063</v>
+        <v>0.0467</v>
       </c>
       <c r="I4" s="17" t="n">
-        <v>-20.29</v>
+        <v>-21.81</v>
       </c>
       <c r="J4" s="16" t="inlineStr">
         <is>
-          <t>Staat €9,61 in de plus. Zakt de koers 6,3% naar 509,90, dan verkoopt de bot met ongeveer €20,29 verlies.</t>
+          <t>Staat €0,50 in de plus. Zakt de koers 4,7% naar 509,90, dan verkoopt de bot met ongeveer €21,81 verlies.</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2091,7 @@
         </is>
       </c>
       <c r="B8" s="19" t="n">
-        <v>0.0043</v>
+        <v>0.0012</v>
       </c>
       <c r="C8" s="19" t="n">
         <v>-0.01</v>
@@ -2179,40 +2147,40 @@
       <c r="A12" s="16" t="inlineStr"/>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>IFX.DE</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C12" s="21" t="n">
-        <v>569.8099999999999</v>
+        <v>554.28</v>
       </c>
       <c r="D12" s="21" t="n">
         <v>600</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>-30.19</v>
+        <v>-45.72</v>
       </c>
       <c r="F12" s="18" t="n">
-        <v>-0.0503</v>
+        <v>-0.0762</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="16" t="inlineStr"/>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>IFX.DE</t>
         </is>
       </c>
       <c r="C13" s="21" t="n">
-        <v>572.28</v>
+        <v>563</v>
       </c>
       <c r="D13" s="21" t="n">
         <v>600</v>
       </c>
       <c r="E13" s="17" t="n">
-        <v>-27.72</v>
+        <v>-37</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>-0.0462</v>
+        <v>-0.0617</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2223,16 +2191,16 @@
         </is>
       </c>
       <c r="C14" s="21" t="n">
-        <v>579.26</v>
+        <v>571.26</v>
       </c>
       <c r="D14" s="21" t="n">
         <v>600</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>-20.74</v>
+        <v>-28.74</v>
       </c>
       <c r="F14" s="18" t="n">
-        <v>-0.0346</v>
+        <v>-0.0479</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2243,16 +2211,16 @@
         </is>
       </c>
       <c r="C15" s="21" t="n">
-        <v>585.09</v>
+        <v>573.0700000000001</v>
       </c>
       <c r="D15" s="21" t="n">
         <v>600</v>
       </c>
       <c r="E15" s="17" t="n">
-        <v>-14.91</v>
+        <v>-26.93</v>
       </c>
       <c r="F15" s="18" t="n">
-        <v>-0.0249</v>
+        <v>-0.0449</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2263,16 +2231,16 @@
         </is>
       </c>
       <c r="C16" s="21" t="n">
-        <v>592.76</v>
+        <v>576.0700000000001</v>
       </c>
       <c r="D16" s="21" t="n">
         <v>600</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>-7.24</v>
+        <v>-23.93</v>
       </c>
       <c r="F16" s="18" t="n">
-        <v>-0.0121</v>
+        <v>-0.0399</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2283,16 +2251,16 @@
         </is>
       </c>
       <c r="C17" s="21" t="n">
-        <v>497.02</v>
+        <v>485.09</v>
       </c>
       <c r="D17" s="21" t="n">
         <v>500</v>
       </c>
       <c r="E17" s="17" t="n">
-        <v>-2.98</v>
+        <v>-14.91</v>
       </c>
       <c r="F17" s="18" t="n">
-        <v>-0.006</v>
+        <v>-0.0298</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2303,16 +2271,16 @@
         </is>
       </c>
       <c r="C18" s="21" t="n">
-        <v>499.91</v>
+        <v>493.14</v>
       </c>
       <c r="D18" s="21" t="n">
         <v>500</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>-0.09</v>
+        <v>-6.86</v>
       </c>
       <c r="F18" s="18" t="n">
-        <v>-0.0002</v>
+        <v>-0.0137</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2323,16 +2291,16 @@
         </is>
       </c>
       <c r="C19" s="21" t="n">
-        <v>6022.68</v>
+        <v>6000.38</v>
       </c>
       <c r="D19" s="21" t="n">
         <v>6000</v>
       </c>
       <c r="E19" s="17" t="n">
-        <v>22.68</v>
+        <v>0.38</v>
       </c>
       <c r="F19" s="18" t="n">
-        <v>0.0038</v>
+        <v>0.0001</v>
       </c>
     </row>
   </sheetData>
@@ -2384,7 +2352,7 @@
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>Opgelopen: de koers staat +7,1% van het 20-daags gemiddelde (3,7x de normale dagbeweging) en RSI is 81; na zo'n sprint volgt vaak eerst een terugval</t>
+          <t>Opgelopen: de koers staat +7,0% van het 20-daags gemiddelde (3,6x de normale dagbeweging) en RSI is 81; na zo'n sprint volgt vaak eerst een terugval</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2364,7 @@
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>Shell steeg +23,5% in 3 maanden en +8,9% in 1 maand; koers boven het 50-daags en dat boven het 200-daags gemiddelde; MACD positief (de stijging versnelt); handel 1,0x het normale volume; beweegt gemiddeld 1,9% per dag</t>
+          <t>Shell steeg +23,4% in 3 maanden en +8,8% in 1 maand; koers boven het 50-daags en dat boven het 200-daags gemiddelde; MACD positief (de stijging versnelt); handel 1,0x het normale volume; beweegt gemiddeld 1,9% per dag</t>
         </is>
       </c>
     </row>
@@ -2408,7 +2376,7 @@
       </c>
       <c r="C7" s="25" t="inlineStr">
         <is>
-          <t>Koop 13 stuks rond 46,53 EUR (inzet €604,93). Stop-loss op 44,72 EUR (-3,9%). Gaat het mis, dan is het verlies ongeveer €25,59.</t>
+          <t>Koop 13 stuks rond 46,48 EUR (inzet €604,22). Stop-loss op 44,66 EUR (-3,9%). Gaat het mis, dan is het verlies ongeveer €25,59.</t>
         </is>
       </c>
     </row>
@@ -2439,7 +2407,7 @@
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>Neutraal: de koers staat +5,2% van het 20-daags gemiddelde, RSI 68</t>
+          <t>Neutraal: de koers staat +4,6% van het 20-daags gemiddelde, RSI 66</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2419,7 @@
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>SAP steeg +43,7% in 3 maanden en +6,0% in 1 maand; koers boven het 50-daags en dat boven het 200-daags gemiddelde; MACD positief (de stijging versnelt); handel 0,8x het normale volume; beweegt gemiddeld 2,7% per dag</t>
+          <t>SAP steeg +42,8% in 3 maanden en +5,3% in 1 maand; koers boven het 50-daags en dat boven het 200-daags gemiddelde; MACD positief (de stijging versnelt); handel 0,8x het normale volume; beweegt gemiddeld 2,8% per dag</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2431,7 @@
       </c>
       <c r="C13" s="25" t="inlineStr">
         <is>
-          <t>Koop 2 stuks rond 198,36 EUR (inzet €396,72). Stop-loss op 187,65 EUR (-5,4%). Gaat het mis, dan is het verlies ongeveer €23,42.</t>
+          <t>Koop 2 stuks rond 197,04 EUR (inzet €394,08). Stop-loss op 186,21 EUR (-5,5%). Gaat het mis, dan is het verlies ongeveer €23,66.</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2462,7 @@
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>Opgelopen: de koers staat +9,4% van het 20-daags gemiddelde (3,3x de normale dagbeweging) en RSI is 74; na zo'n sprint volgt vaak eerst een terugval</t>
+          <t>Opgelopen: de koers staat +8,9% van het 20-daags gemiddelde (3,2x de normale dagbeweging) en RSI is 73; na zo'n sprint volgt vaak eerst een terugval</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2474,7 @@
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>Wolters Kluwer steeg +28,7% in 3 maanden en +14,2% in 1 maand; koers boven het 50-daags en dat boven het 200-daags gemiddelde; MACD positief (de stijging versnelt); handel 1,2x het normale volume; beweegt gemiddeld 2,8% per dag</t>
+          <t>Wolters Kluwer steeg +28,2% in 3 maanden en +13,7% in 1 maand; koers boven het 50-daags en dat boven het 200-daags gemiddelde; MACD positief (de stijging versnelt); handel 1,2x het normale volume; beweegt gemiddeld 2,8% per dag</t>
         </is>
       </c>
     </row>
@@ -2518,7 +2486,7 @@
       </c>
       <c r="C19" s="25" t="inlineStr">
         <is>
-          <t>Koop 5 stuks rond 78,44 EUR (inzet €392,20). Stop-loss op 74,02 EUR (-5,6%). Gaat het mis, dan is het verlies ongeveer €24,10.</t>
+          <t>Koop 5 stuks rond 78,10 EUR (inzet €390,50). Stop-loss op 73,68 EUR (-5,7%). Gaat het mis, dan is het verlies ongeveer €24,10.</t>
         </is>
       </c>
     </row>
@@ -2537,7 +2505,7 @@
     <row r="22">
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>4. Microsoft (MSFT)</t>
+          <t>4. Energie-ETF (XLE)</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2517,7 @@
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>Neutraal: de koers staat +4,1% van het 20-daags gemiddelde, RSI 70</t>
+          <t>Neutraal: de koers staat +5,2% van het 20-daags gemiddelde, RSI 72</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2529,7 @@
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>Microsoft steeg +35,4% in 3 maanden en +9,0% in 1 maand; koers boven het 50-daags en dat boven het 200-daags gemiddelde; MACD positief (de stijging versnelt); handel 0,8x het normale volume; beweegt gemiddeld 2,1% per dag</t>
+          <t>Energie-ETF steeg +19,3% in 3 maanden en +3,2% in 1 maand; koers boven het 50-daags en dat boven het 200-daags gemiddelde; MACD positief (de stijging versnelt); handel 1,1x het normale volume; beweegt gemiddeld 1,8% per dag</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2541,7 @@
       </c>
       <c r="C25" s="25" t="inlineStr">
         <is>
-          <t>Koop 1 stuk rond 542,31 USD (inzet €487,59). Stop-loss op 519,16 USD (-4,3%). Gaat het mis, dan is het verlies ongeveer €22,81.</t>
+          <t>Koop 11 stuks rond 67,66 USD (inzet €666,97). Stop-loss op 65,22 USD (-3,6%). Gaat het mis, dan is het verlies ongeveer €26,10.</t>
         </is>
       </c>
     </row>
@@ -2585,26 +2553,26 @@
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>Al in bezit</t>
+          <t>Niet gekocht: alle 3 plekken zijn bezet</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>5. Energie-ETF (XLE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="21.4" customHeight="1">
-      <c r="B29" s="24" t="inlineStr">
+          <t>5. ExxonMobil (XOM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="38.8" customHeight="1">
+      <c r="B29" s="23" t="inlineStr">
         <is>
           <t>Instapmoment</t>
         </is>
       </c>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>Neutraal: de koers staat +4,9% van het 20-daags gemiddelde, RSI 71</t>
+          <t>Opgelopen: de koers staat +6,2% van het 20-daags gemiddelde (3,4x de normale dagbeweging) en RSI is 75; na zo'n sprint volgt vaak eerst een terugval</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2584,7 @@
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>Energie-ETF steeg +18,9% in 3 maanden en +2,8% in 1 maand; koers boven het 50-daags en dat boven het 200-daags gemiddelde; MACD positief (de stijging versnelt); handel 1,1x het normale volume; beweegt gemiddeld 1,8% per dag</t>
+          <t>ExxonMobil steeg +22,1% in 3 maanden en +4,5% in 1 maand; koers boven het 50-daags en dat boven het 200-daags gemiddelde; MACD positief (de stijging versnelt); handel 0,9x het normale volume; beweegt gemiddeld 1,8% per dag</t>
         </is>
       </c>
     </row>
@@ -2628,7 +2596,7 @@
       </c>
       <c r="C31" s="25" t="inlineStr">
         <is>
-          <t>Koop 11 stuks rond 67,40 USD (inzet €666,63). Stop-loss op 64,97 USD (-3,6%). Gaat het mis, dan is het verlies ongeveer €26,09.</t>
+          <t>Koop 4 stuks rond 177,10 USD (inzet €634,79). Stop-loss op 170,67 USD (-3,6%). Gaat het mis, dan is het verlies ongeveer €25,03.</t>
         </is>
       </c>
     </row>
@@ -2705,7 +2673,7 @@
       </c>
       <c r="D2" s="16" t="inlineStr">
         <is>
-          <t>1 van 63 handelsdagen (ongeveer 3 maanden)</t>
+          <t>2 van 63 handelsdagen (ongeveer 3 maanden)</t>
         </is>
       </c>
     </row>
@@ -2727,7 +2695,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>nog te weinig dagen</t>
+          <t>verschil tot nu toe -1,36%</t>
         </is>
       </c>
     </row>
@@ -2749,7 +2717,7 @@
       </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
-          <t>bot -0,81%, ETF +0,00%</t>
+          <t>bot -1,84%, ETF -0,34%</t>
         </is>
       </c>
     </row>
@@ -2790,7 +2758,7 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>2 van 63 handelsdagen (ongeveer 3 maanden)</t>
+          <t>3 van 63 handelsdagen (ongeveer 3 maanden)</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2780,7 @@
       </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
-          <t>nog te weinig dagen</t>
+          <t>verschil tot nu toe +0,46%</t>
         </is>
       </c>
     </row>
@@ -2899,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2983,19 +2951,41 @@
         </is>
       </c>
       <c r="B4" s="21" t="n">
-        <v>9918.809999999999</v>
+        <v>9985.620000000001</v>
       </c>
       <c r="C4" s="17" t="n">
-        <v>-81.19</v>
+        <v>-14.38</v>
       </c>
       <c r="D4" s="21" t="n">
-        <v>10038.91</v>
+        <v>10014.42</v>
       </c>
       <c r="E4" s="17" t="n">
-        <v>38.91</v>
+        <v>14.42</v>
       </c>
       <c r="F4" t="n">
-        <v>132.3</v>
+        <v>132.26</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="n">
+        <v>9816.290000000001</v>
+      </c>
+      <c r="C5" s="17" t="n">
+        <v>-183.71</v>
+      </c>
+      <c r="D5" s="21" t="n">
+        <v>10026.44</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>26.44</v>
+      </c>
+      <c r="F5" t="n">
+        <v>131.81</v>
       </c>
     </row>
   </sheetData>

--- a/rapporten/voorbeeld/dagrapport.xlsx
+++ b/rapporten/voorbeeld/dagrapport.xlsx
@@ -32,7 +32,7 @@
     <numFmt numFmtId="166" formatCode="[Color10]+0.00%;[Red]-0.00%;0.00%"/>
     <numFmt numFmtId="167" formatCode="0.00%;[Red]-0.00%"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -80,13 +80,23 @@
       <sz val="18"/>
     </font>
     <font>
+      <i val="1"/>
+      <color rgb="0052514E"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="000B0B0B"/>
-      <sz val="14"/>
+      <sz val="13"/>
     </font>
     <font>
       <color rgb="0052514E"/>
-      <sz val="11"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000B0B0B"/>
+      <sz val="15"/>
     </font>
   </fonts>
   <fills count="5">
@@ -124,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -177,11 +187,17 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -845,8 +861,8 @@
         <minorTickMark val="none"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="9"/>
-        <tickMarkSkip val="9"/>
+        <tickLblSkip val="13"/>
+        <tickMarkSkip val="13"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -1240,8 +1256,8 @@
         <minorTickMark val="none"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="9"/>
-        <tickMarkSkip val="9"/>
+        <tickLblSkip val="13"/>
+        <tickMarkSkip val="13"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -1635,8 +1651,8 @@
         <minorTickMark val="none"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="9"/>
-        <tickMarkSkip val="9"/>
+        <tickLblSkip val="13"/>
+        <tickMarkSkip val="13"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -2102,8 +2118,8 @@
         <minorTickMark val="none"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="9"/>
-        <tickMarkSkip val="9"/>
+        <tickLblSkip val="13"/>
+        <tickMarkSkip val="13"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -2569,8 +2585,8 @@
         <minorTickMark val="none"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="9"/>
-        <tickMarkSkip val="9"/>
+        <tickLblSkip val="13"/>
+        <tickMarkSkip val="13"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -3036,8 +3052,8 @@
         <minorTickMark val="none"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="9"/>
-        <tickMarkSkip val="9"/>
+        <tickLblSkip val="13"/>
+        <tickMarkSkip val="13"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -3431,8 +3447,8 @@
         <minorTickMark val="none"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="9"/>
-        <tickMarkSkip val="9"/>
+        <tickLblSkip val="13"/>
+        <tickMarkSkip val="13"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -3826,8 +3842,8 @@
         <minorTickMark val="none"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="9"/>
-        <tickMarkSkip val="9"/>
+        <tickLblSkip val="13"/>
+        <tickMarkSkip val="13"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -4221,8 +4237,8 @@
         <minorTickMark val="none"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="9"/>
-        <tickMarkSkip val="9"/>
+        <tickLblSkip val="13"/>
+        <tickMarkSkip val="13"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -4616,8 +4632,8 @@
         <minorTickMark val="none"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="9"/>
-        <tickMarkSkip val="9"/>
+        <tickLblSkip val="13"/>
+        <tickMarkSkip val="13"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -5011,8 +5027,8 @@
         <minorTickMark val="none"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="9"/>
-        <tickMarkSkip val="9"/>
+        <tickLblSkip val="13"/>
+        <tickMarkSkip val="13"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -5067,10 +5083,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9360000" cy="4140000"/>
+    <ext cx="11340000" cy="3600000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -5089,10 +5105,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>35</row>
+      <row>30</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9360000" cy="4140000"/>
+    <ext cx="5580000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -5109,12 +5125,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>3</col>
       <colOff>0</colOff>
-      <row>65</row>
+      <row>30</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9360000" cy="4140000"/>
+    <ext cx="5580000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -5133,10 +5149,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>95</row>
+      <row>51</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9360000" cy="4140000"/>
+    <ext cx="5580000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -5155,10 +5171,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>124</row>
+      <row>74</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9360000" cy="4140000"/>
+    <ext cx="5580000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -5175,12 +5191,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>3</col>
       <colOff>0</colOff>
-      <row>153</row>
+      <row>74</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9360000" cy="4140000"/>
+    <ext cx="5580000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
@@ -5199,10 +5215,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>182</row>
+      <row>95</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9360000" cy="4140000"/>
+    <ext cx="5580000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="7" name="Chart 7"/>
@@ -5219,12 +5235,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>3</col>
       <colOff>0</colOff>
-      <row>211</row>
+      <row>95</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9360000" cy="4140000"/>
+    <ext cx="5580000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="8" name="Chart 8"/>
@@ -5243,10 +5259,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>240</row>
+      <row>116</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9360000" cy="4140000"/>
+    <ext cx="5580000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="9" name="Chart 9"/>
@@ -5263,12 +5279,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>3</col>
       <colOff>0</colOff>
-      <row>269</row>
+      <row>116</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9360000" cy="4140000"/>
+    <ext cx="5580000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="10" name="Chart 10"/>
@@ -5287,10 +5303,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>298</row>
+      <row>137</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9360000" cy="4140000"/>
+    <ext cx="5580000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="11" name="Chart 11"/>
@@ -5307,12 +5323,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>3</col>
       <colOff>0</colOff>
-      <row>327</row>
+      <row>137</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9360000" cy="4140000"/>
+    <ext cx="5580000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="12" name="Chart 12"/>
@@ -5655,7 +5671,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>9820.860000000001</v>
+        <v>9820.690000000001</v>
       </c>
     </row>
     <row r="6">
@@ -5665,7 +5681,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>-179.14</v>
+        <v>-179.31</v>
       </c>
     </row>
     <row r="7">
@@ -5675,7 +5691,7 @@
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>-0.01791399999999999</v>
+        <v>-0.01793099999999992</v>
       </c>
     </row>
     <row r="8">
@@ -5685,7 +5701,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>-164.7600000000002</v>
+        <v>-164.9300000000003</v>
       </c>
     </row>
     <row r="9">
@@ -5705,7 +5721,7 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>-0.01309733737353247</v>
+        <v>-0.01311436185473647</v>
       </c>
     </row>
     <row r="11">
@@ -6751,26 +6767,26 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>15 jul</t>
+          <t>16 jul</t>
         </is>
       </c>
       <c r="BT2" t="n">
-        <v>126.42</v>
+        <v>126.06</v>
       </c>
       <c r="BU2" t="n">
-        <v>126.64</v>
+        <v>126.29</v>
       </c>
       <c r="BV2" t="n">
-        <v>126.12</v>
+        <v>125.5</v>
       </c>
       <c r="BW2" t="n">
-        <v>126.29</v>
+        <v>126.26</v>
       </c>
       <c r="BX2" t="n">
-        <v>123.3492</v>
+        <v>123.4818</v>
       </c>
       <c r="BY2" t="n">
-        <v>114.7279</v>
+        <v>114.8231</v>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
@@ -7026,26 +7042,26 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>16 jul</t>
+          <t>17 jul</t>
         </is>
       </c>
       <c r="BT3" t="n">
-        <v>126.06</v>
+        <v>124.66</v>
       </c>
       <c r="BU3" t="n">
-        <v>126.29</v>
+        <v>125.18</v>
       </c>
       <c r="BV3" t="n">
-        <v>125.5</v>
+        <v>124.27</v>
       </c>
       <c r="BW3" t="n">
-        <v>126.26</v>
+        <v>124.85</v>
       </c>
       <c r="BX3" t="n">
-        <v>123.4818</v>
+        <v>123.5886</v>
       </c>
       <c r="BY3" t="n">
-        <v>114.8231</v>
+        <v>114.9072</v>
       </c>
       <c r="CA3" t="inlineStr">
         <is>
@@ -7307,26 +7323,26 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>17 jul</t>
+          <t>20 jul</t>
         </is>
       </c>
       <c r="BT4" t="n">
+        <v>124.77</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>125.63</v>
+      </c>
+      <c r="BV4" t="n">
         <v>124.66</v>
       </c>
-      <c r="BU4" t="n">
-        <v>125.18</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>124.27</v>
-      </c>
       <c r="BW4" t="n">
-        <v>124.85</v>
+        <v>125.26</v>
       </c>
       <c r="BX4" t="n">
-        <v>123.5886</v>
+        <v>123.6952</v>
       </c>
       <c r="BY4" t="n">
-        <v>114.9072</v>
+        <v>114.9915</v>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
@@ -7380,7 +7396,7 @@
         </is>
       </c>
       <c r="KO4" t="n">
-        <v>9820.860000000001</v>
+        <v>9820.690000000001</v>
       </c>
       <c r="KP4" t="n">
         <v>10026.55</v>
@@ -7588,26 +7604,26 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>20 jul</t>
+          <t>21 jul</t>
         </is>
       </c>
       <c r="BT5" t="n">
-        <v>124.77</v>
+        <v>125.34</v>
       </c>
       <c r="BU5" t="n">
-        <v>125.63</v>
+        <v>125.75</v>
       </c>
       <c r="BV5" t="n">
-        <v>124.66</v>
+        <v>125.05</v>
       </c>
       <c r="BW5" t="n">
-        <v>125.26</v>
+        <v>125.75</v>
       </c>
       <c r="BX5" t="n">
-        <v>123.6952</v>
+        <v>123.827</v>
       </c>
       <c r="BY5" t="n">
-        <v>114.9915</v>
+        <v>115.076</v>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
@@ -7861,26 +7877,26 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>21 jul</t>
+          <t>22 jul</t>
         </is>
       </c>
       <c r="BT6" t="n">
-        <v>125.34</v>
+        <v>125.39</v>
       </c>
       <c r="BU6" t="n">
-        <v>125.75</v>
+        <v>126.08</v>
       </c>
       <c r="BV6" t="n">
-        <v>125.05</v>
+        <v>125.3</v>
       </c>
       <c r="BW6" t="n">
-        <v>125.75</v>
+        <v>126.03</v>
       </c>
       <c r="BX6" t="n">
-        <v>123.827</v>
+        <v>123.939</v>
       </c>
       <c r="BY6" t="n">
-        <v>115.076</v>
+        <v>115.1599</v>
       </c>
       <c r="CA6" t="inlineStr">
         <is>
@@ -8134,26 +8150,26 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>22 jul</t>
+          <t>23 jul</t>
         </is>
       </c>
       <c r="BT7" t="n">
-        <v>125.39</v>
+        <v>125.34</v>
       </c>
       <c r="BU7" t="n">
-        <v>126.08</v>
+        <v>125.59</v>
       </c>
       <c r="BV7" t="n">
-        <v>125.3</v>
+        <v>124.27</v>
       </c>
       <c r="BW7" t="n">
-        <v>126.03</v>
+        <v>124.4</v>
       </c>
       <c r="BX7" t="n">
-        <v>123.939</v>
+        <v>123.9872</v>
       </c>
       <c r="BY7" t="n">
-        <v>115.1599</v>
+        <v>115.2366</v>
       </c>
       <c r="CA7" t="inlineStr">
         <is>
@@ -8407,26 +8423,26 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>23 jul</t>
+          <t>24 jul</t>
         </is>
       </c>
       <c r="BT8" t="n">
-        <v>125.34</v>
+        <v>124.62</v>
       </c>
       <c r="BU8" t="n">
-        <v>125.59</v>
+        <v>125.39</v>
       </c>
       <c r="BV8" t="n">
-        <v>124.27</v>
+        <v>124.57</v>
       </c>
       <c r="BW8" t="n">
-        <v>124.4</v>
+        <v>125.26</v>
       </c>
       <c r="BX8" t="n">
-        <v>123.9872</v>
+        <v>124.0724</v>
       </c>
       <c r="BY8" t="n">
-        <v>115.2366</v>
+        <v>115.3129</v>
       </c>
       <c r="CA8" t="inlineStr">
         <is>
@@ -8680,26 +8696,26 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>24 jul</t>
+          <t>27 jul</t>
         </is>
       </c>
       <c r="BT9" t="n">
-        <v>124.62</v>
+        <v>125.76</v>
       </c>
       <c r="BU9" t="n">
-        <v>125.39</v>
+        <v>125.97</v>
       </c>
       <c r="BV9" t="n">
-        <v>124.57</v>
+        <v>124.73</v>
       </c>
       <c r="BW9" t="n">
-        <v>125.26</v>
+        <v>124.75</v>
       </c>
       <c r="BX9" t="n">
-        <v>124.0724</v>
+        <v>124.1596</v>
       </c>
       <c r="BY9" t="n">
-        <v>115.3129</v>
+        <v>115.3865</v>
       </c>
       <c r="CA9" t="inlineStr">
         <is>
@@ -8953,26 +8969,26 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>27 jul</t>
+          <t>28 jul</t>
         </is>
       </c>
       <c r="BT10" t="n">
-        <v>125.76</v>
+        <v>124.82</v>
       </c>
       <c r="BU10" t="n">
-        <v>125.97</v>
+        <v>125.24</v>
       </c>
       <c r="BV10" t="n">
-        <v>124.73</v>
+        <v>124.53</v>
       </c>
       <c r="BW10" t="n">
-        <v>124.75</v>
+        <v>125.18</v>
       </c>
       <c r="BX10" t="n">
-        <v>124.1596</v>
+        <v>124.2572</v>
       </c>
       <c r="BY10" t="n">
-        <v>115.3865</v>
+        <v>115.4728</v>
       </c>
       <c r="CA10" t="inlineStr">
         <is>
@@ -9226,26 +9242,26 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>28 jul</t>
+          <t>29 jul</t>
         </is>
       </c>
       <c r="BT11" t="n">
-        <v>124.82</v>
+        <v>125.36</v>
       </c>
       <c r="BU11" t="n">
-        <v>125.24</v>
+        <v>125.48</v>
       </c>
       <c r="BV11" t="n">
-        <v>124.53</v>
+        <v>124.05</v>
       </c>
       <c r="BW11" t="n">
-        <v>125.18</v>
+        <v>124.33</v>
       </c>
       <c r="BX11" t="n">
-        <v>124.2572</v>
+        <v>124.3162</v>
       </c>
       <c r="BY11" t="n">
-        <v>115.4728</v>
+        <v>115.5507</v>
       </c>
       <c r="CA11" t="inlineStr">
         <is>
@@ -9499,26 +9515,26 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>29 jul</t>
+          <t>30 jul</t>
         </is>
       </c>
       <c r="BT12" t="n">
-        <v>125.36</v>
+        <v>123.55</v>
       </c>
       <c r="BU12" t="n">
-        <v>125.48</v>
+        <v>124.08</v>
       </c>
       <c r="BV12" t="n">
-        <v>124.05</v>
+        <v>123.17</v>
       </c>
       <c r="BW12" t="n">
-        <v>124.33</v>
+        <v>123.69</v>
       </c>
       <c r="BX12" t="n">
-        <v>124.3162</v>
+        <v>124.3596</v>
       </c>
       <c r="BY12" t="n">
-        <v>115.5507</v>
+        <v>115.6281</v>
       </c>
       <c r="CA12" t="inlineStr">
         <is>
@@ -9699,7 +9715,7 @@
         <v>1535.6006</v>
       </c>
       <c r="AS13" t="n">
-        <v>1204.2381</v>
+        <v>1204.238</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -9772,26 +9788,26 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>30 jul</t>
+          <t>31 jul</t>
         </is>
       </c>
       <c r="BT13" t="n">
-        <v>123.55</v>
+        <v>124.77</v>
       </c>
       <c r="BU13" t="n">
-        <v>124.08</v>
+        <v>125.22</v>
       </c>
       <c r="BV13" t="n">
-        <v>123.17</v>
+        <v>123.95</v>
       </c>
       <c r="BW13" t="n">
-        <v>123.69</v>
+        <v>124.23</v>
       </c>
       <c r="BX13" t="n">
-        <v>124.3596</v>
+        <v>124.3876</v>
       </c>
       <c r="BY13" t="n">
-        <v>115.6281</v>
+        <v>115.7046</v>
       </c>
       <c r="CA13" t="inlineStr">
         <is>
@@ -10045,26 +10061,26 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>31 jul</t>
+          <t>3 aug</t>
         </is>
       </c>
       <c r="BT14" t="n">
-        <v>124.77</v>
+        <v>125.4</v>
       </c>
       <c r="BU14" t="n">
-        <v>125.22</v>
+        <v>126.2</v>
       </c>
       <c r="BV14" t="n">
-        <v>123.95</v>
+        <v>125.1</v>
       </c>
       <c r="BW14" t="n">
-        <v>124.23</v>
+        <v>126.12</v>
       </c>
       <c r="BX14" t="n">
-        <v>124.3876</v>
+        <v>124.4394</v>
       </c>
       <c r="BY14" t="n">
-        <v>115.7046</v>
+        <v>115.7914</v>
       </c>
       <c r="CA14" t="inlineStr">
         <is>
@@ -10318,26 +10334,26 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>3 aug</t>
+          <t>4 aug</t>
         </is>
       </c>
       <c r="BT15" t="n">
-        <v>125.4</v>
+        <v>126.84</v>
       </c>
       <c r="BU15" t="n">
-        <v>126.2</v>
+        <v>127.88</v>
       </c>
       <c r="BV15" t="n">
-        <v>125.1</v>
+        <v>126.53</v>
       </c>
       <c r="BW15" t="n">
-        <v>126.12</v>
+        <v>127.8</v>
       </c>
       <c r="BX15" t="n">
-        <v>124.4394</v>
+        <v>124.5332</v>
       </c>
       <c r="BY15" t="n">
-        <v>115.7914</v>
+        <v>115.8921</v>
       </c>
       <c r="CA15" t="inlineStr">
         <is>
@@ -10591,26 +10607,26 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>4 aug</t>
+          <t>5 aug</t>
         </is>
       </c>
       <c r="BT16" t="n">
-        <v>126.84</v>
+        <v>128.61</v>
       </c>
       <c r="BU16" t="n">
-        <v>127.88</v>
+        <v>128.96</v>
       </c>
       <c r="BV16" t="n">
-        <v>126.53</v>
+        <v>128.16</v>
       </c>
       <c r="BW16" t="n">
-        <v>127.8</v>
+        <v>128.26</v>
       </c>
       <c r="BX16" t="n">
-        <v>124.5332</v>
+        <v>124.6406</v>
       </c>
       <c r="BY16" t="n">
-        <v>115.8921</v>
+        <v>115.9859</v>
       </c>
       <c r="CA16" t="inlineStr">
         <is>
@@ -10864,26 +10880,26 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>5 aug</t>
+          <t>6 aug</t>
         </is>
       </c>
       <c r="BT17" t="n">
-        <v>128.61</v>
+        <v>128.24</v>
       </c>
       <c r="BU17" t="n">
-        <v>128.96</v>
+        <v>128.49</v>
       </c>
       <c r="BV17" t="n">
-        <v>128.16</v>
+        <v>128.02</v>
       </c>
       <c r="BW17" t="n">
-        <v>128.26</v>
+        <v>128.12</v>
       </c>
       <c r="BX17" t="n">
-        <v>124.6406</v>
+        <v>124.7396</v>
       </c>
       <c r="BY17" t="n">
-        <v>115.9859</v>
+        <v>116.0767</v>
       </c>
       <c r="CA17" t="inlineStr">
         <is>
@@ -11137,26 +11153,26 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>6 aug</t>
+          <t>7 aug</t>
         </is>
       </c>
       <c r="BT18" t="n">
-        <v>128.24</v>
+        <v>128.31</v>
       </c>
       <c r="BU18" t="n">
-        <v>128.49</v>
+        <v>128.72</v>
       </c>
       <c r="BV18" t="n">
-        <v>128.02</v>
+        <v>128.2</v>
       </c>
       <c r="BW18" t="n">
-        <v>128.12</v>
+        <v>128.65</v>
       </c>
       <c r="BX18" t="n">
-        <v>124.7396</v>
+        <v>124.845</v>
       </c>
       <c r="BY18" t="n">
-        <v>116.0767</v>
+        <v>116.1734</v>
       </c>
       <c r="CA18" t="inlineStr">
         <is>
@@ -11410,26 +11426,26 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>7 aug</t>
+          <t>10 aug</t>
         </is>
       </c>
       <c r="BT19" t="n">
-        <v>128.31</v>
+        <v>128.78</v>
       </c>
       <c r="BU19" t="n">
-        <v>128.72</v>
+        <v>128.89</v>
       </c>
       <c r="BV19" t="n">
-        <v>128.2</v>
+        <v>128.55</v>
       </c>
       <c r="BW19" t="n">
-        <v>128.65</v>
+        <v>128.75</v>
       </c>
       <c r="BX19" t="n">
-        <v>124.845</v>
+        <v>124.9454</v>
       </c>
       <c r="BY19" t="n">
-        <v>116.1734</v>
+        <v>116.2684</v>
       </c>
       <c r="CA19" t="inlineStr">
         <is>
@@ -11683,26 +11699,26 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>10 aug</t>
+          <t>11 aug</t>
         </is>
       </c>
       <c r="BT20" t="n">
-        <v>128.78</v>
+        <v>128.8</v>
       </c>
       <c r="BU20" t="n">
-        <v>128.89</v>
+        <v>129.11</v>
       </c>
       <c r="BV20" t="n">
-        <v>128.55</v>
+        <v>128.7</v>
       </c>
       <c r="BW20" t="n">
-        <v>128.75</v>
+        <v>128.7</v>
       </c>
       <c r="BX20" t="n">
-        <v>124.9454</v>
+        <v>125.0336</v>
       </c>
       <c r="BY20" t="n">
-        <v>116.2684</v>
+        <v>116.3589</v>
       </c>
       <c r="CA20" t="inlineStr">
         <is>
@@ -11956,26 +11972,26 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>11 aug</t>
+          <t>12 aug</t>
         </is>
       </c>
       <c r="BT21" t="n">
+        <v>128.75</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>129.05</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>128.64</v>
+      </c>
+      <c r="BW21" t="n">
         <v>128.8</v>
       </c>
-      <c r="BU21" t="n">
-        <v>129.11</v>
-      </c>
-      <c r="BV21" t="n">
-        <v>128.7</v>
-      </c>
-      <c r="BW21" t="n">
-        <v>128.7</v>
-      </c>
       <c r="BX21" t="n">
-        <v>125.0336</v>
+        <v>125.1314</v>
       </c>
       <c r="BY21" t="n">
-        <v>116.3589</v>
+        <v>116.4461</v>
       </c>
       <c r="CA21" t="inlineStr">
         <is>
@@ -12229,26 +12245,26 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>12 aug</t>
+          <t>13 aug</t>
         </is>
       </c>
       <c r="BT22" t="n">
-        <v>128.75</v>
+        <v>129.19</v>
       </c>
       <c r="BU22" t="n">
-        <v>129.05</v>
+        <v>129.83</v>
       </c>
       <c r="BV22" t="n">
-        <v>128.64</v>
+        <v>129.11</v>
       </c>
       <c r="BW22" t="n">
-        <v>128.8</v>
+        <v>129.39</v>
       </c>
       <c r="BX22" t="n">
-        <v>125.1314</v>
+        <v>125.2418</v>
       </c>
       <c r="BY22" t="n">
-        <v>116.4461</v>
+        <v>116.5352</v>
       </c>
       <c r="CA22" t="inlineStr">
         <is>
@@ -12502,26 +12518,26 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>13 aug</t>
+          <t>14 aug</t>
         </is>
       </c>
       <c r="BT23" t="n">
-        <v>129.19</v>
+        <v>129.51</v>
       </c>
       <c r="BU23" t="n">
-        <v>129.83</v>
+        <v>129.55</v>
       </c>
       <c r="BV23" t="n">
-        <v>129.11</v>
+        <v>128.84</v>
       </c>
       <c r="BW23" t="n">
-        <v>129.39</v>
+        <v>128.84</v>
       </c>
       <c r="BX23" t="n">
-        <v>125.2418</v>
+        <v>125.352</v>
       </c>
       <c r="BY23" t="n">
-        <v>116.5352</v>
+        <v>116.6207</v>
       </c>
       <c r="CA23" t="inlineStr">
         <is>
@@ -12775,26 +12791,26 @@
       </c>
       <c r="BS24" t="inlineStr">
         <is>
-          <t>14 aug</t>
+          <t>17 aug</t>
         </is>
       </c>
       <c r="BT24" t="n">
-        <v>129.51</v>
+        <v>129.03</v>
       </c>
       <c r="BU24" t="n">
-        <v>129.55</v>
+        <v>129.04</v>
       </c>
       <c r="BV24" t="n">
-        <v>128.84</v>
+        <v>128.61</v>
       </c>
       <c r="BW24" t="n">
-        <v>128.84</v>
+        <v>128.72</v>
       </c>
       <c r="BX24" t="n">
-        <v>125.352</v>
+        <v>125.4734</v>
       </c>
       <c r="BY24" t="n">
-        <v>116.6207</v>
+        <v>116.7047</v>
       </c>
       <c r="CA24" t="inlineStr">
         <is>
@@ -13048,26 +13064,26 @@
       </c>
       <c r="BS25" t="inlineStr">
         <is>
-          <t>17 aug</t>
+          <t>18 aug</t>
         </is>
       </c>
       <c r="BT25" t="n">
-        <v>129.03</v>
+        <v>127.99</v>
       </c>
       <c r="BU25" t="n">
-        <v>129.04</v>
+        <v>128.06</v>
       </c>
       <c r="BV25" t="n">
-        <v>128.61</v>
+        <v>127.38</v>
       </c>
       <c r="BW25" t="n">
-        <v>128.72</v>
+        <v>127.42</v>
       </c>
       <c r="BX25" t="n">
-        <v>125.4734</v>
+        <v>125.6048</v>
       </c>
       <c r="BY25" t="n">
-        <v>116.7047</v>
+        <v>116.7829</v>
       </c>
       <c r="CA25" t="inlineStr">
         <is>
@@ -13321,26 +13337,26 @@
       </c>
       <c r="BS26" t="inlineStr">
         <is>
-          <t>18 aug</t>
+          <t>19 aug</t>
         </is>
       </c>
       <c r="BT26" t="n">
-        <v>127.99</v>
+        <v>127.18</v>
       </c>
       <c r="BU26" t="n">
-        <v>128.06</v>
+        <v>127.47</v>
       </c>
       <c r="BV26" t="n">
-        <v>127.38</v>
+        <v>126.78</v>
       </c>
       <c r="BW26" t="n">
-        <v>127.42</v>
+        <v>126.99</v>
       </c>
       <c r="BX26" t="n">
-        <v>125.6048</v>
+        <v>125.7298</v>
       </c>
       <c r="BY26" t="n">
-        <v>116.7829</v>
+        <v>116.8581</v>
       </c>
       <c r="CA26" t="inlineStr">
         <is>
@@ -13594,26 +13610,26 @@
       </c>
       <c r="BS27" t="inlineStr">
         <is>
-          <t>19 aug</t>
+          <t>20 aug</t>
         </is>
       </c>
       <c r="BT27" t="n">
-        <v>127.18</v>
+        <v>126.71</v>
       </c>
       <c r="BU27" t="n">
-        <v>127.47</v>
+        <v>126.78</v>
       </c>
       <c r="BV27" t="n">
-        <v>126.78</v>
+        <v>125.8</v>
       </c>
       <c r="BW27" t="n">
-        <v>126.99</v>
+        <v>126.18</v>
       </c>
       <c r="BX27" t="n">
-        <v>125.7298</v>
+        <v>125.8356</v>
       </c>
       <c r="BY27" t="n">
-        <v>116.8581</v>
+        <v>116.9312</v>
       </c>
       <c r="CA27" t="inlineStr">
         <is>
@@ -13867,26 +13883,26 @@
       </c>
       <c r="BS28" t="inlineStr">
         <is>
-          <t>20 aug</t>
+          <t>21 aug</t>
         </is>
       </c>
       <c r="BT28" t="n">
-        <v>126.71</v>
+        <v>125.87</v>
       </c>
       <c r="BU28" t="n">
-        <v>126.78</v>
+        <v>126.51</v>
       </c>
       <c r="BV28" t="n">
-        <v>125.8</v>
+        <v>125.86</v>
       </c>
       <c r="BW28" t="n">
-        <v>126.18</v>
+        <v>126.51</v>
       </c>
       <c r="BX28" t="n">
-        <v>125.8356</v>
+        <v>125.9096</v>
       </c>
       <c r="BY28" t="n">
-        <v>116.9312</v>
+        <v>117.0051</v>
       </c>
       <c r="CA28" t="inlineStr">
         <is>
@@ -14140,26 +14156,26 @@
       </c>
       <c r="BS29" t="inlineStr">
         <is>
-          <t>21 aug</t>
+          <t>24 aug</t>
         </is>
       </c>
       <c r="BT29" t="n">
-        <v>125.87</v>
+        <v>126.15</v>
       </c>
       <c r="BU29" t="n">
-        <v>126.51</v>
+        <v>126.5</v>
       </c>
       <c r="BV29" t="n">
-        <v>125.86</v>
+        <v>125.99</v>
       </c>
       <c r="BW29" t="n">
-        <v>126.51</v>
+        <v>126.23</v>
       </c>
       <c r="BX29" t="n">
-        <v>125.9096</v>
+        <v>125.9494</v>
       </c>
       <c r="BY29" t="n">
-        <v>117.0051</v>
+        <v>117.0851</v>
       </c>
       <c r="CA29" t="inlineStr">
         <is>
@@ -14413,26 +14429,26 @@
       </c>
       <c r="BS30" t="inlineStr">
         <is>
-          <t>24 aug</t>
+          <t>25 aug</t>
         </is>
       </c>
       <c r="BT30" t="n">
-        <v>126.15</v>
+        <v>126.7</v>
       </c>
       <c r="BU30" t="n">
-        <v>126.5</v>
+        <v>126.9</v>
       </c>
       <c r="BV30" t="n">
-        <v>125.99</v>
+        <v>126.31</v>
       </c>
       <c r="BW30" t="n">
-        <v>126.23</v>
+        <v>126.53</v>
       </c>
       <c r="BX30" t="n">
-        <v>125.9494</v>
+        <v>125.9972</v>
       </c>
       <c r="BY30" t="n">
-        <v>117.0851</v>
+        <v>117.174</v>
       </c>
       <c r="CA30" t="inlineStr">
         <is>
@@ -14686,26 +14702,26 @@
       </c>
       <c r="BS31" t="inlineStr">
         <is>
-          <t>25 aug</t>
+          <t>26 aug</t>
         </is>
       </c>
       <c r="BT31" t="n">
-        <v>126.7</v>
+        <v>126.67</v>
       </c>
       <c r="BU31" t="n">
-        <v>126.9</v>
+        <v>127.04</v>
       </c>
       <c r="BV31" t="n">
-        <v>126.31</v>
+        <v>126.49</v>
       </c>
       <c r="BW31" t="n">
-        <v>126.53</v>
+        <v>126.67</v>
       </c>
       <c r="BX31" t="n">
-        <v>125.9972</v>
+        <v>126.0464</v>
       </c>
       <c r="BY31" t="n">
-        <v>117.174</v>
+        <v>117.2526</v>
       </c>
       <c r="CA31" t="inlineStr">
         <is>
@@ -14959,26 +14975,26 @@
       </c>
       <c r="BS32" t="inlineStr">
         <is>
-          <t>26 aug</t>
+          <t>27 aug</t>
         </is>
       </c>
       <c r="BT32" t="n">
-        <v>126.67</v>
+        <v>127.06</v>
       </c>
       <c r="BU32" t="n">
-        <v>127.04</v>
+        <v>127.29</v>
       </c>
       <c r="BV32" t="n">
-        <v>126.49</v>
+        <v>126.78</v>
       </c>
       <c r="BW32" t="n">
-        <v>126.67</v>
+        <v>127.14</v>
       </c>
       <c r="BX32" t="n">
-        <v>126.0464</v>
+        <v>126.0968</v>
       </c>
       <c r="BY32" t="n">
-        <v>117.2526</v>
+        <v>117.3316</v>
       </c>
       <c r="CA32" t="inlineStr">
         <is>
@@ -15232,26 +15248,26 @@
       </c>
       <c r="BS33" t="inlineStr">
         <is>
-          <t>27 aug</t>
+          <t>28 aug</t>
         </is>
       </c>
       <c r="BT33" t="n">
-        <v>127.06</v>
+        <v>127.56</v>
       </c>
       <c r="BU33" t="n">
-        <v>127.29</v>
+        <v>128.28</v>
       </c>
       <c r="BV33" t="n">
-        <v>126.78</v>
+        <v>127.42</v>
       </c>
       <c r="BW33" t="n">
-        <v>127.14</v>
+        <v>128.22</v>
       </c>
       <c r="BX33" t="n">
-        <v>126.0968</v>
+        <v>126.1648</v>
       </c>
       <c r="BY33" t="n">
-        <v>117.3316</v>
+        <v>117.4129</v>
       </c>
       <c r="CA33" t="inlineStr">
         <is>
@@ -15505,26 +15521,26 @@
       </c>
       <c r="BS34" t="inlineStr">
         <is>
-          <t>28 aug</t>
+          <t>31 aug</t>
         </is>
       </c>
       <c r="BT34" t="n">
-        <v>127.56</v>
+        <v>127.59</v>
       </c>
       <c r="BU34" t="n">
-        <v>128.28</v>
+        <v>127.64</v>
       </c>
       <c r="BV34" t="n">
-        <v>127.42</v>
+        <v>126.77</v>
       </c>
       <c r="BW34" t="n">
-        <v>128.22</v>
+        <v>126.78</v>
       </c>
       <c r="BX34" t="n">
-        <v>126.1648</v>
+        <v>126.1998</v>
       </c>
       <c r="BY34" t="n">
-        <v>117.4129</v>
+        <v>117.4943</v>
       </c>
       <c r="CA34" t="inlineStr">
         <is>
@@ -15778,26 +15794,26 @@
       </c>
       <c r="BS35" t="inlineStr">
         <is>
-          <t>31 aug</t>
+          <t>1 sep</t>
         </is>
       </c>
       <c r="BT35" t="n">
-        <v>127.59</v>
+        <v>127.21</v>
       </c>
       <c r="BU35" t="n">
-        <v>127.64</v>
+        <v>127.35</v>
       </c>
       <c r="BV35" t="n">
-        <v>126.77</v>
+        <v>126.26</v>
       </c>
       <c r="BW35" t="n">
-        <v>126.78</v>
+        <v>126.58</v>
       </c>
       <c r="BX35" t="n">
-        <v>126.1998</v>
+        <v>126.2516</v>
       </c>
       <c r="BY35" t="n">
-        <v>117.4943</v>
+        <v>117.5762</v>
       </c>
       <c r="CA35" t="inlineStr">
         <is>
@@ -16051,26 +16067,26 @@
       </c>
       <c r="BS36" t="inlineStr">
         <is>
-          <t>1 sep</t>
+          <t>2 sep</t>
         </is>
       </c>
       <c r="BT36" t="n">
-        <v>127.21</v>
+        <v>126.5</v>
       </c>
       <c r="BU36" t="n">
-        <v>127.35</v>
+        <v>126.91</v>
       </c>
       <c r="BV36" t="n">
-        <v>126.26</v>
+        <v>125.92</v>
       </c>
       <c r="BW36" t="n">
-        <v>126.58</v>
+        <v>126.79</v>
       </c>
       <c r="BX36" t="n">
-        <v>126.2516</v>
+        <v>126.2926</v>
       </c>
       <c r="BY36" t="n">
-        <v>117.5762</v>
+        <v>117.6614</v>
       </c>
       <c r="CA36" t="inlineStr">
         <is>
@@ -16324,26 +16340,26 @@
       </c>
       <c r="BS37" t="inlineStr">
         <is>
-          <t>2 sep</t>
+          <t>3 sep</t>
         </is>
       </c>
       <c r="BT37" t="n">
-        <v>126.5</v>
+        <v>126.81</v>
       </c>
       <c r="BU37" t="n">
-        <v>126.91</v>
+        <v>127.88</v>
       </c>
       <c r="BV37" t="n">
-        <v>125.92</v>
+        <v>126.71</v>
       </c>
       <c r="BW37" t="n">
-        <v>126.79</v>
+        <v>127.88</v>
       </c>
       <c r="BX37" t="n">
-        <v>126.2926</v>
+        <v>126.3684</v>
       </c>
       <c r="BY37" t="n">
-        <v>117.6614</v>
+        <v>117.7593</v>
       </c>
       <c r="CA37" t="inlineStr">
         <is>
@@ -16597,26 +16613,26 @@
       </c>
       <c r="BS38" t="inlineStr">
         <is>
-          <t>3 sep</t>
+          <t>4 sep</t>
         </is>
       </c>
       <c r="BT38" t="n">
-        <v>126.81</v>
+        <v>127.75</v>
       </c>
       <c r="BU38" t="n">
-        <v>127.88</v>
+        <v>128.09</v>
       </c>
       <c r="BV38" t="n">
-        <v>126.71</v>
+        <v>127</v>
       </c>
       <c r="BW38" t="n">
-        <v>127.88</v>
+        <v>127.44</v>
       </c>
       <c r="BX38" t="n">
-        <v>126.3684</v>
+        <v>126.4426</v>
       </c>
       <c r="BY38" t="n">
-        <v>117.7593</v>
+        <v>117.8536</v>
       </c>
       <c r="CA38" t="inlineStr">
         <is>
@@ -16870,26 +16886,26 @@
       </c>
       <c r="BS39" t="inlineStr">
         <is>
-          <t>4 sep</t>
+          <t>7 sep</t>
         </is>
       </c>
       <c r="BT39" t="n">
-        <v>127.75</v>
+        <v>127.66</v>
       </c>
       <c r="BU39" t="n">
-        <v>128.09</v>
+        <v>127.7</v>
       </c>
       <c r="BV39" t="n">
-        <v>127</v>
+        <v>127.27</v>
       </c>
       <c r="BW39" t="n">
-        <v>127.44</v>
+        <v>127.33</v>
       </c>
       <c r="BX39" t="n">
-        <v>126.4426</v>
+        <v>126.5118</v>
       </c>
       <c r="BY39" t="n">
-        <v>117.8536</v>
+        <v>117.9441</v>
       </c>
       <c r="CA39" t="inlineStr">
         <is>
@@ -17143,26 +17159,26 @@
       </c>
       <c r="BS40" t="inlineStr">
         <is>
-          <t>7 sep</t>
+          <t>8 sep</t>
         </is>
       </c>
       <c r="BT40" t="n">
-        <v>127.66</v>
+        <v>127.25</v>
       </c>
       <c r="BU40" t="n">
-        <v>127.7</v>
+        <v>127.5</v>
       </c>
       <c r="BV40" t="n">
-        <v>127.27</v>
+        <v>126.95</v>
       </c>
       <c r="BW40" t="n">
-        <v>127.33</v>
+        <v>127.16</v>
       </c>
       <c r="BX40" t="n">
-        <v>126.5118</v>
+        <v>126.5524</v>
       </c>
       <c r="BY40" t="n">
-        <v>117.9441</v>
+        <v>118.0394</v>
       </c>
       <c r="CA40" t="inlineStr">
         <is>
@@ -17416,26 +17432,26 @@
       </c>
       <c r="BS41" t="inlineStr">
         <is>
-          <t>8 sep</t>
+          <t>9 sep</t>
         </is>
       </c>
       <c r="BT41" t="n">
-        <v>127.25</v>
+        <v>126.85</v>
       </c>
       <c r="BU41" t="n">
-        <v>127.5</v>
+        <v>126.93</v>
       </c>
       <c r="BV41" t="n">
-        <v>126.95</v>
+        <v>125.85</v>
       </c>
       <c r="BW41" t="n">
-        <v>127.16</v>
+        <v>126.05</v>
       </c>
       <c r="BX41" t="n">
-        <v>126.5524</v>
+        <v>126.5562</v>
       </c>
       <c r="BY41" t="n">
-        <v>118.0394</v>
+        <v>118.122</v>
       </c>
       <c r="CA41" t="inlineStr">
         <is>
@@ -17689,26 +17705,26 @@
       </c>
       <c r="BS42" t="inlineStr">
         <is>
-          <t>9 sep</t>
+          <t>10 sep</t>
         </is>
       </c>
       <c r="BT42" t="n">
-        <v>126.85</v>
+        <v>126.31</v>
       </c>
       <c r="BU42" t="n">
-        <v>126.93</v>
+        <v>126.35</v>
       </c>
       <c r="BV42" t="n">
-        <v>125.85</v>
+        <v>125.17</v>
       </c>
       <c r="BW42" t="n">
-        <v>126.05</v>
+        <v>125.44</v>
       </c>
       <c r="BX42" t="n">
-        <v>126.5562</v>
+        <v>126.5604</v>
       </c>
       <c r="BY42" t="n">
-        <v>118.122</v>
+        <v>118.2</v>
       </c>
       <c r="CA42" t="inlineStr">
         <is>
@@ -17779,7 +17795,7 @@
         <v>453.115</v>
       </c>
       <c r="G43" t="n">
-        <v>429.6539</v>
+        <v>429.654</v>
       </c>
       <c r="H43" t="n">
         <v>535.3375423278808</v>
@@ -17962,26 +17978,26 @@
       </c>
       <c r="BS43" t="inlineStr">
         <is>
-          <t>10 sep</t>
+          <t>11 sep</t>
         </is>
       </c>
       <c r="BT43" t="n">
-        <v>126.31</v>
+        <v>125.94</v>
       </c>
       <c r="BU43" t="n">
-        <v>126.35</v>
+        <v>126.81</v>
       </c>
       <c r="BV43" t="n">
-        <v>125.17</v>
+        <v>125.8</v>
       </c>
       <c r="BW43" t="n">
-        <v>125.44</v>
+        <v>126.64</v>
       </c>
       <c r="BX43" t="n">
-        <v>126.5604</v>
+        <v>126.5784</v>
       </c>
       <c r="BY43" t="n">
-        <v>118.2</v>
+        <v>118.2779</v>
       </c>
       <c r="CA43" t="inlineStr">
         <is>
@@ -18235,26 +18251,26 @@
       </c>
       <c r="BS44" t="inlineStr">
         <is>
-          <t>11 sep</t>
+          <t>14 sep</t>
         </is>
       </c>
       <c r="BT44" t="n">
-        <v>125.94</v>
+        <v>126.14</v>
       </c>
       <c r="BU44" t="n">
-        <v>126.81</v>
+        <v>126.57</v>
       </c>
       <c r="BV44" t="n">
-        <v>125.8</v>
+        <v>125.98</v>
       </c>
       <c r="BW44" t="n">
-        <v>126.64</v>
+        <v>126.43</v>
       </c>
       <c r="BX44" t="n">
-        <v>126.5784</v>
+        <v>126.58</v>
       </c>
       <c r="BY44" t="n">
-        <v>118.2779</v>
+        <v>118.3551</v>
       </c>
       <c r="CA44" t="inlineStr">
         <is>
@@ -18435,7 +18451,7 @@
         <v>1502.867</v>
       </c>
       <c r="AS45" t="n">
-        <v>1301.1272</v>
+        <v>1301.1271</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
@@ -18508,26 +18524,26 @@
       </c>
       <c r="BS45" t="inlineStr">
         <is>
-          <t>14 sep</t>
+          <t>15 sep</t>
         </is>
       </c>
       <c r="BT45" t="n">
-        <v>126.14</v>
+        <v>126.03</v>
       </c>
       <c r="BU45" t="n">
-        <v>126.57</v>
+        <v>126.34</v>
       </c>
       <c r="BV45" t="n">
-        <v>125.98</v>
+        <v>125.52</v>
       </c>
       <c r="BW45" t="n">
-        <v>126.43</v>
+        <v>125.81</v>
       </c>
       <c r="BX45" t="n">
-        <v>126.58</v>
+        <v>126.5882</v>
       </c>
       <c r="BY45" t="n">
-        <v>118.3551</v>
+        <v>118.4271</v>
       </c>
       <c r="CA45" t="inlineStr">
         <is>
@@ -18781,26 +18797,26 @@
       </c>
       <c r="BS46" t="inlineStr">
         <is>
-          <t>15 sep</t>
+          <t>16 sep</t>
         </is>
       </c>
       <c r="BT46" t="n">
-        <v>126.03</v>
+        <v>126.18</v>
       </c>
       <c r="BU46" t="n">
-        <v>126.34</v>
+        <v>126.55</v>
       </c>
       <c r="BV46" t="n">
-        <v>125.52</v>
+        <v>125.97</v>
       </c>
       <c r="BW46" t="n">
-        <v>125.81</v>
+        <v>126.47</v>
       </c>
       <c r="BX46" t="n">
-        <v>126.5882</v>
+        <v>126.6282</v>
       </c>
       <c r="BY46" t="n">
-        <v>118.4271</v>
+        <v>118.5046</v>
       </c>
       <c r="CA46" t="inlineStr">
         <is>
@@ -19054,26 +19070,26 @@
       </c>
       <c r="BS47" t="inlineStr">
         <is>
-          <t>16 sep</t>
+          <t>17 sep</t>
         </is>
       </c>
       <c r="BT47" t="n">
-        <v>126.18</v>
+        <v>127.05</v>
       </c>
       <c r="BU47" t="n">
-        <v>126.55</v>
+        <v>127.65</v>
       </c>
       <c r="BV47" t="n">
-        <v>125.97</v>
+        <v>126.94</v>
       </c>
       <c r="BW47" t="n">
-        <v>126.47</v>
+        <v>127.4</v>
       </c>
       <c r="BX47" t="n">
-        <v>126.6282</v>
+        <v>126.6618</v>
       </c>
       <c r="BY47" t="n">
-        <v>118.5046</v>
+        <v>118.5867</v>
       </c>
       <c r="CA47" t="inlineStr">
         <is>
@@ -19327,26 +19343,26 @@
       </c>
       <c r="BS48" t="inlineStr">
         <is>
-          <t>17 sep</t>
+          <t>18 sep</t>
         </is>
       </c>
       <c r="BT48" t="n">
+        <v>127.69</v>
+      </c>
+      <c r="BU48" t="n">
+        <v>127.78</v>
+      </c>
+      <c r="BV48" t="n">
+        <v>126.9</v>
+      </c>
+      <c r="BW48" t="n">
         <v>127.05</v>
       </c>
-      <c r="BU48" t="n">
-        <v>127.65</v>
-      </c>
-      <c r="BV48" t="n">
-        <v>126.94</v>
-      </c>
-      <c r="BW48" t="n">
-        <v>127.4</v>
-      </c>
       <c r="BX48" t="n">
-        <v>126.6618</v>
+        <v>126.6798</v>
       </c>
       <c r="BY48" t="n">
-        <v>118.5867</v>
+        <v>118.6667</v>
       </c>
       <c r="CA48" t="inlineStr">
         <is>
@@ -19600,26 +19616,26 @@
       </c>
       <c r="BS49" t="inlineStr">
         <is>
-          <t>18 sep</t>
+          <t>21 sep</t>
         </is>
       </c>
       <c r="BT49" t="n">
-        <v>127.69</v>
+        <v>127.98</v>
       </c>
       <c r="BU49" t="n">
-        <v>127.78</v>
+        <v>128.65</v>
       </c>
       <c r="BV49" t="n">
-        <v>126.9</v>
+        <v>127.89</v>
       </c>
       <c r="BW49" t="n">
-        <v>127.05</v>
+        <v>128.62</v>
       </c>
       <c r="BX49" t="n">
-        <v>126.6798</v>
+        <v>126.7256</v>
       </c>
       <c r="BY49" t="n">
-        <v>118.6667</v>
+        <v>118.7534</v>
       </c>
       <c r="CA49" t="inlineStr">
         <is>
@@ -19873,26 +19889,26 @@
       </c>
       <c r="BS50" t="inlineStr">
         <is>
-          <t>21 sep</t>
+          <t>22 sep</t>
         </is>
       </c>
       <c r="BT50" t="n">
-        <v>127.98</v>
+        <v>129.21</v>
       </c>
       <c r="BU50" t="n">
-        <v>128.65</v>
+        <v>129.55</v>
       </c>
       <c r="BV50" t="n">
-        <v>127.89</v>
+        <v>129</v>
       </c>
       <c r="BW50" t="n">
-        <v>128.62</v>
+        <v>129.38</v>
       </c>
       <c r="BX50" t="n">
-        <v>126.7256</v>
+        <v>126.7914</v>
       </c>
       <c r="BY50" t="n">
-        <v>118.7534</v>
+        <v>118.8419</v>
       </c>
       <c r="CA50" t="inlineStr">
         <is>
@@ -20146,26 +20162,26 @@
       </c>
       <c r="BS51" t="inlineStr">
         <is>
-          <t>22 sep</t>
+          <t>23 sep</t>
         </is>
       </c>
       <c r="BT51" t="n">
-        <v>129.21</v>
+        <v>129.76</v>
       </c>
       <c r="BU51" t="n">
-        <v>129.55</v>
+        <v>129.83</v>
       </c>
       <c r="BV51" t="n">
-        <v>129</v>
+        <v>129.04</v>
       </c>
       <c r="BW51" t="n">
-        <v>129.38</v>
+        <v>129.1</v>
       </c>
       <c r="BX51" t="n">
-        <v>126.7914</v>
+        <v>126.8476</v>
       </c>
       <c r="BY51" t="n">
-        <v>118.8419</v>
+        <v>118.9298</v>
       </c>
       <c r="CA51" t="inlineStr">
         <is>
@@ -20419,26 +20435,26 @@
       </c>
       <c r="BS52" t="inlineStr">
         <is>
-          <t>23 sep</t>
+          <t>24 sep</t>
         </is>
       </c>
       <c r="BT52" t="n">
-        <v>129.76</v>
+        <v>128.26</v>
       </c>
       <c r="BU52" t="n">
-        <v>129.83</v>
+        <v>128.77</v>
       </c>
       <c r="BV52" t="n">
-        <v>129.04</v>
+        <v>128.03</v>
       </c>
       <c r="BW52" t="n">
-        <v>129.1</v>
+        <v>128.37</v>
       </c>
       <c r="BX52" t="n">
-        <v>126.8476</v>
+        <v>126.8898</v>
       </c>
       <c r="BY52" t="n">
-        <v>118.9298</v>
+        <v>119.0135</v>
       </c>
       <c r="CA52" t="inlineStr">
         <is>
@@ -20692,26 +20708,26 @@
       </c>
       <c r="BS53" t="inlineStr">
         <is>
-          <t>24 sep</t>
+          <t>25 sep</t>
         </is>
       </c>
       <c r="BT53" t="n">
-        <v>128.26</v>
+        <v>129.11</v>
       </c>
       <c r="BU53" t="n">
-        <v>128.77</v>
+        <v>129.3</v>
       </c>
       <c r="BV53" t="n">
-        <v>128.03</v>
+        <v>128.49</v>
       </c>
       <c r="BW53" t="n">
-        <v>128.37</v>
+        <v>128.91</v>
       </c>
       <c r="BX53" t="n">
-        <v>126.8898</v>
+        <v>126.971</v>
       </c>
       <c r="BY53" t="n">
-        <v>119.0135</v>
+        <v>119.1011</v>
       </c>
       <c r="CA53" t="inlineStr">
         <is>
@@ -20965,26 +20981,26 @@
       </c>
       <c r="BS54" t="inlineStr">
         <is>
-          <t>25 sep</t>
+          <t>28 sep</t>
         </is>
       </c>
       <c r="BT54" t="n">
-        <v>129.11</v>
+        <v>129.02</v>
       </c>
       <c r="BU54" t="n">
-        <v>129.3</v>
+        <v>129.26</v>
       </c>
       <c r="BV54" t="n">
-        <v>128.49</v>
+        <v>128.54</v>
       </c>
       <c r="BW54" t="n">
-        <v>128.91</v>
+        <v>128.57</v>
       </c>
       <c r="BX54" t="n">
-        <v>126.971</v>
+        <v>127.0372</v>
       </c>
       <c r="BY54" t="n">
-        <v>119.1011</v>
+        <v>119.1891</v>
       </c>
       <c r="CA54" t="inlineStr">
         <is>
@@ -21238,26 +21254,26 @@
       </c>
       <c r="BS55" t="inlineStr">
         <is>
-          <t>28 sep</t>
+          <t>29 sep</t>
         </is>
       </c>
       <c r="BT55" t="n">
-        <v>129.02</v>
+        <v>128.72</v>
       </c>
       <c r="BU55" t="n">
-        <v>129.26</v>
+        <v>129.27</v>
       </c>
       <c r="BV55" t="n">
-        <v>128.54</v>
+        <v>128.55</v>
       </c>
       <c r="BW55" t="n">
-        <v>128.57</v>
+        <v>128.7</v>
       </c>
       <c r="BX55" t="n">
-        <v>127.0372</v>
+        <v>127.0962</v>
       </c>
       <c r="BY55" t="n">
-        <v>119.1891</v>
+        <v>119.2811</v>
       </c>
       <c r="CA55" t="inlineStr">
         <is>
@@ -21438,7 +21454,7 @@
         <v>1490.0724</v>
       </c>
       <c r="AS56" t="n">
-        <v>1332.1048</v>
+        <v>1332.1047</v>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
@@ -21511,26 +21527,26 @@
       </c>
       <c r="BS56" t="inlineStr">
         <is>
-          <t>29 sep</t>
+          <t>30 sep</t>
         </is>
       </c>
       <c r="BT56" t="n">
-        <v>128.72</v>
+        <v>129.08</v>
       </c>
       <c r="BU56" t="n">
-        <v>129.27</v>
+        <v>129.4</v>
       </c>
       <c r="BV56" t="n">
-        <v>128.55</v>
+        <v>128.57</v>
       </c>
       <c r="BW56" t="n">
-        <v>128.7</v>
+        <v>129.15</v>
       </c>
       <c r="BX56" t="n">
-        <v>127.0962</v>
+        <v>127.1586</v>
       </c>
       <c r="BY56" t="n">
-        <v>119.2811</v>
+        <v>119.3744</v>
       </c>
       <c r="CA56" t="inlineStr">
         <is>
@@ -21784,26 +21800,26 @@
       </c>
       <c r="BS57" t="inlineStr">
         <is>
-          <t>30 sep</t>
+          <t>1 okt</t>
         </is>
       </c>
       <c r="BT57" t="n">
-        <v>129.08</v>
+        <v>129.07</v>
       </c>
       <c r="BU57" t="n">
         <v>129.4</v>
       </c>
       <c r="BV57" t="n">
-        <v>128.57</v>
+        <v>128.31</v>
       </c>
       <c r="BW57" t="n">
-        <v>129.15</v>
+        <v>128.81</v>
       </c>
       <c r="BX57" t="n">
-        <v>127.1586</v>
+        <v>127.2468</v>
       </c>
       <c r="BY57" t="n">
-        <v>119.3744</v>
+        <v>119.4698</v>
       </c>
       <c r="CA57" t="inlineStr">
         <is>
@@ -22057,26 +22073,26 @@
       </c>
       <c r="BS58" t="inlineStr">
         <is>
-          <t>1 okt</t>
+          <t>2 okt</t>
         </is>
       </c>
       <c r="BT58" t="n">
-        <v>129.07</v>
+        <v>129.53</v>
       </c>
       <c r="BU58" t="n">
-        <v>129.4</v>
+        <v>130.55</v>
       </c>
       <c r="BV58" t="n">
-        <v>128.31</v>
+        <v>129.43</v>
       </c>
       <c r="BW58" t="n">
-        <v>128.81</v>
+        <v>130.05</v>
       </c>
       <c r="BX58" t="n">
-        <v>127.2468</v>
+        <v>127.3426</v>
       </c>
       <c r="BY58" t="n">
-        <v>119.4698</v>
+        <v>119.5736</v>
       </c>
       <c r="CA58" t="inlineStr">
         <is>
@@ -22330,26 +22346,26 @@
       </c>
       <c r="BS59" t="inlineStr">
         <is>
-          <t>2 okt</t>
+          <t>5 okt</t>
         </is>
       </c>
       <c r="BT59" t="n">
-        <v>129.53</v>
+        <v>130.86</v>
       </c>
       <c r="BU59" t="n">
-        <v>130.55</v>
+        <v>131.42</v>
       </c>
       <c r="BV59" t="n">
-        <v>129.43</v>
+        <v>130.48</v>
       </c>
       <c r="BW59" t="n">
-        <v>130.05</v>
+        <v>131.18</v>
       </c>
       <c r="BX59" t="n">
-        <v>127.3426</v>
+        <v>127.4712</v>
       </c>
       <c r="BY59" t="n">
-        <v>119.5736</v>
+        <v>119.6774</v>
       </c>
       <c r="CA59" t="inlineStr">
         <is>
@@ -22603,26 +22619,26 @@
       </c>
       <c r="BS60" t="inlineStr">
         <is>
-          <t>5 okt</t>
+          <t>6 okt</t>
         </is>
       </c>
       <c r="BT60" t="n">
-        <v>130.86</v>
+        <v>131.69</v>
       </c>
       <c r="BU60" t="n">
-        <v>131.42</v>
+        <v>131.94</v>
       </c>
       <c r="BV60" t="n">
-        <v>130.48</v>
+        <v>131.41</v>
       </c>
       <c r="BW60" t="n">
-        <v>131.18</v>
+        <v>131.87</v>
       </c>
       <c r="BX60" t="n">
-        <v>127.4712</v>
+        <v>127.605</v>
       </c>
       <c r="BY60" t="n">
-        <v>119.6774</v>
+        <v>119.782</v>
       </c>
       <c r="CA60" t="inlineStr">
         <is>
@@ -22876,26 +22892,26 @@
       </c>
       <c r="BS61" t="inlineStr">
         <is>
-          <t>6 okt</t>
+          <t>7 okt</t>
         </is>
       </c>
       <c r="BT61" t="n">
-        <v>131.69</v>
+        <v>131.82</v>
       </c>
       <c r="BU61" t="n">
-        <v>131.94</v>
+        <v>132.32</v>
       </c>
       <c r="BV61" t="n">
-        <v>131.41</v>
+        <v>131.18</v>
       </c>
       <c r="BW61" t="n">
-        <v>131.87</v>
+        <v>131.45</v>
       </c>
       <c r="BX61" t="n">
-        <v>127.605</v>
+        <v>127.7474</v>
       </c>
       <c r="BY61" t="n">
-        <v>119.782</v>
+        <v>119.8834</v>
       </c>
       <c r="CA61" t="inlineStr">
         <is>
@@ -23149,26 +23165,26 @@
       </c>
       <c r="BS62" t="inlineStr">
         <is>
-          <t>7 okt</t>
+          <t>8 okt</t>
         </is>
       </c>
       <c r="BT62" t="n">
-        <v>131.82</v>
+        <v>130.99</v>
       </c>
       <c r="BU62" t="n">
-        <v>132.32</v>
+        <v>131.39</v>
       </c>
       <c r="BV62" t="n">
-        <v>131.18</v>
+        <v>130.81</v>
       </c>
       <c r="BW62" t="n">
-        <v>131.45</v>
+        <v>130.98</v>
       </c>
       <c r="BX62" t="n">
-        <v>127.7474</v>
+        <v>127.8932</v>
       </c>
       <c r="BY62" t="n">
-        <v>119.8834</v>
+        <v>119.9813</v>
       </c>
       <c r="CA62" t="inlineStr">
         <is>
@@ -23422,26 +23438,26 @@
       </c>
       <c r="BS63" t="inlineStr">
         <is>
-          <t>8 okt</t>
+          <t>9 okt</t>
         </is>
       </c>
       <c r="BT63" t="n">
-        <v>130.99</v>
+        <v>131.19</v>
       </c>
       <c r="BU63" t="n">
-        <v>131.39</v>
+        <v>131.73</v>
       </c>
       <c r="BV63" t="n">
-        <v>130.81</v>
+        <v>131.14</v>
       </c>
       <c r="BW63" t="n">
-        <v>130.98</v>
+        <v>131.67</v>
       </c>
       <c r="BX63" t="n">
-        <v>127.8932</v>
+        <v>128.042</v>
       </c>
       <c r="BY63" t="n">
-        <v>119.9813</v>
+        <v>120.0822</v>
       </c>
       <c r="CA63" t="inlineStr">
         <is>
@@ -23695,26 +23711,26 @@
       </c>
       <c r="BS64" t="inlineStr">
         <is>
-          <t>9 okt</t>
+          <t>12 okt</t>
         </is>
       </c>
       <c r="BT64" t="n">
-        <v>131.19</v>
+        <v>132.12</v>
       </c>
       <c r="BU64" t="n">
-        <v>131.73</v>
+        <v>132.32</v>
       </c>
       <c r="BV64" t="n">
-        <v>131.14</v>
+        <v>132.04</v>
       </c>
       <c r="BW64" t="n">
-        <v>131.67</v>
+        <v>132.26</v>
       </c>
       <c r="BX64" t="n">
-        <v>128.042</v>
+        <v>128.1648</v>
       </c>
       <c r="BY64" t="n">
-        <v>120.0822</v>
+        <v>120.1856</v>
       </c>
       <c r="CA64" t="inlineStr">
         <is>
@@ -23968,26 +23984,26 @@
       </c>
       <c r="BS65" t="inlineStr">
         <is>
-          <t>12 okt</t>
+          <t>13 okt</t>
         </is>
       </c>
       <c r="BT65" t="n">
-        <v>132.12</v>
+        <v>132.04</v>
       </c>
       <c r="BU65" t="n">
-        <v>132.32</v>
+        <v>132.4</v>
       </c>
       <c r="BV65" t="n">
-        <v>132.04</v>
+        <v>131.71</v>
       </c>
       <c r="BW65" t="n">
-        <v>132.26</v>
+        <v>131.73</v>
       </c>
       <c r="BX65" t="n">
-        <v>128.1648</v>
+        <v>128.2434</v>
       </c>
       <c r="BY65" t="n">
-        <v>120.1856</v>
+        <v>120.2853</v>
       </c>
       <c r="CA65" t="inlineStr">
         <is>
@@ -24185,13 +24201,13 @@
         <v>81469.35159999999</v>
       </c>
       <c r="AY66" t="n">
-        <v>81822.75780000001</v>
+        <v>81779.10159999999</v>
       </c>
       <c r="AZ66" t="n">
-        <v>81169.9184</v>
+        <v>81169.0453</v>
       </c>
       <c r="BA66" t="n">
-        <v>72206.2684</v>
+        <v>72206.0502</v>
       </c>
       <c r="BC66" t="inlineStr">
         <is>
@@ -24208,13 +24224,13 @@
         <v>2408.7908</v>
       </c>
       <c r="BG66" t="n">
-        <v>2423.8</v>
+        <v>2422.78</v>
       </c>
       <c r="BH66" t="n">
-        <v>2555.6857</v>
+        <v>2555.6653</v>
       </c>
       <c r="BI66" t="n">
-        <v>2140.4752</v>
+        <v>2140.4701</v>
       </c>
       <c r="BK66" t="inlineStr">
         <is>
@@ -24257,10 +24273,10 @@
         <v>131.81</v>
       </c>
       <c r="BX66" t="n">
-        <v>128.245</v>
+        <v>128.3144</v>
       </c>
       <c r="BY66" t="n">
-        <v>120.2857</v>
+        <v>120.3867</v>
       </c>
       <c r="CA66" t="inlineStr">
         <is>
@@ -24274,7 +24290,7 @@
         <v>949.42</v>
       </c>
       <c r="CD66" t="n">
-        <v>913.65</v>
+        <v>913.6</v>
       </c>
       <c r="CE66" t="n">
         <v>914.13</v>
@@ -24320,1035 +24336,290 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:B327"/>
+  <dimension ref="B1:D137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="135" customWidth="1" min="2" max="2"/>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="84" customWidth="1" min="2" max="2"/>
+    <col width="3" customWidth="1" min="3" max="3"/>
+    <col width="84" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="B1" s="22" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Grafieken van vandaag</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="50" customHeight="1">
-      <c r="B2" s="26" t="inlineStr">
-        <is>
-          <t>Scroll naar beneden: alle grafieken staan onder elkaar. Elke kaars is één handelsdag: groen = die dag gestegen, rood = die dag gedaald; de dunne streep is de hoogste en laagste koers. Blauwe lijn = gemiddelde van 50 dagen, oranje = van 200 dagen, grijze stippellijn = instap, rode stippellijn = stop-loss (daar verkoopt de bot). Ga met de muis over een kaars of lijn voor de waarde.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="24" customHeight="1">
-      <c r="B4" s="27" t="inlineStr">
-        <is>
-          <t>1. Hoeveel zijn de bots waard?</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="28" t="inlineStr">
-        <is>
-          <t>Boven €10.000 = winst, eronder = verlies. De grijze stippellijn is wat je had gehad met gewoon de wereld-ETF kopen en vasthouden.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="24" customHeight="1">
-      <c r="B32" s="27" t="inlineStr">
-        <is>
-          <t>2. Microsoft (MSFT)  ·  533,69 USD</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="28" t="inlineStr">
-        <is>
-          <t>Gestegen: 35,2% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="28" t="inlineStr">
-        <is>
-          <t>Sinds de bot kocht: -0,3% (verlies). De bot verkoopt als de koers onder 509,90 zakt (-4,5%).</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" t="inlineStr">
+    <row r="2" ht="20" customHeight="1">
+      <c r="B2" t="inlineStr">
         <is>
           <r>
             <rPr>
               <b val="1"/>
               <color rgb="00008300"/>
-              <sz val="11"/>
+              <sz val="12"/>
             </rPr>
             <t>▮ groen</t>
           </r>
           <r>
             <rPr>
               <color rgb="0052514E"/>
-              <sz val="11"/>
+              <sz val="12"/>
             </rPr>
-            <t xml:space="preserve"> = dag gestegen   </t>
+            <t xml:space="preserve"> = dag gestegen    </t>
           </r>
           <r>
             <rPr>
               <b val="1"/>
               <color rgb="00E34948"/>
-              <sz val="11"/>
+              <sz val="12"/>
             </rPr>
             <t>▮ rood</t>
           </r>
           <r>
             <rPr>
               <color rgb="0052514E"/>
-              <sz val="11"/>
+              <sz val="12"/>
             </rPr>
-            <t xml:space="preserve"> = dag gedaald   </t>
+            <t xml:space="preserve"> = dag gedaald    </t>
           </r>
           <r>
             <rPr>
               <b val="1"/>
               <color rgb="002A78D6"/>
-              <sz val="11"/>
+              <sz val="12"/>
             </rPr>
             <t>━ blauw</t>
           </r>
           <r>
             <rPr>
               <color rgb="0052514E"/>
-              <sz val="11"/>
+              <sz val="12"/>
             </rPr>
-            <t xml:space="preserve"> = gemiddelde 50 dagen   </t>
+            <t xml:space="preserve"> = gemiddelde 50 dagen    </t>
           </r>
           <r>
             <rPr>
               <b val="1"/>
               <color rgb="00EB6834"/>
-              <sz val="11"/>
+              <sz val="12"/>
             </rPr>
             <t>━ oranje</t>
           </r>
           <r>
             <rPr>
               <color rgb="0052514E"/>
-              <sz val="11"/>
+              <sz val="12"/>
             </rPr>
-            <t xml:space="preserve"> = gemiddelde 200 dagen   </t>
+            <t xml:space="preserve"> = gemiddelde 200 dagen    </t>
           </r>
           <r>
             <rPr>
               <b val="1"/>
               <color rgb="0052514E"/>
-              <sz val="11"/>
+              <sz val="12"/>
             </rPr>
             <t>╌ grijs</t>
           </r>
           <r>
             <rPr>
               <color rgb="0052514E"/>
-              <sz val="11"/>
+              <sz val="12"/>
             </rPr>
-            <t xml:space="preserve"> = instap   </t>
+            <t xml:space="preserve"> = instap    </t>
           </r>
           <r>
             <rPr>
               <b val="1"/>
               <color rgb="00E34948"/>
-              <sz val="11"/>
+              <sz val="12"/>
             </rPr>
             <t>╌ rood</t>
           </r>
           <r>
             <rPr>
               <color rgb="0052514E"/>
-              <sz val="11"/>
+              <sz val="12"/>
             </rPr>
             <t xml:space="preserve"> = stop-loss, hier verkoopt de bot</t>
           </r>
         </is>
       </c>
     </row>
-    <row r="62" ht="24" customHeight="1">
-      <c r="B62" s="27" t="inlineStr">
-        <is>
-          <t>3. SAP (SAP.DE)  ·  196,94 EUR</t>
+    <row r="3">
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>Elke kaars is één handelsdag; het dunne streepje loopt van de laagste naar de hoogste koers van die dag. Ga met de muis over een kaars of lijn om de waarde te zien.</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="B63" s="28" t="inlineStr">
-        <is>
-          <t>Gestegen: 43,1% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden.</t>
+    <row r="5" ht="22" customHeight="1">
+      <c r="B5" s="27" t="inlineStr">
+        <is>
+          <t>Hoeveel zijn de bots waard?</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="B64" s="28" t="inlineStr">
-        <is>
-          <t>Sinds de bot kocht: +2,8% (winst). De bot verkoopt als de koers onder 181,04 zakt (-8,1%).</t>
+    <row r="6" ht="20" customHeight="1">
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>Boven €10.000 = winst, eronder = verlies. De grijze stippellijn is wat je had gehad met gewoon de wereld-ETF kopen en vasthouden.</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="B65" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00008300"/>
-              <sz val="11"/>
-            </rPr>
-            <t>▮ groen</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = dag gestegen   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00E34948"/>
-              <sz val="11"/>
-            </rPr>
-            <t>▮ rood</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = dag gedaald   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="002A78D6"/>
-              <sz val="11"/>
-            </rPr>
-            <t>━ blauw</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = gemiddelde 50 dagen   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00EB6834"/>
-              <sz val="11"/>
-            </rPr>
-            <t>━ oranje</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = gemiddelde 200 dagen   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t>╌ grijs</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = instap   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00E34948"/>
-              <sz val="11"/>
-            </rPr>
-            <t>╌ rood</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = stop-loss, hier verkoopt de bot</t>
-          </r>
+    <row r="28" ht="26" customHeight="1">
+      <c r="B28" s="29" t="inlineStr">
+        <is>
+          <t>Trend-agent: open posities</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="24" customHeight="1">
-      <c r="B92" s="27" t="inlineStr">
-        <is>
-          <t>4. Shell (SHELL.AS)  ·  46,46 EUR</t>
+    <row r="29" ht="22" customHeight="1">
+      <c r="B29" s="27" t="inlineStr">
+        <is>
+          <t>Microsoft (MSFT)  ·  533,69 USD</t>
+        </is>
+      </c>
+      <c r="D29" s="27" t="inlineStr">
+        <is>
+          <t>SAP (SAP.DE)  ·  196,94 EUR</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="B93" s="28" t="inlineStr">
-        <is>
-          <t>Gestegen: 26,0% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden.</t>
+    <row r="30" ht="30" customHeight="1">
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>Gestegen: 35,2% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: -0,3% (verlies). De bot verkoopt als de koers onder 509,90 zakt (-4,5%).</t>
+        </is>
+      </c>
+      <c r="D30" s="30" t="inlineStr">
+        <is>
+          <t>Gestegen: 43,1% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +2,8% (winst). De bot verkoopt als de koers onder 181,04 zakt (-8,1%).</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="B94" s="28" t="inlineStr">
-        <is>
-          <t>Sinds de bot kocht: +3,1% (winst). De bot verkoopt als de koers onder 43,73 zakt (-5,9%).</t>
+    <row r="50" ht="22" customHeight="1">
+      <c r="B50" s="27" t="inlineStr">
+        <is>
+          <t>Shell (SHELL.AS)  ·  46,46 EUR</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="B95" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00008300"/>
-              <sz val="11"/>
-            </rPr>
-            <t>▮ groen</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = dag gestegen   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00E34948"/>
-              <sz val="11"/>
-            </rPr>
-            <t>▮ rood</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = dag gedaald   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="002A78D6"/>
-              <sz val="11"/>
-            </rPr>
-            <t>━ blauw</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = gemiddelde 50 dagen   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00EB6834"/>
-              <sz val="11"/>
-            </rPr>
-            <t>━ oranje</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = gemiddelde 200 dagen   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t>╌ grijs</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = instap   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00E34948"/>
-              <sz val="11"/>
-            </rPr>
-            <t>╌ rood</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = stop-loss, hier verkoopt de bot</t>
-          </r>
+    <row r="51" ht="30" customHeight="1">
+      <c r="B51" s="30" t="inlineStr">
+        <is>
+          <t>Gestegen: 26,0% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +3,1% (winst). De bot verkoopt als de koers onder 43,73 zakt (-5,9%).</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="24" customHeight="1">
-      <c r="B122" s="27" t="inlineStr">
-        <is>
-          <t>5. AMD (AMD)  ·  570,82 USD</t>
+    <row r="72" ht="26" customHeight="1">
+      <c r="B72" s="29" t="inlineStr">
+        <is>
+          <t>Investeerder: beleggingen</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="B123" s="28" t="inlineStr">
+    <row r="73" ht="22" customHeight="1">
+      <c r="B73" s="27" t="inlineStr">
+        <is>
+          <t>AMD (AMD)  ·  570,82 USD</t>
+        </is>
+      </c>
+      <c r="D73" s="27" t="inlineStr">
+        <is>
+          <t>ASML (ASML.AS)  ·  1.528,20 EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="30" customHeight="1">
+      <c r="B74" s="30" t="inlineStr">
         <is>
           <t>Gestegen: 7,9% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden.</t>
         </is>
       </c>
+      <c r="D74" s="30" t="inlineStr">
+        <is>
+          <t>Gedaald: -4,3% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden.</t>
+        </is>
+      </c>
     </row>
-    <row r="124">
-      <c r="B124" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00008300"/>
-              <sz val="11"/>
-            </rPr>
-            <t>▮ groen</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = dag gestegen   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00E34948"/>
-              <sz val="11"/>
-            </rPr>
-            <t>▮ rood</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = dag gedaald   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="002A78D6"/>
-              <sz val="11"/>
-            </rPr>
-            <t>━ blauw</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = gemiddelde 50 dagen   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00EB6834"/>
-              <sz val="11"/>
-            </rPr>
-            <t>━ oranje</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = gemiddelde 200 dagen   </t>
-          </r>
+    <row r="94" ht="22" customHeight="1">
+      <c r="B94" s="27" t="inlineStr">
+        <is>
+          <t>Bitcoin (BTC-USD)  ·  81.779,10 USD</t>
+        </is>
+      </c>
+      <c r="D94" s="27" t="inlineStr">
+        <is>
+          <t>Ethereum (ETH-USD)  ·  2.422,78 USD</t>
         </is>
       </c>
     </row>
-    <row r="151" ht="24" customHeight="1">
-      <c r="B151" s="27" t="inlineStr">
-        <is>
-          <t>6. ASML (ASML.AS)  ·  1.528,20 EUR</t>
+    <row r="95" ht="30" customHeight="1">
+      <c r="B95" s="30" t="inlineStr">
+        <is>
+          <t>Gestegen: 28,7% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden.</t>
+        </is>
+      </c>
+      <c r="D95" s="30" t="inlineStr">
+        <is>
+          <t>Gestegen: 28,8% in de laatste 3 maanden. Trend verzwakt: de koers is onder het 50-daags gemiddelde gezakt.</t>
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="B152" s="28" t="inlineStr">
-        <is>
-          <t>Gedaald: -4,3% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden.</t>
+    <row r="115" ht="22" customHeight="1">
+      <c r="B115" s="27" t="inlineStr">
+        <is>
+          <t>Infineon (IFX.DE)  ·  55,35 EUR</t>
+        </is>
+      </c>
+      <c r="D115" s="27" t="inlineStr">
+        <is>
+          <t>iShares MSCI World (IWDA.AS)  ·  131,81 EUR</t>
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="B153" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00008300"/>
-              <sz val="11"/>
-            </rPr>
-            <t>▮ groen</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = dag gestegen   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00E34948"/>
-              <sz val="11"/>
-            </rPr>
-            <t>▮ rood</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = dag gedaald   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="002A78D6"/>
-              <sz val="11"/>
-            </rPr>
-            <t>━ blauw</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = gemiddelde 50 dagen   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00EB6834"/>
-              <sz val="11"/>
-            </rPr>
-            <t>━ oranje</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = gemiddelde 200 dagen   </t>
-          </r>
+    <row r="116" ht="30" customHeight="1">
+      <c r="B116" s="30" t="inlineStr">
+        <is>
+          <t>Gedaald: -14,5% in de laatste 3 maanden. Trend verzwakt: de koers is onder het 50-daags gemiddelde gezakt.</t>
+        </is>
+      </c>
+      <c r="D116" s="30" t="inlineStr">
+        <is>
+          <t>Gestegen: 4,4% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden.</t>
         </is>
       </c>
     </row>
-    <row r="180" ht="24" customHeight="1">
-      <c r="B180" s="27" t="inlineStr">
-        <is>
-          <t>7. Bitcoin (BTC-USD)  ·  81.822,76 USD</t>
+    <row r="136" ht="22" customHeight="1">
+      <c r="B136" s="27" t="inlineStr">
+        <is>
+          <t>Micron (MU)  ·  914,13 USD</t>
+        </is>
+      </c>
+      <c r="D136" s="27" t="inlineStr">
+        <is>
+          <t>Halfgeleider-ETF (SMH)  ·  564,74 USD</t>
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="B181" s="28" t="inlineStr">
-        <is>
-          <t>Gestegen: 28,7% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden.</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="B182" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00008300"/>
-              <sz val="11"/>
-            </rPr>
-            <t>▮ groen</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = dag gestegen   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00E34948"/>
-              <sz val="11"/>
-            </rPr>
-            <t>▮ rood</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = dag gedaald   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="002A78D6"/>
-              <sz val="11"/>
-            </rPr>
-            <t>━ blauw</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = gemiddelde 50 dagen   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00EB6834"/>
-              <sz val="11"/>
-            </rPr>
-            <t>━ oranje</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = gemiddelde 200 dagen   </t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="209" ht="24" customHeight="1">
-      <c r="B209" s="27" t="inlineStr">
-        <is>
-          <t>8. Ethereum (ETH-USD)  ·  2.423,80 USD</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="B210" s="28" t="inlineStr">
-        <is>
-          <t>Gestegen: 28,8% in de laatste 3 maanden. Trend verzwakt: de koers is onder het 50-daags gemiddelde gezakt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="B211" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00008300"/>
-              <sz val="11"/>
-            </rPr>
-            <t>▮ groen</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = dag gestegen   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00E34948"/>
-              <sz val="11"/>
-            </rPr>
-            <t>▮ rood</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = dag gedaald   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="002A78D6"/>
-              <sz val="11"/>
-            </rPr>
-            <t>━ blauw</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = gemiddelde 50 dagen   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00EB6834"/>
-              <sz val="11"/>
-            </rPr>
-            <t>━ oranje</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = gemiddelde 200 dagen   </t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="238" ht="24" customHeight="1">
-      <c r="B238" s="27" t="inlineStr">
-        <is>
-          <t>9. Infineon (IFX.DE)  ·  55,35 EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="B239" s="28" t="inlineStr">
-        <is>
-          <t>Gedaald: -14,5% in de laatste 3 maanden. Trend verzwakt: de koers is onder het 50-daags gemiddelde gezakt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="B240" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00008300"/>
-              <sz val="11"/>
-            </rPr>
-            <t>▮ groen</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = dag gestegen   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00E34948"/>
-              <sz val="11"/>
-            </rPr>
-            <t>▮ rood</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = dag gedaald   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="002A78D6"/>
-              <sz val="11"/>
-            </rPr>
-            <t>━ blauw</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = gemiddelde 50 dagen   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00EB6834"/>
-              <sz val="11"/>
-            </rPr>
-            <t>━ oranje</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = gemiddelde 200 dagen   </t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="267" ht="24" customHeight="1">
-      <c r="B267" s="27" t="inlineStr">
-        <is>
-          <t>10. iShares MSCI World (IWDA.AS)  ·  131,81 EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="B268" s="28" t="inlineStr">
-        <is>
-          <t>Gestegen: 4,4% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden.</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="B269" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00008300"/>
-              <sz val="11"/>
-            </rPr>
-            <t>▮ groen</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = dag gestegen   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00E34948"/>
-              <sz val="11"/>
-            </rPr>
-            <t>▮ rood</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = dag gedaald   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="002A78D6"/>
-              <sz val="11"/>
-            </rPr>
-            <t>━ blauw</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = gemiddelde 50 dagen   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00EB6834"/>
-              <sz val="11"/>
-            </rPr>
-            <t>━ oranje</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = gemiddelde 200 dagen   </t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="296" ht="24" customHeight="1">
-      <c r="B296" s="27" t="inlineStr">
-        <is>
-          <t>11. Micron (MU)  ·  914,13 USD</t>
-        </is>
-      </c>
-    </row>
-    <row r="297">
-      <c r="B297" s="28" t="inlineStr">
+    <row r="137" ht="30" customHeight="1">
+      <c r="B137" s="30" t="inlineStr">
         <is>
           <t>Gestegen: 1,1% in de laatste 3 maanden. Trend verzwakt: de koers is onder het 50-daags gemiddelde gezakt.</t>
         </is>
       </c>
-    </row>
-    <row r="298">
-      <c r="B298" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00008300"/>
-              <sz val="11"/>
-            </rPr>
-            <t>▮ groen</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = dag gestegen   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00E34948"/>
-              <sz val="11"/>
-            </rPr>
-            <t>▮ rood</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = dag gedaald   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="002A78D6"/>
-              <sz val="11"/>
-            </rPr>
-            <t>━ blauw</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = gemiddelde 50 dagen   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00EB6834"/>
-              <sz val="11"/>
-            </rPr>
-            <t>━ oranje</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = gemiddelde 200 dagen   </t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="325" ht="24" customHeight="1">
-      <c r="B325" s="27" t="inlineStr">
-        <is>
-          <t>12. Halfgeleider-ETF (SMH)  ·  564,74 USD</t>
-        </is>
-      </c>
-    </row>
-    <row r="326">
-      <c r="B326" s="28" t="inlineStr">
+      <c r="D137" s="30" t="inlineStr">
         <is>
           <t>Gedaald: -4,4% in de laatste 3 maanden. Trend verzwakt: de koers is onder het 50-daags gemiddelde gezakt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="327">
-      <c r="B327" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00008300"/>
-              <sz val="11"/>
-            </rPr>
-            <t>▮ groen</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = dag gestegen   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00E34948"/>
-              <sz val="11"/>
-            </rPr>
-            <t>▮ rood</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = dag gedaald   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="002A78D6"/>
-              <sz val="11"/>
-            </rPr>
-            <t>━ blauw</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = gemiddelde 50 dagen   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00EB6834"/>
-              <sz val="11"/>
-            </rPr>
-            <t>━ oranje</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = gemiddelde 200 dagen   </t>
-          </r>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -25397,7 +24668,7 @@
       </c>
       <c r="C2" s="16" t="inlineStr">
         <is>
-          <t>koers 131,81, 9,6% boven het 200-daags gemiddelde (120,29); de afgelopen maand +4,3%. Trend: stijgend.</t>
+          <t>koers 131,81, 9,5% boven het 200-daags gemiddelde (120,39); de afgelopen maand +4,8%. Trend: stijgend.</t>
         </is>
       </c>
     </row>
@@ -25533,7 +24804,7 @@
       </c>
       <c r="C10" s="16" t="inlineStr">
         <is>
-          <t>koers 131,81, 9,6% boven het 200-daags gemiddelde (120,29); de afgelopen maand +4,3%. Trend: stijgend.</t>
+          <t>koers 131,81, 9,5% boven het 200-daags gemiddelde (120,39); de afgelopen maand +4,8%. Trend: stijgend.</t>
         </is>
       </c>
     </row>
@@ -25998,16 +25269,16 @@
         </is>
       </c>
       <c r="C12" s="21" t="n">
-        <v>554.41</v>
+        <v>554.47</v>
       </c>
       <c r="D12" s="21" t="n">
         <v>600</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>-45.59</v>
+        <v>-45.53</v>
       </c>
       <c r="F12" s="18" t="n">
-        <v>-0.076</v>
+        <v>-0.0759</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -26058,16 +25329,16 @@
         </is>
       </c>
       <c r="C15" s="21" t="n">
-        <v>573.2</v>
+        <v>573.26</v>
       </c>
       <c r="D15" s="21" t="n">
         <v>600</v>
       </c>
       <c r="E15" s="17" t="n">
-        <v>-26.8</v>
+        <v>-26.74</v>
       </c>
       <c r="F15" s="18" t="n">
-        <v>-0.0447</v>
+        <v>-0.0446</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -26078,16 +25349,16 @@
         </is>
       </c>
       <c r="C16" s="21" t="n">
-        <v>576.2</v>
+        <v>576.26</v>
       </c>
       <c r="D16" s="21" t="n">
         <v>600</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>-23.8</v>
+        <v>-23.74</v>
       </c>
       <c r="F16" s="18" t="n">
-        <v>-0.0397</v>
+        <v>-0.0396</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -26098,16 +25369,16 @@
         </is>
       </c>
       <c r="C17" s="21" t="n">
-        <v>488.14</v>
+        <v>487.99</v>
       </c>
       <c r="D17" s="21" t="n">
         <v>500</v>
       </c>
       <c r="E17" s="17" t="n">
-        <v>-11.86</v>
+        <v>-12.01</v>
       </c>
       <c r="F17" s="18" t="n">
-        <v>-0.0237</v>
+        <v>-0.024</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -26118,16 +25389,16 @@
         </is>
       </c>
       <c r="C18" s="21" t="n">
-        <v>494.29</v>
+        <v>494.08</v>
       </c>
       <c r="D18" s="21" t="n">
         <v>500</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>-5.71</v>
+        <v>-5.92</v>
       </c>
       <c r="F18" s="18" t="n">
-        <v>-0.0114</v>
+        <v>-0.0118</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -26820,10 +26091,10 @@
         </is>
       </c>
       <c r="B5" s="21" t="n">
-        <v>9820.860000000001</v>
+        <v>9820.690000000001</v>
       </c>
       <c r="C5" s="17" t="n">
-        <v>-179.14</v>
+        <v>-179.31</v>
       </c>
       <c r="D5" s="21" t="n">
         <v>10026.55</v>

--- a/rapporten/voorbeeld/dagrapport.xlsx
+++ b/rapporten/voorbeeld/dagrapport.xlsx
@@ -9,15 +9,16 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overzicht" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grafieken" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analyse" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verlies en risico" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kansen" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Klaar voor echt geld" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Waarde per dag" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trades" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Controles" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Uitleg" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grafiekdata" sheetId="11" state="hidden" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Patronen" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analyse" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verlies en risico" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kansen" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Klaar voor echt geld" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Waarde per dag" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trades" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Controles" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Uitleg" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grafiekdata" sheetId="12" state="hidden" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -32,7 +33,7 @@
     <numFmt numFmtId="166" formatCode="[Color10]+0.00%;[Red]-0.00%;0.00%"/>
     <numFmt numFmtId="167" formatCode="0.00%;[Red]-0.00%"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -78,6 +79,11 @@
     <font>
       <b val="1"/>
       <sz val="18"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="0052514E"/>
+      <sz val="10"/>
     </font>
     <font>
       <i val="1"/>
@@ -134,7 +140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -164,11 +170,20 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -177,7 +192,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
@@ -187,15 +201,15 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5671,7 +5685,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>9820.690000000001</v>
+        <v>9803.33</v>
       </c>
     </row>
     <row r="6">
@@ -5681,7 +5695,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>-179.31</v>
+        <v>-196.67</v>
       </c>
     </row>
     <row r="7">
@@ -5691,7 +5705,7 @@
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>-0.01793099999999992</v>
+        <v>-0.01966699999999999</v>
       </c>
     </row>
     <row r="8">
@@ -5701,7 +5715,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>-164.9300000000003</v>
+        <v>-182.2900000000009</v>
       </c>
     </row>
     <row r="9">
@@ -5721,7 +5735,7 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>-0.01311436185473647</v>
+        <v>-0.01462603586879463</v>
       </c>
     </row>
     <row r="11">
@@ -5750,7 +5764,7 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>10026.55</v>
+        <v>10024.15</v>
       </c>
     </row>
     <row r="15">
@@ -5760,7 +5774,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>26.55</v>
+        <v>24.15</v>
       </c>
     </row>
     <row r="16">
@@ -5770,7 +5784,7 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>0.002654999999999852</v>
+        <v>0.002415000000000056</v>
       </c>
     </row>
     <row r="17">
@@ -5780,7 +5794,7 @@
         </is>
       </c>
       <c r="C17" s="9" t="n">
-        <v>12.1299999999992</v>
+        <v>9.729999999999563</v>
       </c>
     </row>
     <row r="18">
@@ -5800,7 +5814,7 @@
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>0.004613642605964752</v>
+        <v>0.004600814136524578</v>
       </c>
     </row>
     <row r="20">
@@ -5951,166 +5965,70 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="110" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
-        <is>
-          <t>Begrip</t>
-        </is>
-      </c>
-      <c r="B1" s="15" t="inlineStr">
-        <is>
-          <t>Betekenis</t>
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>Bot</t>
+        </is>
+      </c>
+      <c r="B1" s="21" t="inlineStr">
+        <is>
+          <t>Controle</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="35.9" customHeight="1">
-      <c r="A2" s="16" t="inlineStr">
-        <is>
-          <t>Wereld-ETF</t>
-        </is>
-      </c>
-      <c r="B2" s="16" t="inlineStr">
-        <is>
-          <t>Een fonds met ongeveer 1.500 grote bedrijven wereldwijd (IWDA). Dit is de maatstaf: doet de bot het beter dan dit simpelweg vasthouden?</t>
+    <row r="2" ht="19.95" customHeight="1">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Investeerder</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="inlineStr">
+        <is>
+          <t>Investeerder: status OK, 52 van 52 koersen opgehaald, marktregime stijgend-laag.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="19.95" customHeight="1">
-      <c r="A3" s="16" t="inlineStr">
-        <is>
-          <t>200-daags gemiddelde</t>
-        </is>
-      </c>
-      <c r="B3" s="16" t="inlineStr">
-        <is>
-          <t>De gemiddelde slotkoers van de laatste 200 handelsdagen. Erboven = stijgende trend op lange termijn.</t>
+    <row r="3" ht="35.9" customHeight="1">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>Investeerder</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>Koersbronnen: 0 bevestigd door twee bronnen, 52 uit één bron, 0 afwijkend. Wisselkoers: bevestigd. Tweede bron overgeslagen na herhaalde fouten (GOOGL: Stooq gaf geen koersen ('&lt;!DOCTYPE html&gt;&lt;html&gt;&lt;head&gt;&lt;meta charset')).</t>
         </is>
       </c>
     </row>
     <row r="4" ht="19.95" customHeight="1">
-      <c r="A4" s="16" t="inlineStr">
-        <is>
-          <t>Breedte</t>
-        </is>
-      </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>Hoeveel van de gevolgde aandelen boven hun 200-daags gemiddelde staan. Hoog = de stijging wordt breed gedragen.</t>
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>Trend-agent</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>Trend-agent: status OK, 50 van 50 koersen opgehaald, marktregime stijgend-laag.</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="19.95" customHeight="1">
-      <c r="A5" s="16" t="inlineStr">
-        <is>
-          <t>Beweeglijkheid</t>
-        </is>
-      </c>
-      <c r="B5" s="16" t="inlineStr">
-        <is>
-          <t>Hoe hard de koersen op en neer gaan, vergeleken met het afgelopen jaar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="19.95" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t>ATR</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>De gemiddelde dagbeweging van een aandeel. De stop-loss ligt 2x de ATR onder de instap.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="19.95" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>RSI</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>Maat voor hoe hard een koers recent is gestegen (0-100). Boven 70-75 = mogelijk te snel opgelopen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="19.95" customHeight="1">
-      <c r="A8" s="16" t="inlineStr">
-        <is>
-          <t>MACD</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>Laat zien of een stijging versnelt (positief) of vertraagt (negatief).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="19.95" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
-        <is>
-          <t>Stop-loss</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>De prijs waarop de bot automatisch verkoopt om het verlies te beperken. Schuift mee omhoog als het goed gaat.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="19.95" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>Resultaat van een trade gedeeld door het risico bij instap. +2 R = twee keer zoveel gewonnen als je riskeerde.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="19.95" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
-        <is>
-          <t>Instapmoment</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>Ongeteste vuistregel: gunstig = sterk maar niet ver weggelopen; opgelopen = ver boven het 20-daags gemiddelde.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="19.95" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>Momentum</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>Stijging over 12 maanden zonder de laatste maand. De investeerder kiest de 5 hoogste.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="19.95" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>Kill switch</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>Noodstop. Bij te veel verlies koopt de bot niets meer tot jij hem weer aanzet.</t>
+    <row r="5" ht="35.9" customHeight="1">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>Trend-agent</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>Koersbronnen: 0 bevestigd door twee bronnen, 50 uit één bron, 0 afwijkend. Wisselkoers: bevestigd. Tweede bron overgeslagen na herhaalde fouten (GOOGL: Stooq gaf geen koersen ('&lt;!DOCTYPE html&gt;&lt;html&gt;&lt;head&gt;&lt;meta charset')).</t>
         </is>
       </c>
     </row>
@@ -6124,6 +6042,181 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>Begrip</t>
+        </is>
+      </c>
+      <c r="B1" s="21" t="inlineStr">
+        <is>
+          <t>Betekenis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="35.9" customHeight="1">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Wereld-ETF</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="inlineStr">
+        <is>
+          <t>Een fonds met ongeveer 1.500 grote bedrijven wereldwijd (IWDA). Dit is de maatstaf: doet de bot het beter dan dit simpelweg vasthouden?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="19.95" customHeight="1">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>200-daags gemiddelde</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>De gemiddelde slotkoers van de laatste 200 handelsdagen. Erboven = stijgende trend op lange termijn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="19.95" customHeight="1">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>Breedte</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>Hoeveel van de gevolgde aandelen boven hun 200-daags gemiddelde staan. Hoog = de stijging wordt breed gedragen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="19.95" customHeight="1">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>Beweeglijkheid</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>Hoe hard de koersen op en neer gaan, vergeleken met het afgelopen jaar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="19.95" customHeight="1">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>ATR</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>De gemiddelde dagbeweging van een aandeel. De stop-loss ligt 2x de ATR onder de instap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="19.95" customHeight="1">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>RSI</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>Maat voor hoe hard een koers recent is gestegen (0-100). Boven 70-75 = mogelijk te snel opgelopen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="19.95" customHeight="1">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>MACD</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>Laat zien of een stijging versnelt (positief) of vertraagt (negatief).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="19.95" customHeight="1">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>Stop-loss</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>De prijs waarop de bot automatisch verkoopt om het verlies te beperken. Schuift mee omhoog als het goed gaat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="19.95" customHeight="1">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>Resultaat van een trade gedeeld door het risico bij instap. +2 R = twee keer zoveel gewonnen als je riskeerde.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="19.95" customHeight="1">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>Instapmoment</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>Ongeteste vuistregel: gunstig = sterk maar niet ver weggelopen; opgelopen = ver boven het 20-daags gemiddelde.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="19.95" customHeight="1">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>Momentum</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>Stijging over 12 maanden zonder de laatste maand. De investeerder kiest de 5 hoogste.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="19.95" customHeight="1">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>Kill switch</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>Noodstop. Bij te veel verlies koopt de bot niets meer tot jij hem weer aanzet.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:KR66"/>
@@ -6622,7 +6715,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S2" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -6648,7 +6741,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC2" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -6794,22 +6887,22 @@
         </is>
       </c>
       <c r="CB2" t="n">
-        <v>975.8099999999999</v>
+        <v>975.6565000000001</v>
       </c>
       <c r="CC2" t="n">
-        <v>978.4</v>
+        <v>978.2461</v>
       </c>
       <c r="CD2" t="n">
-        <v>873.63</v>
+        <v>873.4926</v>
       </c>
       <c r="CE2" t="n">
-        <v>904.28</v>
+        <v>904.1378</v>
       </c>
       <c r="CF2" t="n">
-        <v>923.8603000000001</v>
+        <v>923.7148999999999</v>
       </c>
       <c r="CG2" t="n">
-        <v>476.0013</v>
+        <v>475.9264</v>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
@@ -6897,7 +6990,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S3" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -6923,7 +7016,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC3" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -7069,22 +7162,22 @@
         </is>
       </c>
       <c r="CB3" t="n">
-        <v>866.77</v>
+        <v>866.6336</v>
       </c>
       <c r="CC3" t="n">
-        <v>887.71</v>
+        <v>887.5703</v>
       </c>
       <c r="CD3" t="n">
-        <v>840.51</v>
+        <v>840.3777</v>
       </c>
       <c r="CE3" t="n">
-        <v>853.2</v>
+        <v>853.0657</v>
       </c>
       <c r="CF3" t="n">
-        <v>929.3971</v>
+        <v>929.2508</v>
       </c>
       <c r="CG3" t="n">
-        <v>479.4822</v>
+        <v>479.4068</v>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
@@ -7178,7 +7271,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S4" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -7204,7 +7297,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC4" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -7350,22 +7443,22 @@
         </is>
       </c>
       <c r="CB4" t="n">
-        <v>822.53</v>
+        <v>822.4006000000001</v>
       </c>
       <c r="CC4" t="n">
-        <v>903.96</v>
+        <v>903.8178</v>
       </c>
       <c r="CD4" t="n">
-        <v>804</v>
+        <v>803.8735</v>
       </c>
       <c r="CE4" t="n">
-        <v>848.95</v>
+        <v>848.8164</v>
       </c>
       <c r="CF4" t="n">
-        <v>933.574</v>
+        <v>933.4271</v>
       </c>
       <c r="CG4" t="n">
-        <v>482.9088</v>
+        <v>482.8328</v>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
@@ -7396,13 +7489,13 @@
         </is>
       </c>
       <c r="KO4" t="n">
-        <v>9820.690000000001</v>
+        <v>9803.33</v>
       </c>
       <c r="KP4" t="n">
-        <v>10026.55</v>
+        <v>10024.15</v>
       </c>
       <c r="KQ4" t="n">
-        <v>9951.65</v>
+        <v>9949.379999999999</v>
       </c>
       <c r="KR4" t="n">
         <v>10000</v>
@@ -7459,7 +7552,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S5" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -7485,7 +7578,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC5" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -7631,22 +7724,22 @@
         </is>
       </c>
       <c r="CB5" t="n">
-        <v>885.5700000000001</v>
+        <v>885.4307</v>
       </c>
       <c r="CC5" t="n">
-        <v>901</v>
+        <v>900.8582</v>
       </c>
       <c r="CD5" t="n">
-        <v>858.9</v>
+        <v>858.7649</v>
       </c>
       <c r="CE5" t="n">
-        <v>865.46</v>
+        <v>865.3239</v>
       </c>
       <c r="CF5" t="n">
-        <v>937.5535</v>
+        <v>937.4059999999999</v>
       </c>
       <c r="CG5" t="n">
-        <v>486.4008</v>
+        <v>486.3243</v>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
@@ -7729,7 +7822,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S6" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -7758,7 +7851,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC6" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -7904,22 +7997,22 @@
         </is>
       </c>
       <c r="CB6" t="n">
-        <v>925.35</v>
+        <v>925.2044</v>
       </c>
       <c r="CC6" t="n">
-        <v>982.88</v>
+        <v>982.7252999999999</v>
       </c>
       <c r="CD6" t="n">
-        <v>916.5700000000001</v>
+        <v>916.4258</v>
       </c>
       <c r="CE6" t="n">
-        <v>970.8200000000001</v>
+        <v>970.6672</v>
       </c>
       <c r="CF6" t="n">
-        <v>944.0393</v>
+        <v>943.8907</v>
       </c>
       <c r="CG6" t="n">
-        <v>490.3456</v>
+        <v>490.2685</v>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
@@ -8002,7 +8095,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S7" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -8031,7 +8124,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC7" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -8177,22 +8270,22 @@
         </is>
       </c>
       <c r="CB7" t="n">
-        <v>938.25</v>
+        <v>938.1023</v>
       </c>
       <c r="CC7" t="n">
-        <v>982.62</v>
+        <v>982.4654</v>
       </c>
       <c r="CD7" t="n">
-        <v>936.0599999999999</v>
+        <v>935.9127</v>
       </c>
       <c r="CE7" t="n">
-        <v>959.48</v>
+        <v>959.329</v>
       </c>
       <c r="CF7" t="n">
-        <v>948.295</v>
+        <v>948.1458</v>
       </c>
       <c r="CG7" t="n">
-        <v>494.2258</v>
+        <v>494.148</v>
       </c>
       <c r="CI7" t="inlineStr">
         <is>
@@ -8275,7 +8368,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S8" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -8304,7 +8397,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC8" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -8450,22 +8543,22 @@
         </is>
       </c>
       <c r="CB8" t="n">
-        <v>975.13</v>
+        <v>974.9766</v>
       </c>
       <c r="CC8" t="n">
-        <v>1011.77</v>
+        <v>1011.6108</v>
       </c>
       <c r="CD8" t="n">
-        <v>964.4</v>
+        <v>964.2483</v>
       </c>
       <c r="CE8" t="n">
-        <v>990.21</v>
+        <v>990.0542</v>
       </c>
       <c r="CF8" t="n">
-        <v>952.1950000000001</v>
+        <v>952.0452</v>
       </c>
       <c r="CG8" t="n">
-        <v>498.2386</v>
+        <v>498.1602</v>
       </c>
       <c r="CI8" t="inlineStr">
         <is>
@@ -8548,7 +8641,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S9" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -8577,7 +8670,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC9" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -8723,22 +8816,22 @@
         </is>
       </c>
       <c r="CB9" t="n">
-        <v>959.03</v>
+        <v>958.8791</v>
       </c>
       <c r="CC9" t="n">
-        <v>967.14</v>
+        <v>966.9878</v>
       </c>
       <c r="CD9" t="n">
-        <v>904</v>
+        <v>903.8578</v>
       </c>
       <c r="CE9" t="n">
-        <v>920.95</v>
+        <v>920.8051</v>
       </c>
       <c r="CF9" t="n">
-        <v>955.2848</v>
+        <v>955.1345</v>
       </c>
       <c r="CG9" t="n">
-        <v>501.8895</v>
+        <v>501.8105</v>
       </c>
       <c r="CI9" t="inlineStr">
         <is>
@@ -8821,7 +8914,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S10" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -8850,7 +8943,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC10" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -8996,22 +9089,22 @@
         </is>
       </c>
       <c r="CB10" t="n">
-        <v>932.45</v>
+        <v>932.3033</v>
       </c>
       <c r="CC10" t="n">
-        <v>935</v>
+        <v>934.8529</v>
       </c>
       <c r="CD10" t="n">
-        <v>854.79</v>
+        <v>854.6555</v>
       </c>
       <c r="CE10" t="n">
-        <v>900.2</v>
+        <v>900.0583</v>
       </c>
       <c r="CF10" t="n">
-        <v>957.2186</v>
+        <v>957.068</v>
       </c>
       <c r="CG10" t="n">
-        <v>505.4629</v>
+        <v>505.3834</v>
       </c>
       <c r="CI10" t="inlineStr">
         <is>
@@ -9094,7 +9187,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S11" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -9123,7 +9216,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC11" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -9269,22 +9362,22 @@
         </is>
       </c>
       <c r="CB11" t="n">
-        <v>839.61</v>
+        <v>839.4779</v>
       </c>
       <c r="CC11" t="n">
-        <v>848.36</v>
+        <v>848.2265</v>
       </c>
       <c r="CD11" t="n">
-        <v>789.09</v>
+        <v>788.9659</v>
       </c>
       <c r="CE11" t="n">
-        <v>820.53</v>
+        <v>820.4009</v>
       </c>
       <c r="CF11" t="n">
-        <v>958.1114</v>
+        <v>957.9607</v>
       </c>
       <c r="CG11" t="n">
-        <v>508.5838</v>
+        <v>508.5038</v>
       </c>
       <c r="CI11" t="inlineStr">
         <is>
@@ -9367,7 +9460,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S12" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
@@ -9396,7 +9489,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC12" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -9442,7 +9535,7 @@
         <v>1535.0628</v>
       </c>
       <c r="AS12" t="n">
-        <v>1201.4256</v>
+        <v>1201.4255</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
@@ -9542,22 +9635,22 @@
         </is>
       </c>
       <c r="CB12" t="n">
-        <v>833</v>
+        <v>832.8689000000001</v>
       </c>
       <c r="CC12" t="n">
-        <v>841.8</v>
+        <v>841.6675</v>
       </c>
       <c r="CD12" t="n">
-        <v>737.88</v>
+        <v>737.7639</v>
       </c>
       <c r="CE12" t="n">
-        <v>739</v>
+        <v>738.8837</v>
       </c>
       <c r="CF12" t="n">
-        <v>958.4005</v>
+        <v>958.2497</v>
       </c>
       <c r="CG12" t="n">
-        <v>511.3181</v>
+        <v>511.2377</v>
       </c>
       <c r="CI12" t="inlineStr">
         <is>
@@ -9640,7 +9733,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S13" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -9669,7 +9762,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC13" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -9815,22 +9908,22 @@
         </is>
       </c>
       <c r="CB13" t="n">
-        <v>793.14</v>
+        <v>793.0152</v>
       </c>
       <c r="CC13" t="n">
-        <v>882.5</v>
+        <v>882.3611</v>
       </c>
       <c r="CD13" t="n">
-        <v>789</v>
+        <v>788.8758</v>
       </c>
       <c r="CE13" t="n">
-        <v>874.66</v>
+        <v>874.5223</v>
       </c>
       <c r="CF13" t="n">
-        <v>962.265</v>
+        <v>962.1135</v>
       </c>
       <c r="CG13" t="n">
-        <v>514.7843</v>
+        <v>514.7033</v>
       </c>
       <c r="CI13" t="inlineStr">
         <is>
@@ -9913,7 +10006,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S14" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -9942,7 +10035,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC14" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -10088,22 +10181,22 @@
         </is>
       </c>
       <c r="CB14" t="n">
-        <v>919.65</v>
+        <v>919.5053</v>
       </c>
       <c r="CC14" t="n">
-        <v>930.88</v>
+        <v>930.7335</v>
       </c>
       <c r="CD14" t="n">
-        <v>818</v>
+        <v>817.8713</v>
       </c>
       <c r="CE14" t="n">
-        <v>823.03</v>
+        <v>822.9005</v>
       </c>
       <c r="CF14" t="n">
-        <v>964.7529</v>
+        <v>964.6011</v>
       </c>
       <c r="CG14" t="n">
-        <v>517.9365</v>
+        <v>517.855</v>
       </c>
       <c r="CI14" t="inlineStr">
         <is>
@@ -10186,7 +10279,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S15" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -10215,7 +10308,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC15" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -10361,22 +10454,22 @@
         </is>
       </c>
       <c r="CB15" t="n">
-        <v>786.36</v>
+        <v>786.2362000000001</v>
       </c>
       <c r="CC15" t="n">
-        <v>836.62</v>
+        <v>836.4883</v>
       </c>
       <c r="CD15" t="n">
-        <v>770.1</v>
+        <v>769.9788</v>
       </c>
       <c r="CE15" t="n">
-        <v>829.5</v>
+        <v>829.3694</v>
       </c>
       <c r="CF15" t="n">
-        <v>966.7054000000001</v>
+        <v>966.5531999999999</v>
       </c>
       <c r="CG15" t="n">
-        <v>521.1497000000001</v>
+        <v>521.0676999999999</v>
       </c>
       <c r="CI15" t="inlineStr">
         <is>
@@ -10459,7 +10552,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S16" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -10488,7 +10581,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC16" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -10634,22 +10727,22 @@
         </is>
       </c>
       <c r="CB16" t="n">
-        <v>866.8200000000001</v>
+        <v>866.6836</v>
       </c>
       <c r="CC16" t="n">
-        <v>902.4299999999999</v>
+        <v>902.288</v>
       </c>
       <c r="CD16" t="n">
-        <v>858.5</v>
+        <v>858.3649</v>
       </c>
       <c r="CE16" t="n">
-        <v>892.67</v>
+        <v>892.5295</v>
       </c>
       <c r="CF16" t="n">
-        <v>969.3191</v>
+        <v>969.1666</v>
       </c>
       <c r="CG16" t="n">
-        <v>524.6541999999999</v>
+        <v>524.5717</v>
       </c>
       <c r="CI16" t="inlineStr">
         <is>
@@ -10732,7 +10825,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S17" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -10761,7 +10854,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC17" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -10907,22 +11000,22 @@
         </is>
       </c>
       <c r="CB17" t="n">
-        <v>885.3</v>
+        <v>885.1607</v>
       </c>
       <c r="CC17" t="n">
-        <v>928.98</v>
+        <v>928.8338</v>
       </c>
       <c r="CD17" t="n">
-        <v>881.2</v>
+        <v>881.0613</v>
       </c>
       <c r="CE17" t="n">
-        <v>893.1900000000001</v>
+        <v>893.0494</v>
       </c>
       <c r="CF17" t="n">
-        <v>972.1652</v>
+        <v>972.0122</v>
       </c>
       <c r="CG17" t="n">
-        <v>528.1085</v>
+        <v>528.0254</v>
       </c>
       <c r="CI17" t="inlineStr">
         <is>
@@ -11005,7 +11098,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S18" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -11034,7 +11127,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC18" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -11180,22 +11273,22 @@
         </is>
       </c>
       <c r="CB18" t="n">
-        <v>843.11</v>
+        <v>842.9773</v>
       </c>
       <c r="CC18" t="n">
-        <v>913.33</v>
+        <v>913.1863</v>
       </c>
       <c r="CD18" t="n">
-        <v>827</v>
+        <v>826.8698000000001</v>
       </c>
       <c r="CE18" t="n">
-        <v>881.47</v>
+        <v>881.3312</v>
       </c>
       <c r="CF18" t="n">
-        <v>971.8798</v>
+        <v>971.7268</v>
       </c>
       <c r="CG18" t="n">
-        <v>531.505</v>
+        <v>531.4213</v>
       </c>
       <c r="CI18" t="inlineStr">
         <is>
@@ -11278,7 +11371,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S19" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
@@ -11307,7 +11400,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC19" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -11453,22 +11546,22 @@
         </is>
       </c>
       <c r="CB19" t="n">
-        <v>903.6</v>
+        <v>903.4578</v>
       </c>
       <c r="CC19" t="n">
-        <v>904.8</v>
+        <v>904.6576</v>
       </c>
       <c r="CD19" t="n">
-        <v>847.02</v>
+        <v>846.8868</v>
       </c>
       <c r="CE19" t="n">
-        <v>877.5700000000001</v>
+        <v>877.4319</v>
       </c>
       <c r="CF19" t="n">
-        <v>970.8658</v>
+        <v>970.7131000000001</v>
       </c>
       <c r="CG19" t="n">
-        <v>534.86</v>
+        <v>534.7758</v>
       </c>
       <c r="CI19" t="inlineStr">
         <is>
@@ -11551,7 +11644,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S20" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -11580,7 +11673,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC20" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -11726,22 +11819,22 @@
         </is>
       </c>
       <c r="CB20" t="n">
-        <v>863.67</v>
+        <v>863.5341</v>
       </c>
       <c r="CC20" t="n">
-        <v>894.99</v>
+        <v>894.8491</v>
       </c>
       <c r="CD20" t="n">
-        <v>854.4</v>
+        <v>854.2655999999999</v>
       </c>
       <c r="CE20" t="n">
-        <v>861</v>
+        <v>860.8645</v>
       </c>
       <c r="CF20" t="n">
-        <v>969.6183</v>
+        <v>969.4657</v>
       </c>
       <c r="CG20" t="n">
-        <v>538.1545</v>
+        <v>538.0698</v>
       </c>
       <c r="CI20" t="inlineStr">
         <is>
@@ -11824,7 +11917,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S21" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -11853,7 +11946,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC21" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -11999,22 +12092,22 @@
         </is>
       </c>
       <c r="CB21" t="n">
-        <v>871.8</v>
+        <v>871.6627999999999</v>
       </c>
       <c r="CC21" t="n">
-        <v>879</v>
+        <v>878.8617</v>
       </c>
       <c r="CD21" t="n">
-        <v>844.62</v>
+        <v>844.4871000000001</v>
       </c>
       <c r="CE21" t="n">
-        <v>868.52</v>
+        <v>868.3834000000001</v>
       </c>
       <c r="CF21" t="n">
-        <v>967.5717</v>
+        <v>967.4194</v>
       </c>
       <c r="CG21" t="n">
-        <v>541.5057</v>
+        <v>541.4204999999999</v>
       </c>
       <c r="CI21" t="inlineStr">
         <is>
@@ -12097,7 +12190,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S22" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
@@ -12126,7 +12219,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC22" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -12272,22 +12365,22 @@
         </is>
       </c>
       <c r="CB22" t="n">
-        <v>912.9400000000001</v>
+        <v>912.7963999999999</v>
       </c>
       <c r="CC22" t="n">
-        <v>935.8</v>
+        <v>935.6528</v>
       </c>
       <c r="CD22" t="n">
-        <v>899.54</v>
+        <v>899.3985</v>
       </c>
       <c r="CE22" t="n">
-        <v>911.29</v>
+        <v>911.1466</v>
       </c>
       <c r="CF22" t="n">
-        <v>965.0906</v>
+        <v>964.9388</v>
       </c>
       <c r="CG22" t="n">
-        <v>545.0297</v>
+        <v>544.9439</v>
       </c>
       <c r="CI22" t="inlineStr">
         <is>
@@ -12370,7 +12463,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S23" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
@@ -12399,7 +12492,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC23" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -12545,22 +12638,22 @@
         </is>
       </c>
       <c r="CB23" t="n">
-        <v>912.89</v>
+        <v>912.7464</v>
       </c>
       <c r="CC23" t="n">
-        <v>978</v>
+        <v>977.8461</v>
       </c>
       <c r="CD23" t="n">
-        <v>906.5</v>
+        <v>906.3573</v>
       </c>
       <c r="CE23" t="n">
-        <v>949.83</v>
+        <v>949.6805000000001</v>
       </c>
       <c r="CF23" t="n">
-        <v>962.8085</v>
+        <v>962.657</v>
       </c>
       <c r="CG23" t="n">
-        <v>548.6848</v>
+        <v>548.5984</v>
       </c>
       <c r="CI23" t="inlineStr">
         <is>
@@ -12643,7 +12736,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S24" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
@@ -12672,7 +12765,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC24" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -12818,22 +12911,22 @@
         </is>
       </c>
       <c r="CB24" t="n">
-        <v>979.3200000000001</v>
+        <v>979.1659</v>
       </c>
       <c r="CC24" t="n">
-        <v>984</v>
+        <v>983.8452</v>
       </c>
       <c r="CD24" t="n">
-        <v>956.2</v>
+        <v>956.0496000000001</v>
       </c>
       <c r="CE24" t="n">
-        <v>971.66</v>
+        <v>971.5071</v>
       </c>
       <c r="CF24" t="n">
-        <v>960.6536</v>
+        <v>960.5025000000001</v>
       </c>
       <c r="CG24" t="n">
-        <v>552.4435999999999</v>
+        <v>552.3567</v>
       </c>
       <c r="CI24" t="inlineStr">
         <is>
@@ -12916,7 +13009,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S25" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
@@ -12945,7 +13038,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC25" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -13091,22 +13184,22 @@
         </is>
       </c>
       <c r="CB25" t="n">
-        <v>999.55</v>
+        <v>999.3927</v>
       </c>
       <c r="CC25" t="n">
-        <v>1036.13</v>
+        <v>1035.967</v>
       </c>
       <c r="CD25" t="n">
-        <v>995.26</v>
+        <v>995.1034</v>
       </c>
       <c r="CE25" t="n">
-        <v>1011.75</v>
+        <v>1011.5908</v>
       </c>
       <c r="CF25" t="n">
-        <v>960.9717000000001</v>
+        <v>960.8205</v>
       </c>
       <c r="CG25" t="n">
-        <v>556.3939</v>
+        <v>556.3064000000001</v>
       </c>
       <c r="CI25" t="inlineStr">
         <is>
@@ -13189,7 +13282,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S26" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
@@ -13218,7 +13311,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC26" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -13364,22 +13457,22 @@
         </is>
       </c>
       <c r="CB26" t="n">
-        <v>957.1</v>
+        <v>956.9494</v>
       </c>
       <c r="CC26" t="n">
-        <v>978.67</v>
+        <v>978.516</v>
       </c>
       <c r="CD26" t="n">
-        <v>926.64</v>
+        <v>926.4942</v>
       </c>
       <c r="CE26" t="n">
-        <v>940.76</v>
+        <v>940.612</v>
       </c>
       <c r="CF26" t="n">
-        <v>962.5094</v>
+        <v>962.3579</v>
       </c>
       <c r="CG26" t="n">
-        <v>559.9657</v>
+        <v>559.8776</v>
       </c>
       <c r="CI26" t="inlineStr">
         <is>
@@ -13462,7 +13555,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S27" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -13491,7 +13584,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC27" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -13637,22 +13730,22 @@
         </is>
       </c>
       <c r="CB27" t="n">
-        <v>959.36</v>
+        <v>959.2089999999999</v>
       </c>
       <c r="CC27" t="n">
-        <v>960</v>
+        <v>959.8489</v>
       </c>
       <c r="CD27" t="n">
-        <v>915.1799999999999</v>
+        <v>915.0359999999999</v>
       </c>
       <c r="CE27" t="n">
-        <v>937.11</v>
+        <v>936.9625</v>
       </c>
       <c r="CF27" t="n">
-        <v>962.2689</v>
+        <v>962.1174999999999</v>
       </c>
       <c r="CG27" t="n">
-        <v>563.5323</v>
+        <v>563.4435999999999</v>
       </c>
       <c r="CI27" t="inlineStr">
         <is>
@@ -13735,7 +13828,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S28" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
@@ -13764,7 +13857,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC28" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -13910,22 +14003,22 @@
         </is>
       </c>
       <c r="CB28" t="n">
-        <v>935.01</v>
+        <v>934.8629</v>
       </c>
       <c r="CC28" t="n">
-        <v>977.28</v>
+        <v>977.1262</v>
       </c>
       <c r="CD28" t="n">
-        <v>929.0700000000001</v>
+        <v>928.9238</v>
       </c>
       <c r="CE28" t="n">
-        <v>974.33</v>
+        <v>974.1767</v>
       </c>
       <c r="CF28" t="n">
-        <v>963.0405</v>
+        <v>962.889</v>
       </c>
       <c r="CG28" t="n">
-        <v>567.2862</v>
+        <v>567.1969</v>
       </c>
       <c r="CI28" t="inlineStr">
         <is>
@@ -14008,7 +14101,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S29" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
@@ -14037,7 +14130,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC29" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -14183,22 +14276,22 @@
         </is>
       </c>
       <c r="CB29" t="n">
-        <v>989.6799999999999</v>
+        <v>989.5243</v>
       </c>
       <c r="CC29" t="n">
-        <v>989.96</v>
+        <v>989.8043</v>
       </c>
       <c r="CD29" t="n">
-        <v>958.26</v>
+        <v>958.1093</v>
       </c>
       <c r="CE29" t="n">
-        <v>966.78</v>
+        <v>966.6279</v>
       </c>
       <c r="CF29" t="n">
-        <v>964.5413</v>
+        <v>964.3895</v>
       </c>
       <c r="CG29" t="n">
-        <v>570.9477000000001</v>
+        <v>570.8579</v>
       </c>
       <c r="CI29" t="inlineStr">
         <is>
@@ -14246,7 +14339,7 @@
         <v>421.046</v>
       </c>
       <c r="G30" t="n">
-        <v>429.3185</v>
+        <v>429.3186</v>
       </c>
       <c r="H30" t="n">
         <v>535.3375423278808</v>
@@ -14281,7 +14374,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S30" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
@@ -14310,7 +14403,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC30" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -14456,22 +14549,22 @@
         </is>
       </c>
       <c r="CB30" t="n">
-        <v>934.78</v>
+        <v>934.6328999999999</v>
       </c>
       <c r="CC30" t="n">
-        <v>936.45</v>
+        <v>936.3027</v>
       </c>
       <c r="CD30" t="n">
-        <v>887.61</v>
+        <v>887.4703</v>
       </c>
       <c r="CE30" t="n">
-        <v>910.4299999999999</v>
+        <v>910.2867</v>
       </c>
       <c r="CF30" t="n">
-        <v>962.8356</v>
+        <v>962.684</v>
       </c>
       <c r="CG30" t="n">
-        <v>574.4108</v>
+        <v>574.3203999999999</v>
       </c>
       <c r="CI30" t="inlineStr">
         <is>
@@ -14554,7 +14647,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S31" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
@@ -14583,7 +14676,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC31" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -14729,22 +14822,22 @@
         </is>
       </c>
       <c r="CB31" t="n">
-        <v>928.98</v>
+        <v>928.8338</v>
       </c>
       <c r="CC31" t="n">
-        <v>946.67</v>
+        <v>946.521</v>
       </c>
       <c r="CD31" t="n">
-        <v>916.3</v>
+        <v>916.1558</v>
       </c>
       <c r="CE31" t="n">
-        <v>932.97</v>
+        <v>932.8232</v>
       </c>
       <c r="CF31" t="n">
-        <v>961.8658</v>
+        <v>961.7144</v>
       </c>
       <c r="CG31" t="n">
-        <v>577.8893</v>
+        <v>577.7984</v>
       </c>
       <c r="CI31" t="inlineStr">
         <is>
@@ -14827,7 +14920,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S32" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
@@ -14856,7 +14949,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC32" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -15002,22 +15095,22 @@
         </is>
       </c>
       <c r="CB32" t="n">
-        <v>925.74</v>
+        <v>925.5943</v>
       </c>
       <c r="CC32" t="n">
-        <v>945.75</v>
+        <v>945.6011999999999</v>
       </c>
       <c r="CD32" t="n">
-        <v>924.6</v>
+        <v>924.4545000000001</v>
       </c>
       <c r="CE32" t="n">
-        <v>938.4</v>
+        <v>938.2524</v>
       </c>
       <c r="CF32" t="n">
-        <v>958.8773</v>
+        <v>958.7264</v>
       </c>
       <c r="CG32" t="n">
-        <v>581.3908</v>
+        <v>581.2993</v>
       </c>
       <c r="CI32" t="inlineStr">
         <is>
@@ -15100,7 +15193,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S33" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
@@ -15129,7 +15222,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC33" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -15275,22 +15368,22 @@
         </is>
       </c>
       <c r="CB33" t="n">
-        <v>967.01</v>
+        <v>966.8578</v>
       </c>
       <c r="CC33" t="n">
-        <v>968.71</v>
+        <v>968.5576</v>
       </c>
       <c r="CD33" t="n">
-        <v>906.89</v>
+        <v>906.7473</v>
       </c>
       <c r="CE33" t="n">
-        <v>935.39</v>
+        <v>935.2428</v>
       </c>
       <c r="CF33" t="n">
-        <v>957.1731</v>
+        <v>957.0223999999999</v>
       </c>
       <c r="CG33" t="n">
-        <v>584.8792999999999</v>
+        <v>584.7873</v>
       </c>
       <c r="CI33" t="inlineStr">
         <is>
@@ -15373,7 +15466,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S34" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
@@ -15402,7 +15495,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC34" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -15548,22 +15641,22 @@
         </is>
       </c>
       <c r="CB34" t="n">
-        <v>919.29</v>
+        <v>919.1453</v>
       </c>
       <c r="CC34" t="n">
-        <v>946.8</v>
+        <v>946.651</v>
       </c>
       <c r="CD34" t="n">
-        <v>909.09</v>
+        <v>908.947</v>
       </c>
       <c r="CE34" t="n">
-        <v>932.86</v>
+        <v>932.7132</v>
       </c>
       <c r="CF34" t="n">
-        <v>954.9697</v>
+        <v>954.8194</v>
       </c>
       <c r="CG34" t="n">
-        <v>588.2784</v>
+        <v>588.1858</v>
       </c>
       <c r="CI34" t="inlineStr">
         <is>
@@ -15646,7 +15739,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S35" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
@@ -15675,7 +15768,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC35" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -15821,22 +15914,22 @@
         </is>
       </c>
       <c r="CB35" t="n">
-        <v>931.39</v>
+        <v>931.2434</v>
       </c>
       <c r="CC35" t="n">
-        <v>959.97</v>
+        <v>959.8189</v>
       </c>
       <c r="CD35" t="n">
-        <v>930.79</v>
+        <v>930.6435</v>
       </c>
       <c r="CE35" t="n">
-        <v>958.73</v>
+        <v>958.5791</v>
       </c>
       <c r="CF35" t="n">
-        <v>951.468</v>
+        <v>951.3182</v>
       </c>
       <c r="CG35" t="n">
-        <v>591.8676</v>
+        <v>591.7745</v>
       </c>
       <c r="CI35" t="inlineStr">
         <is>
@@ -15919,7 +16012,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S36" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
@@ -15948,7 +16041,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC36" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -16094,22 +16187,22 @@
         </is>
       </c>
       <c r="CB36" t="n">
-        <v>941.13</v>
+        <v>940.9819</v>
       </c>
       <c r="CC36" t="n">
-        <v>969.4400000000001</v>
+        <v>969.2874</v>
       </c>
       <c r="CD36" t="n">
-        <v>922.39</v>
+        <v>922.2448000000001</v>
       </c>
       <c r="CE36" t="n">
-        <v>933.4400000000001</v>
+        <v>933.2931</v>
       </c>
       <c r="CF36" t="n">
-        <v>945.9129</v>
+        <v>945.764</v>
       </c>
       <c r="CG36" t="n">
-        <v>595.3115</v>
+        <v>595.2179</v>
       </c>
       <c r="CI36" t="inlineStr">
         <is>
@@ -16192,7 +16285,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S37" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
@@ -16221,7 +16314,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC37" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -16367,22 +16460,22 @@
         </is>
       </c>
       <c r="CB37" t="n">
-        <v>930.83</v>
+        <v>930.6835</v>
       </c>
       <c r="CC37" t="n">
-        <v>958</v>
+        <v>957.8492</v>
       </c>
       <c r="CD37" t="n">
-        <v>927.16</v>
+        <v>927.0141</v>
       </c>
       <c r="CE37" t="n">
-        <v>956.08</v>
+        <v>955.9296000000001</v>
       </c>
       <c r="CF37" t="n">
-        <v>944.0023</v>
+        <v>943.8538</v>
       </c>
       <c r="CG37" t="n">
-        <v>598.9083000000001</v>
+        <v>598.8141000000001</v>
       </c>
       <c r="CI37" t="inlineStr">
         <is>
@@ -16465,7 +16558,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S38" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
@@ -16494,7 +16587,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC38" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -16640,22 +16733,22 @@
         </is>
       </c>
       <c r="CB38" t="n">
-        <v>956.91</v>
+        <v>956.7594</v>
       </c>
       <c r="CC38" t="n">
-        <v>959.76</v>
+        <v>959.609</v>
       </c>
       <c r="CD38" t="n">
-        <v>918.88</v>
+        <v>918.7354</v>
       </c>
       <c r="CE38" t="n">
-        <v>958.16</v>
+        <v>958.0092</v>
       </c>
       <c r="CF38" t="n">
-        <v>942.1985</v>
+        <v>942.0503</v>
       </c>
       <c r="CG38" t="n">
-        <v>602.4662</v>
+        <v>602.3714</v>
       </c>
       <c r="CI38" t="inlineStr">
         <is>
@@ -16738,7 +16831,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S39" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
@@ -16767,7 +16860,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC39" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -16913,22 +17006,22 @@
         </is>
       </c>
       <c r="CB39" t="n">
-        <v>971.34</v>
+        <v>971.1872</v>
       </c>
       <c r="CC39" t="n">
-        <v>1017.77</v>
+        <v>1017.6099</v>
       </c>
       <c r="CD39" t="n">
-        <v>969</v>
+        <v>968.8475</v>
       </c>
       <c r="CE39" t="n">
-        <v>1016.59</v>
+        <v>1016.4301</v>
       </c>
       <c r="CF39" t="n">
-        <v>938.2628999999999</v>
+        <v>938.1152</v>
       </c>
       <c r="CG39" t="n">
-        <v>606.3406</v>
+        <v>606.2452</v>
       </c>
       <c r="CI39" t="inlineStr">
         <is>
@@ -17011,7 +17104,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S40" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
@@ -17040,7 +17133,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC40" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -17186,22 +17279,22 @@
         </is>
       </c>
       <c r="CB40" t="n">
-        <v>1036.4</v>
+        <v>1036.2369</v>
       </c>
       <c r="CC40" t="n">
-        <v>1041.0699</v>
+        <v>1040.9061</v>
       </c>
       <c r="CD40" t="n">
-        <v>997.62</v>
+        <v>997.463</v>
       </c>
       <c r="CE40" t="n">
-        <v>1000.26</v>
+        <v>1000.1026</v>
       </c>
       <c r="CF40" t="n">
-        <v>935.625</v>
+        <v>935.4777</v>
       </c>
       <c r="CG40" t="n">
-        <v>610.2005</v>
+        <v>610.1045</v>
       </c>
       <c r="CI40" t="inlineStr">
         <is>
@@ -17284,7 +17377,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S41" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
@@ -17313,7 +17406,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC41" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -17459,22 +17552,22 @@
         </is>
       </c>
       <c r="CB41" t="n">
-        <v>998.8099999999999</v>
+        <v>998.6528</v>
       </c>
       <c r="CC41" t="n">
-        <v>1042.4</v>
+        <v>1042.236</v>
       </c>
       <c r="CD41" t="n">
-        <v>992.29</v>
+        <v>992.1338</v>
       </c>
       <c r="CE41" t="n">
-        <v>1027.77</v>
+        <v>1027.6083</v>
       </c>
       <c r="CF41" t="n">
-        <v>933.2782999999999</v>
+        <v>933.1314</v>
       </c>
       <c r="CG41" t="n">
-        <v>614.2109</v>
+        <v>614.1142</v>
       </c>
       <c r="CI41" t="inlineStr">
         <is>
@@ -17557,7 +17650,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S42" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
@@ -17586,7 +17679,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC42" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -17732,22 +17825,22 @@
         </is>
       </c>
       <c r="CB42" t="n">
-        <v>997</v>
+        <v>996.8431</v>
       </c>
       <c r="CC42" t="n">
-        <v>999</v>
+        <v>998.8428</v>
       </c>
       <c r="CD42" t="n">
-        <v>973.5</v>
+        <v>973.3468</v>
       </c>
       <c r="CE42" t="n">
-        <v>977.41</v>
+        <v>977.2562</v>
       </c>
       <c r="CF42" t="n">
-        <v>929.7442</v>
+        <v>929.5979</v>
       </c>
       <c r="CG42" t="n">
-        <v>618.092</v>
+        <v>617.9948000000001</v>
       </c>
       <c r="CI42" t="inlineStr">
         <is>
@@ -17830,7 +17923,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S43" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
@@ -17859,7 +17952,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC43" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -18005,22 +18098,22 @@
         </is>
       </c>
       <c r="CB43" t="n">
-        <v>993.2</v>
+        <v>993.0436999999999</v>
       </c>
       <c r="CC43" t="n">
-        <v>993.99</v>
+        <v>993.8336</v>
       </c>
       <c r="CD43" t="n">
-        <v>967.38</v>
+        <v>967.2278</v>
       </c>
       <c r="CE43" t="n">
-        <v>975.26</v>
+        <v>975.1066</v>
       </c>
       <c r="CF43" t="n">
-        <v>928.607</v>
+        <v>928.4609</v>
       </c>
       <c r="CG43" t="n">
-        <v>621.9325</v>
+        <v>621.8346</v>
       </c>
       <c r="CI43" t="inlineStr">
         <is>
@@ -18103,7 +18196,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S44" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U44" t="inlineStr">
         <is>
@@ -18132,7 +18225,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC44" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -18278,22 +18371,22 @@
         </is>
       </c>
       <c r="CB44" t="n">
-        <v>906.03</v>
+        <v>905.8875</v>
       </c>
       <c r="CC44" t="n">
-        <v>932.21</v>
+        <v>932.0633</v>
       </c>
       <c r="CD44" t="n">
-        <v>902.6</v>
+        <v>902.458</v>
       </c>
       <c r="CE44" t="n">
-        <v>924.03</v>
+        <v>923.8846</v>
       </c>
       <c r="CF44" t="n">
-        <v>927.5794</v>
+        <v>927.4334</v>
       </c>
       <c r="CG44" t="n">
-        <v>625.4340999999999</v>
+        <v>625.3357</v>
       </c>
       <c r="CI44" t="inlineStr">
         <is>
@@ -18376,7 +18469,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S45" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
@@ -18405,7 +18498,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC45" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -18551,22 +18644,22 @@
         </is>
       </c>
       <c r="CB45" t="n">
-        <v>937.5</v>
+        <v>937.3525</v>
       </c>
       <c r="CC45" t="n">
-        <v>944.9400000000001</v>
+        <v>944.7913</v>
       </c>
       <c r="CD45" t="n">
-        <v>920.13</v>
+        <v>919.9852</v>
       </c>
       <c r="CE45" t="n">
-        <v>927.6</v>
+        <v>927.454</v>
       </c>
       <c r="CF45" t="n">
-        <v>926.4364</v>
+        <v>926.2906</v>
       </c>
       <c r="CG45" t="n">
-        <v>628.9505</v>
+        <v>628.8516</v>
       </c>
       <c r="CI45" t="inlineStr">
         <is>
@@ -18649,7 +18742,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S46" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U46" t="inlineStr">
         <is>
@@ -18678,7 +18771,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC46" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -18824,22 +18917,22 @@
         </is>
       </c>
       <c r="CB46" t="n">
-        <v>934.23</v>
+        <v>934.083</v>
       </c>
       <c r="CC46" t="n">
-        <v>941.2</v>
+        <v>941.0519</v>
       </c>
       <c r="CD46" t="n">
-        <v>917.64</v>
+        <v>917.4956</v>
       </c>
       <c r="CE46" t="n">
-        <v>926.55</v>
+        <v>926.4041999999999</v>
       </c>
       <c r="CF46" t="n">
-        <v>926.1998</v>
+        <v>926.0540999999999</v>
       </c>
       <c r="CG46" t="n">
-        <v>632.4331</v>
+        <v>632.3336</v>
       </c>
       <c r="CI46" t="inlineStr">
         <is>
@@ -18922,7 +19015,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S47" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
@@ -18951,7 +19044,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC47" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -19097,22 +19190,22 @@
         </is>
       </c>
       <c r="CB47" t="n">
-        <v>954.5700000000001</v>
+        <v>954.4198</v>
       </c>
       <c r="CC47" t="n">
-        <v>986.2</v>
+        <v>986.0448</v>
       </c>
       <c r="CD47" t="n">
-        <v>953.5</v>
+        <v>953.35</v>
       </c>
       <c r="CE47" t="n">
-        <v>977.5</v>
+        <v>977.3462</v>
       </c>
       <c r="CF47" t="n">
-        <v>926.7738000000001</v>
+        <v>926.628</v>
       </c>
       <c r="CG47" t="n">
-        <v>636.1394</v>
+        <v>636.0393</v>
       </c>
       <c r="CI47" t="inlineStr">
         <is>
@@ -19195,7 +19288,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S48" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U48" t="inlineStr">
         <is>
@@ -19224,7 +19317,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC48" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -19370,22 +19463,22 @@
         </is>
       </c>
       <c r="CB48" t="n">
-        <v>984.72</v>
+        <v>984.5650000000001</v>
       </c>
       <c r="CC48" t="n">
-        <v>1016.44</v>
+        <v>1016.2801</v>
       </c>
       <c r="CD48" t="n">
-        <v>977.83</v>
+        <v>977.6761</v>
       </c>
       <c r="CE48" t="n">
-        <v>1015.8</v>
+        <v>1015.6401</v>
       </c>
       <c r="CF48" t="n">
-        <v>927.2569999999999</v>
+        <v>927.1111</v>
       </c>
       <c r="CG48" t="n">
-        <v>640.0173</v>
+        <v>639.9165</v>
       </c>
       <c r="CI48" t="inlineStr">
         <is>
@@ -19468,7 +19561,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S49" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
@@ -19497,7 +19590,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC49" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -19643,22 +19736,22 @@
         </is>
       </c>
       <c r="CB49" t="n">
-        <v>1044.99</v>
+        <v>1044.8255</v>
       </c>
       <c r="CC49" t="n">
-        <v>1064.49</v>
+        <v>1064.3225</v>
       </c>
       <c r="CD49" t="n">
-        <v>1030.6801</v>
+        <v>1030.5178</v>
       </c>
       <c r="CE49" t="n">
-        <v>1043.96</v>
+        <v>1043.7957</v>
       </c>
       <c r="CF49" t="n">
-        <v>928.5502</v>
+        <v>928.4041</v>
       </c>
       <c r="CG49" t="n">
-        <v>644.0408</v>
+        <v>643.9394</v>
       </c>
       <c r="CI49" t="inlineStr">
         <is>
@@ -19741,7 +19834,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S50" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
@@ -19770,7 +19863,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC50" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
@@ -19916,22 +20009,22 @@
         </is>
       </c>
       <c r="CB50" t="n">
-        <v>1032.85</v>
+        <v>1032.6875</v>
       </c>
       <c r="CC50" t="n">
-        <v>1097.25</v>
+        <v>1097.0773</v>
       </c>
       <c r="CD50" t="n">
-        <v>1030.02</v>
+        <v>1029.8579</v>
       </c>
       <c r="CE50" t="n">
-        <v>1096.16</v>
+        <v>1095.9875</v>
       </c>
       <c r="CF50" t="n">
-        <v>931.7334</v>
+        <v>931.5868</v>
       </c>
       <c r="CG50" t="n">
-        <v>648.3519</v>
+        <v>648.2499</v>
       </c>
       <c r="CI50" t="inlineStr">
         <is>
@@ -20014,7 +20107,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S51" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
@@ -20043,7 +20136,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC51" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
@@ -20189,22 +20282,22 @@
         </is>
       </c>
       <c r="CB51" t="n">
-        <v>1100.0699</v>
+        <v>1099.8968</v>
       </c>
       <c r="CC51" t="n">
-        <v>1105.5</v>
+        <v>1105.326</v>
       </c>
       <c r="CD51" t="n">
-        <v>1064.25</v>
+        <v>1064.0825</v>
       </c>
       <c r="CE51" t="n">
-        <v>1071.88</v>
+        <v>1071.7113</v>
       </c>
       <c r="CF51" t="n">
-        <v>933.5086</v>
+        <v>933.3617</v>
       </c>
       <c r="CG51" t="n">
-        <v>652.5792</v>
+        <v>652.4765</v>
       </c>
       <c r="CI51" t="inlineStr">
         <is>
@@ -20287,7 +20380,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S52" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
@@ -20316,7 +20409,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC52" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -20462,22 +20555,22 @@
         </is>
       </c>
       <c r="CB52" t="n">
-        <v>1049.75</v>
+        <v>1049.5848</v>
       </c>
       <c r="CC52" t="n">
-        <v>1081.04</v>
+        <v>1080.8699</v>
       </c>
       <c r="CD52" t="n">
-        <v>1044</v>
+        <v>1043.8357</v>
       </c>
       <c r="CE52" t="n">
-        <v>1080.53</v>
+        <v>1080.36</v>
       </c>
       <c r="CF52" t="n">
-        <v>937.0336</v>
+        <v>936.8862</v>
       </c>
       <c r="CG52" t="n">
-        <v>656.7969000000001</v>
+        <v>656.6935</v>
       </c>
       <c r="CI52" t="inlineStr">
         <is>
@@ -20560,7 +20653,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S53" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
@@ -20589,7 +20682,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC53" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
@@ -20735,22 +20828,22 @@
         </is>
       </c>
       <c r="CB53" t="n">
-        <v>1095.83</v>
+        <v>1095.6575</v>
       </c>
       <c r="CC53" t="n">
-        <v>1108.72</v>
+        <v>1108.5455</v>
       </c>
       <c r="CD53" t="n">
-        <v>1073</v>
+        <v>1072.8312</v>
       </c>
       <c r="CE53" t="n">
-        <v>1082.28</v>
+        <v>1082.1097</v>
       </c>
       <c r="CF53" t="n">
-        <v>941.6152</v>
+        <v>941.467</v>
       </c>
       <c r="CG53" t="n">
-        <v>660.9749</v>
+        <v>660.8709</v>
       </c>
       <c r="CI53" t="inlineStr">
         <is>
@@ -20833,7 +20926,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S54" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U54" t="inlineStr">
         <is>
@@ -20862,7 +20955,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC54" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
@@ -21008,22 +21101,22 @@
         </is>
       </c>
       <c r="CB54" t="n">
-        <v>1075.98</v>
+        <v>1075.8106</v>
       </c>
       <c r="CC54" t="n">
-        <v>1084.8101</v>
+        <v>1084.6393</v>
       </c>
       <c r="CD54" t="n">
-        <v>1032</v>
+        <v>1031.8376</v>
       </c>
       <c r="CE54" t="n">
-        <v>1053.98</v>
+        <v>1053.8141</v>
       </c>
       <c r="CF54" t="n">
-        <v>945.7157999999999</v>
+        <v>945.567</v>
       </c>
       <c r="CG54" t="n">
-        <v>664.9838999999999</v>
+        <v>664.8792999999999</v>
       </c>
       <c r="CI54" t="inlineStr">
         <is>
@@ -21106,7 +21199,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S55" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
@@ -21135,7 +21228,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC55" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
@@ -21281,22 +21374,22 @@
         </is>
       </c>
       <c r="CB55" t="n">
-        <v>1076.6899</v>
+        <v>1076.5205</v>
       </c>
       <c r="CC55" t="n">
-        <v>1082.66</v>
+        <v>1082.4897</v>
       </c>
       <c r="CD55" t="n">
-        <v>1057.7</v>
+        <v>1057.5335</v>
       </c>
       <c r="CE55" t="n">
-        <v>1065.08</v>
+        <v>1064.9124</v>
       </c>
       <c r="CF55" t="n">
-        <v>949.7082</v>
+        <v>949.5588</v>
       </c>
       <c r="CG55" t="n">
-        <v>668.9921000000001</v>
+        <v>668.8868</v>
       </c>
       <c r="CI55" t="inlineStr">
         <is>
@@ -21379,7 +21472,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S56" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
@@ -21408,7 +21501,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC56" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
@@ -21554,22 +21647,22 @@
         </is>
       </c>
       <c r="CB56" t="n">
-        <v>1076.76</v>
+        <v>1076.5906</v>
       </c>
       <c r="CC56" t="n">
-        <v>1083.5</v>
+        <v>1083.3295</v>
       </c>
       <c r="CD56" t="n">
-        <v>1062.36</v>
+        <v>1062.1928</v>
       </c>
       <c r="CE56" t="n">
-        <v>1065.11</v>
+        <v>1064.9424</v>
       </c>
       <c r="CF56" t="n">
-        <v>951.5940000000001</v>
+        <v>951.4443</v>
       </c>
       <c r="CG56" t="n">
-        <v>673.0266</v>
+        <v>672.9207</v>
       </c>
       <c r="CI56" t="inlineStr">
         <is>
@@ -21652,7 +21745,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S57" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
@@ -21681,7 +21774,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC57" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
@@ -21827,22 +21920,22 @@
         </is>
       </c>
       <c r="CB57" t="n">
-        <v>1054.08</v>
+        <v>1053.914</v>
       </c>
       <c r="CC57" t="n">
-        <v>1098.9</v>
+        <v>1098.7271</v>
       </c>
       <c r="CD57" t="n">
-        <v>1022.9</v>
+        <v>1022.739</v>
       </c>
       <c r="CE57" t="n">
-        <v>1097.39</v>
+        <v>1097.2173</v>
       </c>
       <c r="CF57" t="n">
-        <v>954.3522</v>
+        <v>954.202</v>
       </c>
       <c r="CG57" t="n">
-        <v>677.309</v>
+        <v>677.2024</v>
       </c>
       <c r="CI57" t="inlineStr">
         <is>
@@ -21925,7 +22018,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S58" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U58" t="inlineStr">
         <is>
@@ -21954,7 +22047,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC58" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE58" t="inlineStr">
         <is>
@@ -22100,22 +22193,22 @@
         </is>
       </c>
       <c r="CB58" t="n">
-        <v>1107.35</v>
+        <v>1107.1757</v>
       </c>
       <c r="CC58" t="n">
-        <v>1108</v>
+        <v>1107.8256</v>
       </c>
       <c r="CD58" t="n">
-        <v>1072.01</v>
+        <v>1071.8413</v>
       </c>
       <c r="CE58" t="n">
-        <v>1074.89</v>
+        <v>1074.7208</v>
       </c>
       <c r="CF58" t="n">
-        <v>956.0458</v>
+        <v>955.8954</v>
       </c>
       <c r="CG58" t="n">
-        <v>681.4971</v>
+        <v>681.3899</v>
       </c>
       <c r="CI58" t="inlineStr">
         <is>
@@ -22198,7 +22291,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S59" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
@@ -22227,7 +22320,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC59" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
@@ -22373,22 +22466,22 @@
         </is>
       </c>
       <c r="CB59" t="n">
-        <v>1069.6801</v>
+        <v>1069.5117</v>
       </c>
       <c r="CC59" t="n">
-        <v>1074.88</v>
+        <v>1074.7108</v>
       </c>
       <c r="CD59" t="n">
-        <v>1055.5601</v>
+        <v>1055.3939</v>
       </c>
       <c r="CE59" t="n">
-        <v>1063.96</v>
+        <v>1063.7925</v>
       </c>
       <c r="CF59" t="n">
-        <v>958.9059999999999</v>
+        <v>958.7551</v>
       </c>
       <c r="CG59" t="n">
-        <v>685.6555</v>
+        <v>685.5476</v>
       </c>
       <c r="CI59" t="inlineStr">
         <is>
@@ -22471,7 +22564,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S60" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U60" t="inlineStr">
         <is>
@@ -22500,7 +22593,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC60" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
@@ -22646,22 +22739,22 @@
         </is>
       </c>
       <c r="CB60" t="n">
-        <v>1064.48</v>
+        <v>1064.3125</v>
       </c>
       <c r="CC60" t="n">
-        <v>1074.3101</v>
+        <v>1074.141</v>
       </c>
       <c r="CD60" t="n">
-        <v>1045.26</v>
+        <v>1045.0955</v>
       </c>
       <c r="CE60" t="n">
-        <v>1045.5601</v>
+        <v>1045.3955</v>
       </c>
       <c r="CF60" t="n">
-        <v>961.8132000000001</v>
+        <v>961.6618</v>
       </c>
       <c r="CG60" t="n">
-        <v>689.7568</v>
+        <v>689.6482999999999</v>
       </c>
       <c r="CI60" t="inlineStr">
         <is>
@@ -22744,7 +22837,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S61" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
@@ -22773,7 +22866,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC61" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE61" t="inlineStr">
         <is>
@@ -22919,22 +23012,22 @@
         </is>
       </c>
       <c r="CB61" t="n">
-        <v>1017.37</v>
+        <v>1017.21</v>
       </c>
       <c r="CC61" t="n">
-        <v>1089.22</v>
+        <v>1089.0486</v>
       </c>
       <c r="CD61" t="n">
-        <v>1011.42</v>
+        <v>1011.2609</v>
       </c>
       <c r="CE61" t="n">
-        <v>1088</v>
+        <v>1087.8289</v>
       </c>
       <c r="CF61" t="n">
-        <v>967.1626</v>
+        <v>967.0104</v>
       </c>
       <c r="CG61" t="n">
-        <v>693.9553</v>
+        <v>693.8461</v>
       </c>
       <c r="CI61" t="inlineStr">
         <is>
@@ -23017,7 +23110,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S62" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U62" t="inlineStr">
         <is>
@@ -23046,7 +23139,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC62" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE62" t="inlineStr">
         <is>
@@ -23192,22 +23285,22 @@
         </is>
       </c>
       <c r="CB62" t="n">
-        <v>1077.5</v>
+        <v>1077.3305</v>
       </c>
       <c r="CC62" t="n">
-        <v>1088.5</v>
+        <v>1088.3288</v>
       </c>
       <c r="CD62" t="n">
-        <v>1032.1</v>
+        <v>1031.9376</v>
       </c>
       <c r="CE62" t="n">
-        <v>1035.84</v>
+        <v>1035.677</v>
       </c>
       <c r="CF62" t="n">
-        <v>973.0993999999999</v>
+        <v>972.9463</v>
       </c>
       <c r="CG62" t="n">
-        <v>697.8062</v>
+        <v>697.6964</v>
       </c>
       <c r="CI62" t="inlineStr">
         <is>
@@ -23290,7 +23383,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S63" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
@@ -23319,7 +23412,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC63" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
@@ -23465,22 +23558,22 @@
         </is>
       </c>
       <c r="CB63" t="n">
-        <v>1054.17</v>
+        <v>1054.0042</v>
       </c>
       <c r="CC63" t="n">
-        <v>1054.17</v>
+        <v>1054.0042</v>
       </c>
       <c r="CD63" t="n">
-        <v>1017</v>
+        <v>1016.84</v>
       </c>
       <c r="CE63" t="n">
-        <v>1029</v>
+        <v>1028.8381</v>
       </c>
       <c r="CF63" t="n">
-        <v>976.1862</v>
+        <v>976.0326</v>
       </c>
       <c r="CG63" t="n">
-        <v>701.5696</v>
+        <v>701.4592</v>
       </c>
       <c r="CI63" t="inlineStr">
         <is>
@@ -23563,7 +23656,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S64" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U64" t="inlineStr">
         <is>
@@ -23592,7 +23685,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC64" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
@@ -23738,22 +23831,22 @@
         </is>
       </c>
       <c r="CB64" t="n">
-        <v>1002.45</v>
+        <v>1002.2923</v>
       </c>
       <c r="CC64" t="n">
-        <v>1002.67</v>
+        <v>1002.5122</v>
       </c>
       <c r="CD64" t="n">
-        <v>978.5</v>
+        <v>978.346</v>
       </c>
       <c r="CE64" t="n">
-        <v>989.04</v>
+        <v>988.8843000000001</v>
       </c>
       <c r="CF64" t="n">
-        <v>979.5064</v>
+        <v>979.3523</v>
       </c>
       <c r="CG64" t="n">
-        <v>705.1348</v>
+        <v>705.0238000000001</v>
       </c>
       <c r="CI64" t="inlineStr">
         <is>
@@ -23836,7 +23929,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S65" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
@@ -23865,7 +23958,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC65" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
@@ -24011,22 +24104,22 @@
         </is>
       </c>
       <c r="CB65" t="n">
-        <v>934.0700000000001</v>
+        <v>933.9231</v>
       </c>
       <c r="CC65" t="n">
-        <v>953.6</v>
+        <v>953.4499</v>
       </c>
       <c r="CD65" t="n">
-        <v>929.03</v>
+        <v>928.8839</v>
       </c>
       <c r="CE65" t="n">
-        <v>953.1900000000001</v>
+        <v>953.04</v>
       </c>
       <c r="CF65" t="n">
-        <v>981.9802</v>
+        <v>981.8257</v>
       </c>
       <c r="CG65" t="n">
-        <v>708.4687</v>
+        <v>708.3572</v>
       </c>
       <c r="CI65" t="inlineStr">
         <is>
@@ -24059,10 +24152,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>545.15</v>
+        <v>545.27</v>
       </c>
       <c r="C66" t="n">
-        <v>545.74</v>
+        <v>545.75</v>
       </c>
       <c r="D66" t="n">
         <v>532.54</v>
@@ -24109,7 +24202,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S66" t="n">
-        <v>181.0371344430106</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U66" t="inlineStr">
         <is>
@@ -24138,7 +24231,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC66" t="n">
-        <v>43.73250225612095</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE66" t="inlineStr">
         <is>
@@ -24146,7 +24239,7 @@
         </is>
       </c>
       <c r="AF66" t="n">
-        <v>589.6525</v>
+        <v>589.5700000000001</v>
       </c>
       <c r="AG66" t="n">
         <v>591.88</v>
@@ -24192,22 +24285,22 @@
         </is>
       </c>
       <c r="AV66" t="n">
-        <v>83092.64840000001</v>
+        <v>83095.125</v>
       </c>
       <c r="AW66" t="n">
-        <v>84005.7188</v>
+        <v>84049.0625</v>
       </c>
       <c r="AX66" t="n">
-        <v>81469.35159999999</v>
+        <v>81345.88280000001</v>
       </c>
       <c r="AY66" t="n">
-        <v>81779.10159999999</v>
+        <v>81562.49219999999</v>
       </c>
       <c r="AZ66" t="n">
-        <v>81169.0453</v>
+        <v>81164.71309999999</v>
       </c>
       <c r="BA66" t="n">
-        <v>72206.0502</v>
+        <v>72204.96709999999</v>
       </c>
       <c r="BC66" t="inlineStr">
         <is>
@@ -24215,22 +24308,22 @@
         </is>
       </c>
       <c r="BD66" t="n">
-        <v>2496.2168</v>
+        <v>2496.6255</v>
       </c>
       <c r="BE66" t="n">
-        <v>2523.0505</v>
+        <v>2526.0706</v>
       </c>
       <c r="BF66" t="n">
-        <v>2408.7908</v>
+        <v>2403.2107</v>
       </c>
       <c r="BG66" t="n">
-        <v>2422.78</v>
+        <v>2418.207</v>
       </c>
       <c r="BH66" t="n">
-        <v>2555.6653</v>
+        <v>2555.5739</v>
       </c>
       <c r="BI66" t="n">
-        <v>2140.4701</v>
+        <v>2140.4473</v>
       </c>
       <c r="BK66" t="inlineStr">
         <is>
@@ -24270,13 +24363,13 @@
         <v>131.75</v>
       </c>
       <c r="BW66" t="n">
-        <v>131.81</v>
+        <v>131.78</v>
       </c>
       <c r="BX66" t="n">
-        <v>128.3144</v>
+        <v>128.3138</v>
       </c>
       <c r="BY66" t="n">
-        <v>120.3867</v>
+        <v>120.3865</v>
       </c>
       <c r="CA66" t="inlineStr">
         <is>
@@ -24284,22 +24377,22 @@
         </is>
       </c>
       <c r="CB66" t="n">
-        <v>934.3</v>
+        <v>934.5599999999999</v>
       </c>
       <c r="CC66" t="n">
         <v>949.42</v>
       </c>
       <c r="CD66" t="n">
-        <v>913.6</v>
+        <v>913.5599999999999</v>
       </c>
       <c r="CE66" t="n">
         <v>914.13</v>
       </c>
       <c r="CF66" t="n">
-        <v>982.4094</v>
+        <v>982.2577</v>
       </c>
       <c r="CG66" t="n">
-        <v>711.6168</v>
+        <v>711.5056</v>
       </c>
       <c r="CI66" t="inlineStr">
         <is>
@@ -24307,7 +24400,7 @@
         </is>
       </c>
       <c r="CJ66" t="n">
-        <v>576.41</v>
+        <v>576.49</v>
       </c>
       <c r="CK66" t="n">
         <v>580.08</v>
@@ -24449,169 +24542,169 @@
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="26" t="inlineStr">
+      <c r="B3" s="30" t="inlineStr">
         <is>
           <t>Elke kaars is één handelsdag; het dunne streepje loopt van de laagste naar de hoogste koers van die dag. Ga met de muis over een kaars of lijn om de waarde te zien.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="31" t="inlineStr">
         <is>
           <t>Hoeveel zijn de bots waard?</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="B6" s="28" t="inlineStr">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>Boven €10.000 = winst, eronder = verlies. De grijze stippellijn is wat je had gehad met gewoon de wereld-ETF kopen en vasthouden.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="26" customHeight="1">
-      <c r="B28" s="29" t="inlineStr">
+      <c r="B28" s="33" t="inlineStr">
         <is>
           <t>Trend-agent: open posities</t>
         </is>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="B29" s="27" t="inlineStr">
+      <c r="B29" s="31" t="inlineStr">
         <is>
           <t>Microsoft (MSFT)  ·  533,69 USD</t>
         </is>
       </c>
-      <c r="D29" s="27" t="inlineStr">
+      <c r="D29" s="31" t="inlineStr">
         <is>
           <t>SAP (SAP.DE)  ·  196,94 EUR</t>
         </is>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
-      <c r="B30" s="30" t="inlineStr">
+      <c r="B30" s="34" t="inlineStr">
         <is>
           <t>Gestegen: 35,2% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: -0,3% (verlies). De bot verkoopt als de koers onder 509,90 zakt (-4,5%).</t>
         </is>
       </c>
-      <c r="D30" s="30" t="inlineStr">
-        <is>
-          <t>Gestegen: 43,1% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +2,8% (winst). De bot verkoopt als de koers onder 181,04 zakt (-8,1%).</t>
+      <c r="D30" s="34" t="inlineStr">
+        <is>
+          <t>Gestegen: 43,1% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +2,8% (winst). De bot verkoopt als de koers onder 181,20 zakt (-8,0%).</t>
         </is>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1">
-      <c r="B50" s="27" t="inlineStr">
+      <c r="B50" s="31" t="inlineStr">
         <is>
           <t>Shell (SHELL.AS)  ·  46,46 EUR</t>
         </is>
       </c>
     </row>
     <row r="51" ht="30" customHeight="1">
-      <c r="B51" s="30" t="inlineStr">
-        <is>
-          <t>Gestegen: 26,0% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +3,1% (winst). De bot verkoopt als de koers onder 43,73 zakt (-5,9%).</t>
+      <c r="B51" s="34" t="inlineStr">
+        <is>
+          <t>Gestegen: 26,0% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +3,1% (winst). De bot verkoopt als de koers onder 43,70 zakt (-5,9%).</t>
         </is>
       </c>
     </row>
     <row r="72" ht="26" customHeight="1">
-      <c r="B72" s="29" t="inlineStr">
+      <c r="B72" s="33" t="inlineStr">
         <is>
           <t>Investeerder: beleggingen</t>
         </is>
       </c>
     </row>
     <row r="73" ht="22" customHeight="1">
-      <c r="B73" s="27" t="inlineStr">
+      <c r="B73" s="31" t="inlineStr">
         <is>
           <t>AMD (AMD)  ·  570,82 USD</t>
         </is>
       </c>
-      <c r="D73" s="27" t="inlineStr">
+      <c r="D73" s="31" t="inlineStr">
         <is>
           <t>ASML (ASML.AS)  ·  1.528,20 EUR</t>
         </is>
       </c>
     </row>
     <row r="74" ht="30" customHeight="1">
-      <c r="B74" s="30" t="inlineStr">
+      <c r="B74" s="34" t="inlineStr">
         <is>
           <t>Gestegen: 7,9% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden.</t>
         </is>
       </c>
-      <c r="D74" s="30" t="inlineStr">
+      <c r="D74" s="34" t="inlineStr">
         <is>
           <t>Gedaald: -4,3% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden.</t>
         </is>
       </c>
     </row>
     <row r="94" ht="22" customHeight="1">
-      <c r="B94" s="27" t="inlineStr">
-        <is>
-          <t>Bitcoin (BTC-USD)  ·  81.779,10 USD</t>
-        </is>
-      </c>
-      <c r="D94" s="27" t="inlineStr">
-        <is>
-          <t>Ethereum (ETH-USD)  ·  2.422,78 USD</t>
+      <c r="B94" s="31" t="inlineStr">
+        <is>
+          <t>Bitcoin (BTC-USD)  ·  81.562,49 USD</t>
+        </is>
+      </c>
+      <c r="D94" s="31" t="inlineStr">
+        <is>
+          <t>Ethereum (ETH-USD)  ·  2.418,21 USD</t>
         </is>
       </c>
     </row>
     <row r="95" ht="30" customHeight="1">
-      <c r="B95" s="30" t="inlineStr">
-        <is>
-          <t>Gestegen: 28,7% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden.</t>
-        </is>
-      </c>
-      <c r="D95" s="30" t="inlineStr">
-        <is>
-          <t>Gestegen: 28,8% in de laatste 3 maanden. Trend verzwakt: de koers is onder het 50-daags gemiddelde gezakt.</t>
+      <c r="B95" s="34" t="inlineStr">
+        <is>
+          <t>Gestegen: 28,3% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden.</t>
+        </is>
+      </c>
+      <c r="D95" s="34" t="inlineStr">
+        <is>
+          <t>Gestegen: 28,5% in de laatste 3 maanden. Trend verzwakt: de koers is onder het 50-daags gemiddelde gezakt.</t>
         </is>
       </c>
     </row>
     <row r="115" ht="22" customHeight="1">
-      <c r="B115" s="27" t="inlineStr">
+      <c r="B115" s="31" t="inlineStr">
         <is>
           <t>Infineon (IFX.DE)  ·  55,35 EUR</t>
         </is>
       </c>
-      <c r="D115" s="27" t="inlineStr">
-        <is>
-          <t>iShares MSCI World (IWDA.AS)  ·  131,81 EUR</t>
+      <c r="D115" s="31" t="inlineStr">
+        <is>
+          <t>iShares MSCI World (IWDA.AS)  ·  131,78 EUR</t>
         </is>
       </c>
     </row>
     <row r="116" ht="30" customHeight="1">
-      <c r="B116" s="30" t="inlineStr">
+      <c r="B116" s="34" t="inlineStr">
         <is>
           <t>Gedaald: -14,5% in de laatste 3 maanden. Trend verzwakt: de koers is onder het 50-daags gemiddelde gezakt.</t>
         </is>
       </c>
-      <c r="D116" s="30" t="inlineStr">
+      <c r="D116" s="34" t="inlineStr">
         <is>
           <t>Gestegen: 4,4% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden.</t>
         </is>
       </c>
     </row>
     <row r="136" ht="22" customHeight="1">
-      <c r="B136" s="27" t="inlineStr">
+      <c r="B136" s="31" t="inlineStr">
         <is>
           <t>Micron (MU)  ·  914,13 USD</t>
         </is>
       </c>
-      <c r="D136" s="27" t="inlineStr">
+      <c r="D136" s="31" t="inlineStr">
         <is>
           <t>Halfgeleider-ETF (SMH)  ·  564,74 USD</t>
         </is>
       </c>
     </row>
     <row r="137" ht="30" customHeight="1">
-      <c r="B137" s="30" t="inlineStr">
+      <c r="B137" s="34" t="inlineStr">
         <is>
           <t>Gestegen: 1,1% in de laatste 3 maanden. Trend verzwakt: de koers is onder het 50-daags gemiddelde gezakt.</t>
         </is>
       </c>
-      <c r="D137" s="30" t="inlineStr">
+      <c r="D137" s="34" t="inlineStr">
         <is>
           <t>Gedaald: -4,4% in de laatste 3 maanden. Trend verzwakt: de koers is onder het 50-daags gemiddelde gezakt.</t>
         </is>
@@ -24630,6 +24723,481 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="B1:H24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="15" t="inlineStr">
+        <is>
+          <t>Wat de grafieken laten zien</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="21.4" customHeight="1">
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>• 7 van de 11 grafieken staan in een stijgende trend, 0 in een dalende, 4 zonder duidelijke richting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="21.4" customHeight="1">
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>• Sterkste van de laatste maand: AMD (+13,2%); zwakste: Ethereum (-9,9%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="21.4" customHeight="1">
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>• Afgelopen week: 4 van de 11 gestegen, gemiddeld -3,8%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="21.4" customHeight="1">
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>• Op of vlak bij hun hoogste punt van 3 maanden: Microsoft, SAP, Shell, iShares MSCI World.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="21.4" customHeight="1">
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>• Terugval binnen een stijgende trend: AMD, ASML.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="21.4" customHeight="1">
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>• Net onder het 50-daags gemiddelde gezakt (voor de trend-agent een verkoopsignaal): ASML, Infineon, Micron, Halfgeleider-ETF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="21.4" customHeight="1">
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>• Dit beschrijft wat er gebeurd is; het voorspelt niet wat de koersen morgen doen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>Aandeel</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>Trend</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
+        <is>
+          <t>Maand</t>
+        </is>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t>3 maanden</t>
+        </is>
+      </c>
+      <c r="G11" s="16" t="inlineStr">
+        <is>
+          <t>Opvallend</t>
+        </is>
+      </c>
+      <c r="H11" s="16" t="inlineStr">
+        <is>
+          <t>Samenvatting</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="67.8" customHeight="1">
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>Microsoft (MSFT)</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>stijgend</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="n">
+        <v>0.0074</v>
+      </c>
+      <c r="E12" s="19" t="n">
+        <v>0.0736</v>
+      </c>
+      <c r="F12" s="19" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="G12" s="17" t="inlineStr">
+        <is>
+          <t>nieuwe 3-maands top · 50-daags gemiddelde kruiste omhoog door het 200-daagse op 28 aug</t>
+        </is>
+      </c>
+      <c r="H12" s="17" t="inlineStr">
+        <is>
+          <t>Stijgende trend: +35,2% in 3 maanden, +7,4% in de laatste maand en +0,7% in de laatste week. Het 50-daags gemiddelde loopt nog op. Opvallend: nieuwe 3-maands top; 50-daags gemiddelde kruiste omhoog door het 200-daagse op 28 aug.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="67.8" customHeight="1">
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>SAP (SAP.DE)</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>stijgend</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="n">
+        <v>0.0497</v>
+      </c>
+      <c r="E13" s="19" t="n">
+        <v>0.0527</v>
+      </c>
+      <c r="F13" s="19" t="n">
+        <v>0.4308</v>
+      </c>
+      <c r="G13" s="17" t="inlineStr">
+        <is>
+          <t>nieuwe 3-maands top · 50-daags gemiddelde kruiste omhoog door het 200-daagse op 14 sep</t>
+        </is>
+      </c>
+      <c r="H13" s="17" t="inlineStr">
+        <is>
+          <t>Stijgende trend: +43,1% in 3 maanden, +5,3% in de laatste maand en +5,0% in de laatste week. Het 50-daags gemiddelde loopt nog op. Opvallend: nieuwe 3-maands top; 50-daags gemiddelde kruiste omhoog door het 200-daagse op 14 sep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="67.8" customHeight="1">
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>Shell (SHELL.AS)</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>stijgend</t>
+        </is>
+      </c>
+      <c r="D14" s="19" t="n">
+        <v>0.0741</v>
+      </c>
+      <c r="E14" s="19" t="n">
+        <v>0.08790000000000001</v>
+      </c>
+      <c r="F14" s="19" t="n">
+        <v>0.2597</v>
+      </c>
+      <c r="G14" s="17" t="inlineStr">
+        <is>
+          <t>nieuwe 3-maands top · 10 dagen op rij gestegen · 9 van de laatste 10 dagen groen</t>
+        </is>
+      </c>
+      <c r="H14" s="17" t="inlineStr">
+        <is>
+          <t>Stijgende trend: +26,0% in 3 maanden, +8,8% in de laatste maand en +7,4% in de laatste week. Het 50-daags gemiddelde loopt nog op. Opvallend: nieuwe 3-maands top; 10 dagen op rij gestegen; 9 van de laatste 10 dagen groen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="51.85" customHeight="1">
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>AMD (AMD)</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>stijgend</t>
+        </is>
+      </c>
+      <c r="D15" s="19" t="n">
+        <v>-0.1162</v>
+      </c>
+      <c r="E15" s="19" t="n">
+        <v>0.1321</v>
+      </c>
+      <c r="F15" s="19" t="n">
+        <v>0.0788</v>
+      </c>
+      <c r="G15" s="17" t="inlineStr">
+        <is>
+          <t>terugval binnen een stijgende trend</t>
+        </is>
+      </c>
+      <c r="H15" s="17" t="inlineStr">
+        <is>
+          <t>Stijgende trend: +7,9% in 3 maanden, +13,2% in de laatste maand en -11,6% in de laatste week. Het 50-daags gemiddelde loopt nog op. Opvallend: terugval binnen een stijgende trend.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="67.8" customHeight="1">
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>ASML (ASML.AS)</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="inlineStr">
+        <is>
+          <t>stijgend</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="n">
+        <v>-0.0509</v>
+      </c>
+      <c r="E16" s="19" t="n">
+        <v>0.1084</v>
+      </c>
+      <c r="F16" s="19" t="n">
+        <v>-0.0428</v>
+      </c>
+      <c r="G16" s="17" t="inlineStr">
+        <is>
+          <t>net onder het 50-daags gemiddelde gezakt · net boven het 50-daags gemiddelde gestegen · terugval binnen een stijgende trend</t>
+        </is>
+      </c>
+      <c r="H16" s="17" t="inlineStr">
+        <is>
+          <t>Stijgende trend: -4,3% in 3 maanden, +10,8% in de laatste maand en -5,1% in de laatste week. Het 50-daags gemiddelde loopt nog op. Opvallend: net onder het 50-daags gemiddelde gezakt; net boven het 50-daags gemiddelde gestegen; terugval binnen een stijgende trend.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="51.85" customHeight="1">
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>Bitcoin (BTC-USD)</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>stijgend</t>
+        </is>
+      </c>
+      <c r="D17" s="19" t="n">
+        <v>-0.0119</v>
+      </c>
+      <c r="E17" s="19" t="n">
+        <v>-0.0334</v>
+      </c>
+      <c r="F17" s="19" t="n">
+        <v>0.2834</v>
+      </c>
+      <c r="G17" s="17" t="inlineStr">
+        <is>
+          <t>50-daags gemiddelde kruiste omhoog door het 200-daagse op 8 sep</t>
+        </is>
+      </c>
+      <c r="H17" s="17" t="inlineStr">
+        <is>
+          <t>Stijgende trend: +28,3% in 3 maanden, -3,3% in de laatste maand en -1,2% in de laatste week. Het 50-daags gemiddelde loopt nog op. Opvallend: 50-daags gemiddelde kruiste omhoog door het 200-daagse op 8 sep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="67.8" customHeight="1">
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>Ethereum (ETH-USD)</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>zijwaarts</t>
+        </is>
+      </c>
+      <c r="D18" s="19" t="n">
+        <v>-0.0271</v>
+      </c>
+      <c r="E18" s="19" t="n">
+        <v>-0.0993</v>
+      </c>
+      <c r="F18" s="19" t="n">
+        <v>0.2853</v>
+      </c>
+      <c r="G18" s="17" t="inlineStr">
+        <is>
+          <t>50-daags gemiddelde kruiste omhoog door het 200-daagse op 31 aug · beweegt de laatste 2 weken veel meer dan daarvoor</t>
+        </is>
+      </c>
+      <c r="H18" s="17" t="inlineStr">
+        <is>
+          <t>Geen duidelijke richting: +28,5% in 3 maanden, -9,9% in de laatste maand en -2,7% in de laatste week. Opvallend: 50-daags gemiddelde kruiste omhoog door het 200-daagse op 31 aug; beweegt de laatste 2 weken veel meer dan daarvoor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="51.85" customHeight="1">
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>Infineon (IFX.DE)</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>zijwaarts</t>
+        </is>
+      </c>
+      <c r="D19" s="19" t="n">
+        <v>-0.0919</v>
+      </c>
+      <c r="E19" s="19" t="n">
+        <v>0.0188</v>
+      </c>
+      <c r="F19" s="19" t="n">
+        <v>-0.1446</v>
+      </c>
+      <c r="G19" s="17" t="inlineStr">
+        <is>
+          <t>net onder het 50-daags gemiddelde gezakt · 6 dagen op rij gedaald</t>
+        </is>
+      </c>
+      <c r="H19" s="17" t="inlineStr">
+        <is>
+          <t>Geen duidelijke richting: -14,5% in 3 maanden, +1,9% in de laatste maand en -9,2% in de laatste week. Opvallend: net onder het 50-daags gemiddelde gezakt; 6 dagen op rij gedaald.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="51.85" customHeight="1">
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>iShares MSCI World (IWDA.AS)</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>stijgend</t>
+        </is>
+      </c>
+      <c r="D20" s="19" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="E20" s="19" t="n">
+        <v>0.0475</v>
+      </c>
+      <c r="F20" s="19" t="n">
+        <v>0.0437</v>
+      </c>
+      <c r="G20" s="17" t="inlineStr">
+        <is>
+          <t>nieuwe 3-maands top</t>
+        </is>
+      </c>
+      <c r="H20" s="17" t="inlineStr">
+        <is>
+          <t>Stijgende trend: +4,4% in 3 maanden, +4,7% in de laatste maand en +0,3% in de laatste week. Het 50-daags gemiddelde loopt nog op. Opvallend: nieuwe 3-maands top.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="51.85" customHeight="1">
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>Micron (MU)</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>zijwaarts</t>
+        </is>
+      </c>
+      <c r="D21" s="19" t="n">
+        <v>-0.1597</v>
+      </c>
+      <c r="E21" s="19" t="n">
+        <v>-0.0144</v>
+      </c>
+      <c r="F21" s="19" t="n">
+        <v>0.0111</v>
+      </c>
+      <c r="G21" s="17" t="inlineStr">
+        <is>
+          <t>net onder het 50-daags gemiddelde gezakt · 5 dagen op rij gedaald</t>
+        </is>
+      </c>
+      <c r="H21" s="17" t="inlineStr">
+        <is>
+          <t>Geen duidelijke richting: +1,1% in 3 maanden, -1,4% in de laatste maand en -16,0% in de laatste week. Opvallend: net onder het 50-daags gemiddelde gezakt; 5 dagen op rij gedaald.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="51.85" customHeight="1">
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>Halfgeleider-ETF (SMH)</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>zijwaarts</t>
+        </is>
+      </c>
+      <c r="D22" s="19" t="n">
+        <v>-0.0965</v>
+      </c>
+      <c r="E22" s="19" t="n">
+        <v>0.0417</v>
+      </c>
+      <c r="F22" s="19" t="n">
+        <v>-0.0441</v>
+      </c>
+      <c r="G22" s="17" t="inlineStr">
+        <is>
+          <t>net onder het 50-daags gemiddelde gezakt · 7 dagen op rij gedaald · grote beweging op de laatste dag (-4,0%) · veel handel op de laatste dag (1,9x normaal)</t>
+        </is>
+      </c>
+      <c r="H22" s="17" t="inlineStr">
+        <is>
+          <t>Geen duidelijke richting: -4,4% in 3 maanden, +4,2% in de laatste maand en -9,6% in de laatste week. Opvallend: net onder het 50-daags gemiddelde gezakt; 7 dagen op rij gedaald; grote beweging op de laatste dag (-4,0%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>Dit beschrijft wat er gebeurd is; het voorspelt niet wat de koersen morgen doen. De bots gebruiken het niet om te beslissen.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B6:H6"/>
+    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B5:H5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -24639,340 +25207,340 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>Bot</t>
         </is>
       </c>
-      <c r="B1" s="15" t="inlineStr">
+      <c r="B1" s="21" t="inlineStr">
         <is>
           <t>Onderdeel</t>
         </is>
       </c>
-      <c r="C1" s="15" t="inlineStr">
+      <c r="C1" s="21" t="inlineStr">
         <is>
           <t>Wat de bot zag of concludeert</t>
         </is>
       </c>
     </row>
     <row r="2" ht="19.95" customHeight="1">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="B2" s="16" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>Markt (IWDA.AS)</t>
         </is>
       </c>
-      <c r="C2" s="16" t="inlineStr">
-        <is>
-          <t>koers 131,81, 9,5% boven het 200-daags gemiddelde (120,39); de afgelopen maand +4,8%. Trend: stijgend.</t>
+      <c r="C2" s="17" t="inlineStr">
+        <is>
+          <t>koers 131,78, 9,5% boven het 200-daags gemiddelde (120,39); de afgelopen maand +4,8%. Trend: stijgend.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19.95" customHeight="1">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>Beweeglijkheid</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="C3" s="17" t="inlineStr">
         <is>
           <t>8% op jaarbasis, tegen normaal 10% het afgelopen jaar: laag.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="19.95" customHeight="1">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>Breedte</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>35 van de 50 instrumenten staan boven hun 200-daags gemiddelde (70%; EU 13 van 23, US 22 van 27).</t>
         </is>
       </c>
     </row>
     <row r="5" ht="51.85" customHeight="1">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>Sterkste momentum nu (12 maanden, zonder laatste maand)</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>Micron +382%, AMD +133%, CrowdStrike +91%, Palo Alto Networks +76%, ING +63%.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="19.95" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>BTC-USD</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>13,3% boven het 200-daags gemiddelde (mag in de mix).</t>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>13,0% boven het 200-daags gemiddelde (mag in de mix).</t>
         </is>
       </c>
     </row>
     <row r="7" ht="19.95" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>ETH-USD</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>13,2% boven het 200-daags gemiddelde (mag in de mix).</t>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>13,0% boven het 200-daags gemiddelde (mag in de mix).</t>
         </is>
       </c>
     </row>
     <row r="8" ht="19.95" customHeight="1">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>Conclusie</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>De markt stijgt: de kern (wereld-ETF) doet zijn werk, de sterkste aandelen lopen mee.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="35.9" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>Conclusie</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>Uit de top gevallen: ASML.AS, IFX.DE, SMH. Blijft dat zo, dan worden ze bij de volgende herverdeling (eerste handelsdag van 2026-11) vervangen door CRWD, PANW, INGA.AS.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="19.95" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>Markt (IWDA.AS)</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>koers 131,81, 9,5% boven het 200-daags gemiddelde (120,39); de afgelopen maand +4,8%. Trend: stijgend.</t>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>koers 131,78, 9,5% boven het 200-daags gemiddelde (120,39); de afgelopen maand +4,8%. Trend: stijgend.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="19.95" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>Beweeglijkheid</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>8% op jaarbasis, tegen normaal 10% het afgelopen jaar: laag.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="19.95" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>Breedte</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>35 van de 50 instrumenten staan boven hun 200-daags gemiddelde (70%; EU 13 van 23, US 22 van 27).</t>
         </is>
       </c>
     </row>
     <row r="13" ht="19.95" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>Bekeken</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>50 instrumenten.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="51.85" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>Afgevallen (een instrument kan op meer regels afvallen)</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>geen stijgende trend (koers niet boven 50- en 200-daags gemiddelde): 26; niet gestegen over 1 of 3 maanden: 27; te weinig handel: 1.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="19.95" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>Door de zeef</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>18. Koopbare trends: 18.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="19.95" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>Conclusie</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>De markt stijgt breed: goede omstandigheden voor trendvolgen.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="19.95" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>Conclusie</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>De markt is rustig: stops liggen dichterbij, posities kunnen iets groter.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="19.95" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>Conclusie</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>Amerika staat er duidelijk beter voor dan Europa (81% tegen 57% in een stijgende trend).</t>
         </is>
       </c>
     </row>
     <row r="19" ht="35.9" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>Conclusie</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C19" s="17" t="inlineStr">
         <is>
           <t>3 van de 5 sterkste staan al ver boven hun gemiddelde (SHELL.AS, WKL.AS, XOM): de trend is sterk, maar instappen op zo'n moment kost vaker een terugval.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="19.95" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>Conclusie</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>Alle plekken zijn bezet, dus de bot koopt niets bij, hoe sterk een trend ook is.</t>
         </is>
@@ -24984,7 +25552,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -25006,64 +25574,64 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>Bot</t>
         </is>
       </c>
-      <c r="B1" s="15" t="inlineStr">
+      <c r="B1" s="21" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C1" s="15" t="inlineStr">
+      <c r="C1" s="21" t="inlineStr">
         <is>
           <t>Instap</t>
         </is>
       </c>
-      <c r="D1" s="15" t="inlineStr">
+      <c r="D1" s="21" t="inlineStr">
         <is>
           <t>Koers nu</t>
         </is>
       </c>
-      <c r="E1" s="15" t="inlineStr">
+      <c r="E1" s="21" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="F1" s="15" t="inlineStr">
+      <c r="F1" s="21" t="inlineStr">
         <is>
           <t>Resultaat €</t>
         </is>
       </c>
-      <c r="G1" s="15" t="inlineStr">
+      <c r="G1" s="21" t="inlineStr">
         <is>
           <t>Resultaat %</t>
         </is>
       </c>
-      <c r="H1" s="15" t="inlineStr">
+      <c r="H1" s="21" t="inlineStr">
         <is>
           <t>Afstand tot stop</t>
         </is>
       </c>
-      <c r="I1" s="15" t="inlineStr">
+      <c r="I1" s="21" t="inlineStr">
         <is>
           <t>Als de stop geraakt wordt €</t>
         </is>
       </c>
-      <c r="J1" s="15" t="inlineStr">
+      <c r="J1" s="21" t="inlineStr">
         <is>
           <t>In gewone taal</t>
         </is>
       </c>
     </row>
     <row r="2" ht="35.9" customHeight="1">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B2" s="16" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>SHELL.AS</t>
         </is>
@@ -25075,33 +25643,33 @@
         <v>46.455</v>
       </c>
       <c r="E2" t="n">
-        <v>43.7325</v>
-      </c>
-      <c r="F2" s="17" t="n">
+        <v>43.6975</v>
+      </c>
+      <c r="F2" s="22" t="n">
         <v>18.17</v>
       </c>
-      <c r="G2" s="18" t="n">
+      <c r="G2" s="23" t="n">
         <v>0.031</v>
       </c>
-      <c r="H2" s="19" t="n">
-        <v>0.0623</v>
-      </c>
-      <c r="I2" s="17" t="n">
-        <v>-18.23</v>
-      </c>
-      <c r="J2" s="16" t="inlineStr">
-        <is>
-          <t>Staat €18,17 in de plus. Zakt de koers 6,2% naar 43,73, dan verkoopt de bot met ongeveer €18,23 verlies.</t>
+      <c r="H2" s="24" t="n">
+        <v>0.0631</v>
+      </c>
+      <c r="I2" s="22" t="n">
+        <v>-18.68</v>
+      </c>
+      <c r="J2" s="17" t="inlineStr">
+        <is>
+          <t>Staat €18,17 in de plus. Zakt de koers 6,3% naar 43,70, dan verkoopt de bot met ongeveer €18,68 verlies.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="35.9" customHeight="1">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>SAP.DE</t>
         </is>
@@ -25113,33 +25681,33 @@
         <v>196.94</v>
       </c>
       <c r="E3" t="n">
-        <v>181.0371</v>
-      </c>
-      <c r="F3" s="17" t="n">
+        <v>181.1971</v>
+      </c>
+      <c r="F3" s="22" t="n">
         <v>10.77</v>
       </c>
-      <c r="G3" s="18" t="n">
+      <c r="G3" s="23" t="n">
         <v>0.0281</v>
       </c>
-      <c r="H3" s="19" t="n">
-        <v>0.0878</v>
-      </c>
-      <c r="I3" s="17" t="n">
-        <v>-22.04</v>
-      </c>
-      <c r="J3" s="16" t="inlineStr">
-        <is>
-          <t>Staat €10,77 in de plus. Zakt de koers 8,8% naar 181,04, dan verkoopt de bot met ongeveer €22,04 verlies.</t>
+      <c r="H3" s="24" t="n">
+        <v>0.08690000000000001</v>
+      </c>
+      <c r="I3" s="22" t="n">
+        <v>-21.72</v>
+      </c>
+      <c r="J3" s="17" t="inlineStr">
+        <is>
+          <t>Staat €10,77 in de plus. Zakt de koers 8,7% naar 181,20, dan verkoopt de bot met ongeveer €21,72 verlies.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="35.9" customHeight="1">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>MSFT</t>
         </is>
@@ -25153,70 +25721,70 @@
       <c r="E4" t="n">
         <v>509.899</v>
       </c>
-      <c r="F4" s="17" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="G4" s="18" t="n">
+      <c r="F4" s="22" t="n">
+        <v>-1.79</v>
+      </c>
+      <c r="G4" s="23" t="n">
         <v>-0.0031</v>
       </c>
-      <c r="H4" s="19" t="n">
+      <c r="H4" s="24" t="n">
         <v>0.0467</v>
       </c>
-      <c r="I4" s="17" t="n">
-        <v>-21.71</v>
-      </c>
-      <c r="J4" s="16" t="inlineStr">
-        <is>
-          <t>Staat €0,61 in de plus. Zakt de koers 4,7% naar 509,90, dan verkoopt de bot met ongeveer €21,71 verlies.</t>
+      <c r="I4" s="22" t="n">
+        <v>-24.01</v>
+      </c>
+      <c r="J4" s="17" t="inlineStr">
+        <is>
+          <t>Staat €1,79 in de min. Zakt de koers 4,7% naar 509,90, dan verkoopt de bot met ongeveer €24,01 verlies.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1"/>
     <row r="6" ht="35.9" customHeight="1">
-      <c r="A6" s="20" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>Trend-agent remmen</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>Nu</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>Grens</t>
         </is>
       </c>
     </row>
     <row r="7" ht="35.9" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>Daling vanaf top</t>
         </is>
       </c>
-      <c r="B7" s="19" t="n">
+      <c r="B7" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="19" t="n">
+      <c r="C7" s="24" t="n">
         <v>-0.05</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>Vandaag</t>
         </is>
       </c>
-      <c r="B8" s="19" t="n">
-        <v>0.0012</v>
-      </c>
-      <c r="C8" s="19" t="n">
+      <c r="B8" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C8" s="24" t="n">
         <v>-0.01</v>
       </c>
     </row>
     <row r="9" ht="35.9" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>Verliestrades op rij</t>
         </is>
@@ -25230,195 +25798,195 @@
     </row>
     <row r="10" ht="18" customHeight="1"/>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="25" t="inlineStr">
         <is>
           <t>Instrument</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="C11" s="25" t="inlineStr">
         <is>
           <t>Waarde</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="25" t="inlineStr">
         <is>
           <t>Ingelegd</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
+      <c r="E11" s="25" t="inlineStr">
         <is>
           <t>Resultaat €</t>
         </is>
       </c>
-      <c r="F11" s="20" t="inlineStr">
+      <c r="F11" s="25" t="inlineStr">
         <is>
           <t>Resultaat %</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="16" t="inlineStr"/>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr"/>
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>MU</t>
         </is>
       </c>
-      <c r="C12" s="21" t="n">
-        <v>554.47</v>
-      </c>
-      <c r="D12" s="21" t="n">
+      <c r="C12" s="26" t="n">
+        <v>551.62</v>
+      </c>
+      <c r="D12" s="26" t="n">
         <v>600</v>
       </c>
-      <c r="E12" s="17" t="n">
-        <v>-45.53</v>
-      </c>
-      <c r="F12" s="18" t="n">
-        <v>-0.0759</v>
+      <c r="E12" s="22" t="n">
+        <v>-48.38</v>
+      </c>
+      <c r="F12" s="23" t="n">
+        <v>-0.0806</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="16" t="inlineStr"/>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr"/>
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>IFX.DE</t>
         </is>
       </c>
-      <c r="C13" s="21" t="n">
+      <c r="C13" s="26" t="n">
         <v>563</v>
       </c>
-      <c r="D13" s="21" t="n">
+      <c r="D13" s="26" t="n">
         <v>600</v>
       </c>
-      <c r="E13" s="17" t="n">
+      <c r="E13" s="22" t="n">
         <v>-37</v>
       </c>
-      <c r="F13" s="18" t="n">
+      <c r="F13" s="23" t="n">
         <v>-0.0617</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="16" t="inlineStr"/>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>ASML.AS</t>
-        </is>
-      </c>
-      <c r="C14" s="21" t="n">
-        <v>571.26</v>
-      </c>
-      <c r="D14" s="21" t="n">
+      <c r="A14" s="17" t="inlineStr"/>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>SMH</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="n">
+        <v>570.3200000000001</v>
+      </c>
+      <c r="D14" s="26" t="n">
         <v>600</v>
       </c>
-      <c r="E14" s="17" t="n">
-        <v>-28.74</v>
-      </c>
-      <c r="F14" s="18" t="n">
-        <v>-0.0479</v>
+      <c r="E14" s="22" t="n">
+        <v>-29.68</v>
+      </c>
+      <c r="F14" s="23" t="n">
+        <v>-0.0495</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="16" t="inlineStr"/>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>SMH</t>
-        </is>
-      </c>
-      <c r="C15" s="21" t="n">
-        <v>573.26</v>
-      </c>
-      <c r="D15" s="21" t="n">
+      <c r="A15" s="17" t="inlineStr"/>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>ASML.AS</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="n">
+        <v>571.26</v>
+      </c>
+      <c r="D15" s="26" t="n">
         <v>600</v>
       </c>
-      <c r="E15" s="17" t="n">
-        <v>-26.74</v>
-      </c>
-      <c r="F15" s="18" t="n">
-        <v>-0.0446</v>
+      <c r="E15" s="22" t="n">
+        <v>-28.74</v>
+      </c>
+      <c r="F15" s="23" t="n">
+        <v>-0.0479</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="16" t="inlineStr"/>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr"/>
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>AMD</t>
         </is>
       </c>
-      <c r="C16" s="21" t="n">
-        <v>576.26</v>
-      </c>
-      <c r="D16" s="21" t="n">
+      <c r="C16" s="26" t="n">
+        <v>573.3</v>
+      </c>
+      <c r="D16" s="26" t="n">
         <v>600</v>
       </c>
-      <c r="E16" s="17" t="n">
-        <v>-23.74</v>
-      </c>
-      <c r="F16" s="18" t="n">
-        <v>-0.0396</v>
+      <c r="E16" s="22" t="n">
+        <v>-26.7</v>
+      </c>
+      <c r="F16" s="23" t="n">
+        <v>-0.0445</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="16" t="inlineStr"/>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr"/>
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>ETH-USD</t>
         </is>
       </c>
-      <c r="C17" s="21" t="n">
-        <v>487.99</v>
-      </c>
-      <c r="D17" s="21" t="n">
+      <c r="C17" s="26" t="n">
+        <v>484.57</v>
+      </c>
+      <c r="D17" s="26" t="n">
         <v>500</v>
       </c>
-      <c r="E17" s="17" t="n">
-        <v>-12.01</v>
-      </c>
-      <c r="F17" s="18" t="n">
-        <v>-0.024</v>
+      <c r="E17" s="22" t="n">
+        <v>-15.43</v>
+      </c>
+      <c r="F17" s="23" t="n">
+        <v>-0.0309</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="16" t="inlineStr"/>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr"/>
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>BTC-USD</t>
         </is>
       </c>
-      <c r="C18" s="21" t="n">
-        <v>494.08</v>
-      </c>
-      <c r="D18" s="21" t="n">
+      <c r="C18" s="26" t="n">
+        <v>490.24</v>
+      </c>
+      <c r="D18" s="26" t="n">
         <v>500</v>
       </c>
-      <c r="E18" s="17" t="n">
-        <v>-5.92</v>
-      </c>
-      <c r="F18" s="18" t="n">
-        <v>-0.0118</v>
+      <c r="E18" s="22" t="n">
+        <v>-9.76</v>
+      </c>
+      <c r="F18" s="23" t="n">
+        <v>-0.0195</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="16" t="inlineStr"/>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="A19" s="17" t="inlineStr"/>
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>IWDA.AS</t>
         </is>
       </c>
-      <c r="C19" s="21" t="n">
-        <v>6000.38</v>
-      </c>
-      <c r="D19" s="21" t="n">
+      <c r="C19" s="26" t="n">
+        <v>5999.01</v>
+      </c>
+      <c r="D19" s="26" t="n">
         <v>6000</v>
       </c>
-      <c r="E19" s="17" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="F19" s="18" t="n">
-        <v>0.0001</v>
+      <c r="E19" s="22" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="F19" s="23" t="n">
+        <v>-0.0002</v>
       </c>
     </row>
   </sheetData>
@@ -25427,7 +25995,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -25442,7 +26010,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="22" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Kansen: wat de trend-agent vandaag het sterkst vond</t>
         </is>
@@ -25463,7 +26031,7 @@
       </c>
     </row>
     <row r="5" ht="38.8" customHeight="1">
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>Instapmoment</t>
         </is>
@@ -25475,7 +26043,7 @@
       </c>
     </row>
     <row r="6" ht="56.2" customHeight="1">
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>Waarom sterk</t>
         </is>
@@ -25487,19 +26055,19 @@
       </c>
     </row>
     <row r="7" ht="38.8" customHeight="1">
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>Plan van de bot</t>
         </is>
       </c>
-      <c r="C7" s="25" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>Koop 13 stuks rond 46,48 EUR (inzet €604,22). Stop-loss op 44,66 EUR (-3,9%). Gaat het mis, dan is het verlies ongeveer €25,59.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="21.4" customHeight="1">
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>Wat deed de bot?</t>
         </is>
@@ -25518,7 +26086,7 @@
       </c>
     </row>
     <row r="11" ht="21.4" customHeight="1">
-      <c r="B11" s="24" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>Instapmoment</t>
         </is>
@@ -25530,7 +26098,7 @@
       </c>
     </row>
     <row r="12" ht="56.2" customHeight="1">
-      <c r="B12" s="24" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>Waarom sterk</t>
         </is>
@@ -25542,19 +26110,19 @@
       </c>
     </row>
     <row r="13" ht="38.8" customHeight="1">
-      <c r="B13" s="24" t="inlineStr">
+      <c r="B13" s="28" t="inlineStr">
         <is>
           <t>Plan van de bot</t>
         </is>
       </c>
-      <c r="C13" s="25" t="inlineStr">
+      <c r="C13" s="29" t="inlineStr">
         <is>
           <t>Koop 2 stuks rond 197,04 EUR (inzet €394,08). Stop-loss op 186,21 EUR (-5,5%). Gaat het mis, dan is het verlies ongeveer €23,66.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="21.4" customHeight="1">
-      <c r="B14" s="24" t="inlineStr">
+      <c r="B14" s="28" t="inlineStr">
         <is>
           <t>Wat deed de bot?</t>
         </is>
@@ -25573,7 +26141,7 @@
       </c>
     </row>
     <row r="17" ht="38.8" customHeight="1">
-      <c r="B17" s="23" t="inlineStr">
+      <c r="B17" s="27" t="inlineStr">
         <is>
           <t>Instapmoment</t>
         </is>
@@ -25585,7 +26153,7 @@
       </c>
     </row>
     <row r="18" ht="56.2" customHeight="1">
-      <c r="B18" s="24" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>Waarom sterk</t>
         </is>
@@ -25597,19 +26165,19 @@
       </c>
     </row>
     <row r="19" ht="38.8" customHeight="1">
-      <c r="B19" s="24" t="inlineStr">
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t>Plan van de bot</t>
         </is>
       </c>
-      <c r="C19" s="25" t="inlineStr">
+      <c r="C19" s="29" t="inlineStr">
         <is>
           <t>Koop 5 stuks rond 78,10 EUR (inzet €390,50). Stop-loss op 73,68 EUR (-5,7%). Gaat het mis, dan is het verlies ongeveer €24,10.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="21.4" customHeight="1">
-      <c r="B20" s="24" t="inlineStr">
+      <c r="B20" s="28" t="inlineStr">
         <is>
           <t>Wat deed de bot?</t>
         </is>
@@ -25628,7 +26196,7 @@
       </c>
     </row>
     <row r="23" ht="21.4" customHeight="1">
-      <c r="B23" s="24" t="inlineStr">
+      <c r="B23" s="28" t="inlineStr">
         <is>
           <t>Instapmoment</t>
         </is>
@@ -25640,7 +26208,7 @@
       </c>
     </row>
     <row r="24" ht="56.2" customHeight="1">
-      <c r="B24" s="24" t="inlineStr">
+      <c r="B24" s="28" t="inlineStr">
         <is>
           <t>Waarom sterk</t>
         </is>
@@ -25652,19 +26220,19 @@
       </c>
     </row>
     <row r="25" ht="38.8" customHeight="1">
-      <c r="B25" s="24" t="inlineStr">
+      <c r="B25" s="28" t="inlineStr">
         <is>
           <t>Plan van de bot</t>
         </is>
       </c>
-      <c r="C25" s="25" t="inlineStr">
-        <is>
-          <t>Koop 11 stuks rond 67,66 USD (inzet €667,12). Stop-loss op 65,22 USD (-3,6%). Gaat het mis, dan is het verlies ongeveer €26,10.</t>
+      <c r="C25" s="29" t="inlineStr">
+        <is>
+          <t>Koop 11 stuks rond 67,66 USD (inzet €663,77). Stop-loss op 65,22 USD (-3,6%). Gaat het mis, dan is het verlies ongeveer €25,98.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="21.4" customHeight="1">
-      <c r="B26" s="24" t="inlineStr">
+      <c r="B26" s="28" t="inlineStr">
         <is>
           <t>Wat deed de bot?</t>
         </is>
@@ -25683,7 +26251,7 @@
       </c>
     </row>
     <row r="29" ht="38.8" customHeight="1">
-      <c r="B29" s="23" t="inlineStr">
+      <c r="B29" s="27" t="inlineStr">
         <is>
           <t>Instapmoment</t>
         </is>
@@ -25695,7 +26263,7 @@
       </c>
     </row>
     <row r="30" ht="56.2" customHeight="1">
-      <c r="B30" s="24" t="inlineStr">
+      <c r="B30" s="28" t="inlineStr">
         <is>
           <t>Waarom sterk</t>
         </is>
@@ -25707,19 +26275,19 @@
       </c>
     </row>
     <row r="31" ht="38.8" customHeight="1">
-      <c r="B31" s="24" t="inlineStr">
+      <c r="B31" s="28" t="inlineStr">
         <is>
           <t>Plan van de bot</t>
         </is>
       </c>
-      <c r="C31" s="25" t="inlineStr">
-        <is>
-          <t>Koop 4 stuks rond 177,10 USD (inzet €634,93). Stop-loss op 170,67 USD (-3,6%). Gaat het mis, dan is het verlies ongeveer €25,04.</t>
+      <c r="C31" s="29" t="inlineStr">
+        <is>
+          <t>Koop 4 stuks rond 177,10 USD (inzet €631,75). Stop-loss op 170,67 USD (-3,6%). Gaat het mis, dan is het verlies ongeveer €24,92.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="21.4" customHeight="1">
-      <c r="B32" s="24" t="inlineStr">
+      <c r="B32" s="28" t="inlineStr">
         <is>
           <t>Wat deed de bot?</t>
         </is>
@@ -25736,7 +26304,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -25752,106 +26320,106 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>Bot</t>
         </is>
       </c>
-      <c r="B1" s="15" t="inlineStr">
+      <c r="B1" s="21" t="inlineStr">
         <is>
           <t>Eis</t>
         </is>
       </c>
-      <c r="C1" s="15" t="inlineStr">
+      <c r="C1" s="21" t="inlineStr">
         <is>
           <t>Stand</t>
         </is>
       </c>
-      <c r="D1" s="15" t="inlineStr">
+      <c r="D1" s="21" t="inlineStr">
         <is>
           <t>Nu</t>
         </is>
       </c>
     </row>
     <row r="2" ht="19.95" customHeight="1">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="B2" s="16" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>Oefentijd</t>
         </is>
       </c>
-      <c r="C2" s="16" t="inlineStr">
+      <c r="C2" s="17" t="inlineStr">
         <is>
           <t>⏳ nog bezig</t>
         </is>
       </c>
-      <c r="D2" s="16" t="inlineStr">
+      <c r="D2" s="17" t="inlineStr">
         <is>
           <t>2 van 63 handelsdagen (ongeveer 3 maanden)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19.95" customHeight="1">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>Minstens zo goed als de wereld-ETF</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="C3" s="17" t="inlineStr">
         <is>
           <t>⏳ nog bezig</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>verschil tot nu toe -1,31%</t>
+      <c r="D3" s="17" t="inlineStr">
+        <is>
+          <t>verschil tot nu toe -1,46%</t>
         </is>
       </c>
     </row>
     <row r="4" ht="19.95" customHeight="1">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>Daling niet veel dieper dan de ETF</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>✅ gehaald</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
-        <is>
-          <t>bot -1,79%, ETF -0,34%</t>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>bot -1,97%, ETF -0,36%</t>
         </is>
       </c>
     </row>
     <row r="5" ht="35.9" customHeight="1">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>Oordeel</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr"/>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr"/>
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>Nog niet klaar: de bot is nog bezig met bewijzen. Blijven oefenen.</t>
         </is>
@@ -25859,106 +26427,106 @@
     </row>
     <row r="6" ht="18" customHeight="1"/>
     <row r="7" ht="19.95" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>Oefentijd</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>⏳ nog bezig</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>3 van 63 handelsdagen (ongeveer 3 maanden)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="19.95" customHeight="1">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>Minstens zo goed als de wereld-ETF</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>⏳ nog bezig</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>verschil tot nu toe +0,46%</t>
         </is>
       </c>
     </row>
     <row r="9" ht="19.95" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>Grootste daling onder 5%</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>✅ gehaald</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>grootste daling tot nu toe -0,04%</t>
         </is>
       </c>
     </row>
     <row r="10" ht="19.95" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>Genoeg afgesloten trades</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>⏳ nog bezig</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>0 van 20</t>
         </is>
       </c>
     </row>
     <row r="11" ht="35.9" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>Oordeel</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr"/>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr"/>
+      <c r="D11" s="25" t="inlineStr">
         <is>
           <t>Nog niet klaar: de bot is nog bezig met bewijzen. Blijven oefenen.</t>
         </is>
@@ -25966,8 +26534,8 @@
     </row>
     <row r="12" ht="18" customHeight="1"/>
     <row r="13" ht="67.8" customHeight="1">
-      <c r="A13" s="16" t="inlineStr"/>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr"/>
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>Eerst bewijzen, dan een oefenaccount bij een echte broker, dan een klein bedrag met jouw goedkeuring per order. Die beslissing neem jij, niet de bot.</t>
         </is>
@@ -25979,7 +26547,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -25997,32 +26565,32 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="B1" s="15" t="inlineStr">
+      <c r="B1" s="21" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="C1" s="15" t="inlineStr">
+      <c r="C1" s="21" t="inlineStr">
         <is>
           <t>Investeerder t.o.v. start</t>
         </is>
       </c>
-      <c r="D1" s="15" t="inlineStr">
+      <c r="D1" s="21" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="E1" s="15" t="inlineStr">
+      <c r="E1" s="21" t="inlineStr">
         <is>
           <t>Trend-agent t.o.v. start</t>
         </is>
       </c>
-      <c r="F1" s="15" t="inlineStr">
+      <c r="F1" s="21" t="inlineStr">
         <is>
           <t>Wereld-ETF (koers in €)</t>
         </is>
@@ -26034,16 +26602,16 @@
           <t>start</t>
         </is>
       </c>
-      <c r="B2" s="21" t="n">
+      <c r="B2" s="26" t="n">
         <v>10000</v>
       </c>
-      <c r="C2" s="17" t="n">
+      <c r="C2" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D2" s="21" t="n">
+      <c r="D2" s="26" t="n">
         <v>10000</v>
       </c>
-      <c r="E2" s="17" t="n">
+      <c r="E2" s="22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -26053,12 +26621,12 @@
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B3" s="21" t="n"/>
-      <c r="C3" s="17" t="n"/>
-      <c r="D3" s="21" t="n">
+      <c r="B3" s="26" t="n"/>
+      <c r="C3" s="22" t="n"/>
+      <c r="D3" s="26" t="n">
         <v>9996.280000000001</v>
       </c>
-      <c r="E3" s="17" t="n">
+      <c r="E3" s="22" t="n">
         <v>-3.72</v>
       </c>
     </row>
@@ -26068,16 +26636,16 @@
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="B4" s="21" t="n">
+      <c r="B4" s="26" t="n">
         <v>9985.620000000001</v>
       </c>
-      <c r="C4" s="17" t="n">
+      <c r="C4" s="22" t="n">
         <v>-14.38</v>
       </c>
-      <c r="D4" s="21" t="n">
+      <c r="D4" s="26" t="n">
         <v>10014.42</v>
       </c>
-      <c r="E4" s="17" t="n">
+      <c r="E4" s="22" t="n">
         <v>14.42</v>
       </c>
       <c r="F4" t="n">
@@ -26090,20 +26658,20 @@
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="B5" s="21" t="n">
-        <v>9820.690000000001</v>
-      </c>
-      <c r="C5" s="17" t="n">
-        <v>-179.31</v>
-      </c>
-      <c r="D5" s="21" t="n">
-        <v>10026.55</v>
-      </c>
-      <c r="E5" s="17" t="n">
-        <v>26.55</v>
+      <c r="B5" s="26" t="n">
+        <v>9803.33</v>
+      </c>
+      <c r="C5" s="22" t="n">
+        <v>-196.67</v>
+      </c>
+      <c r="D5" s="26" t="n">
+        <v>10024.15</v>
+      </c>
+      <c r="E5" s="22" t="n">
+        <v>24.15</v>
       </c>
       <c r="F5" t="n">
-        <v>131.81</v>
+        <v>131.78</v>
       </c>
     </row>
   </sheetData>
@@ -26112,7 +26680,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -26134,74 +26702,74 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="B1" s="15" t="inlineStr">
+      <c r="B1" s="21" t="inlineStr">
         <is>
           <t>Bot</t>
         </is>
       </c>
-      <c r="C1" s="15" t="inlineStr">
+      <c r="C1" s="21" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="D1" s="15" t="inlineStr">
+      <c r="D1" s="21" t="inlineStr">
         <is>
           <t>Koop/verkoop</t>
         </is>
       </c>
-      <c r="E1" s="15" t="inlineStr">
+      <c r="E1" s="21" t="inlineStr">
         <is>
           <t>Aantal</t>
         </is>
       </c>
-      <c r="F1" s="15" t="inlineStr">
+      <c r="F1" s="21" t="inlineStr">
         <is>
           <t>Prijs</t>
         </is>
       </c>
-      <c r="G1" s="15" t="inlineStr">
+      <c r="G1" s="21" t="inlineStr">
         <is>
           <t>Waarde €</t>
         </is>
       </c>
-      <c r="H1" s="15" t="inlineStr">
+      <c r="H1" s="21" t="inlineStr">
         <is>
           <t>Kosten €</t>
         </is>
       </c>
-      <c r="I1" s="15" t="inlineStr">
+      <c r="I1" s="21" t="inlineStr">
         <is>
           <t>Resultaat €</t>
         </is>
       </c>
-      <c r="J1" s="15" t="inlineStr">
+      <c r="J1" s="21" t="inlineStr">
         <is>
           <t>Reden</t>
         </is>
       </c>
     </row>
     <row r="2" ht="19.95" customHeight="1">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B2" s="16" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="C2" s="16" t="inlineStr">
+      <c r="C2" s="17" t="inlineStr">
         <is>
           <t>SHELL.AS</t>
         </is>
       </c>
-      <c r="D2" s="16" t="inlineStr">
+      <c r="D2" s="17" t="inlineStr">
         <is>
           <t>koop</t>
         </is>
@@ -26212,36 +26780,36 @@
       <c r="F2" t="n">
         <v>45.0575</v>
       </c>
-      <c r="G2" s="21" t="n">
+      <c r="G2" s="26" t="n">
         <v>585.75</v>
       </c>
-      <c r="H2" s="21" t="n">
+      <c r="H2" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="17" t="n"/>
-      <c r="J2" s="16" t="inlineStr">
+      <c r="I2" s="22" t="n"/>
+      <c r="J2" s="17" t="inlineStr">
         <is>
           <t>trend OK: 3m +23.4%, 1m +9.2%, volume x1.07</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19.95" customHeight="1">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="C3" s="17" t="inlineStr">
         <is>
           <t>SAP.DE</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="D3" s="17" t="inlineStr">
         <is>
           <t>koop</t>
         </is>
@@ -26252,36 +26820,36 @@
       <c r="F3" t="n">
         <v>191.5557</v>
       </c>
-      <c r="G3" s="21" t="n">
+      <c r="G3" s="26" t="n">
         <v>383.11</v>
       </c>
-      <c r="H3" s="21" t="n">
+      <c r="H3" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="I3" s="17" t="n"/>
-      <c r="J3" s="16" t="inlineStr">
+      <c r="I3" s="22" t="n"/>
+      <c r="J3" s="17" t="inlineStr">
         <is>
           <t>trend OK: 3m +40.0%, 1m +7.7%, volume x0.83</t>
         </is>
       </c>
     </row>
     <row r="4" ht="19.95" customHeight="1">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>MSFT</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>koop</t>
         </is>
@@ -26292,36 +26860,36 @@
       <c r="F4" t="n">
         <v>535.3375</v>
       </c>
-      <c r="G4" s="21" t="n">
+      <c r="G4" s="26" t="n">
         <v>477.74</v>
       </c>
-      <c r="H4" s="21" t="n">
+      <c r="H4" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="I4" s="17" t="n"/>
-      <c r="J4" s="16" t="inlineStr">
+      <c r="I4" s="22" t="n"/>
+      <c r="J4" s="17" t="inlineStr">
         <is>
           <t>trend OK: 3m +37.1%, 1m +8.7%, volume x0.82</t>
         </is>
       </c>
     </row>
     <row r="5" ht="19.95" customHeight="1">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>IWDA.AS</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>koop</t>
         </is>
@@ -26332,36 +26900,36 @@
       <c r="F5" t="n">
         <v>131.7358</v>
       </c>
-      <c r="G5" s="21" t="n">
+      <c r="G5" s="26" t="n">
         <v>5997</v>
       </c>
-      <c r="H5" s="21" t="n">
+      <c r="H5" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="I5" s="17" t="n"/>
-      <c r="J5" s="16" t="inlineStr">
+      <c r="I5" s="22" t="n"/>
+      <c r="J5" s="17" t="inlineStr">
         <is>
           <t>doelgewicht 60%</t>
         </is>
       </c>
     </row>
     <row r="6" ht="19.95" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>MU</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>koop</t>
         </is>
@@ -26372,36 +26940,36 @@
       <c r="F6" t="n">
         <v>885.2376</v>
       </c>
-      <c r="G6" s="21" t="n">
+      <c r="G6" s="26" t="n">
         <v>599</v>
       </c>
-      <c r="H6" s="21" t="n">
+      <c r="H6" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="I6" s="17" t="n"/>
-      <c r="J6" s="16" t="inlineStr">
+      <c r="I6" s="22" t="n"/>
+      <c r="J6" s="17" t="inlineStr">
         <is>
           <t>doelgewicht 6%</t>
         </is>
       </c>
     </row>
     <row r="7" ht="19.95" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>SMH</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>koop</t>
         </is>
@@ -26412,36 +26980,36 @@
       <c r="F7" t="n">
         <v>528.9640000000001</v>
       </c>
-      <c r="G7" s="21" t="n">
+      <c r="G7" s="26" t="n">
         <v>599</v>
       </c>
-      <c r="H7" s="21" t="n">
+      <c r="H7" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="I7" s="17" t="n"/>
-      <c r="J7" s="16" t="inlineStr">
+      <c r="I7" s="22" t="n"/>
+      <c r="J7" s="17" t="inlineStr">
         <is>
           <t>doelgewicht 6%</t>
         </is>
       </c>
     </row>
     <row r="8" ht="19.95" customHeight="1">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>ASML.AS</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>koop</t>
         </is>
@@ -26452,36 +27020,36 @@
       <c r="F8" t="n">
         <v>1602.4008</v>
       </c>
-      <c r="G8" s="21" t="n">
+      <c r="G8" s="26" t="n">
         <v>599</v>
       </c>
-      <c r="H8" s="21" t="n">
+      <c r="H8" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="I8" s="17" t="n"/>
-      <c r="J8" s="16" t="inlineStr">
+      <c r="I8" s="22" t="n"/>
+      <c r="J8" s="17" t="inlineStr">
         <is>
           <t>doelgewicht 6%</t>
         </is>
       </c>
     </row>
     <row r="9" ht="19.95" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>IFX.DE</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>koop</t>
         </is>
@@ -26492,36 +27060,36 @@
       <c r="F9" t="n">
         <v>58.8894</v>
       </c>
-      <c r="G9" s="21" t="n">
+      <c r="G9" s="26" t="n">
         <v>599</v>
       </c>
-      <c r="H9" s="21" t="n">
+      <c r="H9" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="17" t="n"/>
-      <c r="J9" s="16" t="inlineStr">
+      <c r="I9" s="22" t="n"/>
+      <c r="J9" s="17" t="inlineStr">
         <is>
           <t>doelgewicht 6%</t>
         </is>
       </c>
     </row>
     <row r="10" ht="19.95" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>AMD</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>koop</t>
         </is>
@@ -26532,36 +27100,36 @@
       <c r="F10" t="n">
         <v>531.8729</v>
       </c>
-      <c r="G10" s="21" t="n">
+      <c r="G10" s="26" t="n">
         <v>599</v>
       </c>
-      <c r="H10" s="21" t="n">
+      <c r="H10" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="17" t="n"/>
-      <c r="J10" s="16" t="inlineStr">
+      <c r="I10" s="22" t="n"/>
+      <c r="J10" s="17" t="inlineStr">
         <is>
           <t>doelgewicht 6%</t>
         </is>
       </c>
     </row>
     <row r="11" ht="19.95" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>ETH-USD</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>koop</t>
         </is>
@@ -26572,36 +27140,36 @@
       <c r="F11" t="n">
         <v>2220.7914</v>
       </c>
-      <c r="G11" s="21" t="n">
+      <c r="G11" s="26" t="n">
         <v>499</v>
       </c>
-      <c r="H11" s="21" t="n">
+      <c r="H11" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="17" t="n"/>
-      <c r="J11" s="16" t="inlineStr">
+      <c r="I11" s="22" t="n"/>
+      <c r="J11" s="17" t="inlineStr">
         <is>
           <t>doelgewicht 5%</t>
         </is>
       </c>
     </row>
     <row r="12" ht="19.95" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>Investeerder</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>BTC-USD</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>koop</t>
         </is>
@@ -26612,95 +27180,16 @@
       <c r="F12" t="n">
         <v>74036.6848</v>
       </c>
-      <c r="G12" s="21" t="n">
+      <c r="G12" s="26" t="n">
         <v>499</v>
       </c>
-      <c r="H12" s="21" t="n">
+      <c r="H12" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="17" t="n"/>
-      <c r="J12" s="16" t="inlineStr">
+      <c r="I12" s="22" t="n"/>
+      <c r="J12" s="17" t="inlineStr">
         <is>
           <t>doelgewicht 5%</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="120" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="15" t="inlineStr">
-        <is>
-          <t>Bot</t>
-        </is>
-      </c>
-      <c r="B1" s="15" t="inlineStr">
-        <is>
-          <t>Controle</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="19.95" customHeight="1">
-      <c r="A2" s="16" t="inlineStr">
-        <is>
-          <t>Investeerder</t>
-        </is>
-      </c>
-      <c r="B2" s="16" t="inlineStr">
-        <is>
-          <t>Investeerder: status OK, 52 van 52 koersen opgehaald, marktregime stijgend-laag.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="35.9" customHeight="1">
-      <c r="A3" s="16" t="inlineStr">
-        <is>
-          <t>Investeerder</t>
-        </is>
-      </c>
-      <c r="B3" s="16" t="inlineStr">
-        <is>
-          <t>Koersbronnen: 0 bevestigd door twee bronnen, 52 uit één bron, 0 afwijkend. Wisselkoers: bevestigd. Tweede bron overgeslagen na herhaalde fouten (ophalen mislukt: URLError).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="19.95" customHeight="1">
-      <c r="A4" s="16" t="inlineStr">
-        <is>
-          <t>Trend-agent</t>
-        </is>
-      </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>Trend-agent: status OK, 50 van 50 koersen opgehaald, marktregime stijgend-laag.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="35.9" customHeight="1">
-      <c r="A5" s="16" t="inlineStr">
-        <is>
-          <t>Trend-agent</t>
-        </is>
-      </c>
-      <c r="B5" s="16" t="inlineStr">
-        <is>
-          <t>Koersbronnen: 0 bevestigd door twee bronnen, 50 uit één bron, 0 afwijkend. Wisselkoers: bevestigd. Tweede bron overgeslagen na herhaalde fouten (ophalen mislukt: URLError).</t>
         </is>
       </c>
     </row>
